--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -2,26 +2,26 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Siemens Hardware" sheetId="1" r:id="R61cf93095cce4124"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC I-O" sheetId="2" r:id="R6c74ab199ad84670"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drive PZD" sheetId="3" r:id="Rf5386f58899a4175"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HMI Tags" sheetId="4" r:id="R52a62229ba854538"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alarms" sheetId="5" r:id="Rb6044d8bfbae4b77"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFD Parameters" sheetId="6" r:id="R92576ecd5d6e43f9"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA Interface" sheetId="7" r:id="R955b67535ab44798"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Nodes" sheetId="8" r:id="R2f07a0cdce4f4346"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Terminal Plan" sheetId="9" r:id="Redf81f7179ae4ff6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Point-to-Point" sheetId="10" r:id="R67058d6e79a44937"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cable Schedule" sheetId="11" r:id="R8ea039e2baa54ec7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire List" sheetId="12" r:id="Rb838ce9cc2154b0e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="13" r:id="R97596f8083044a3d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Budget" sheetId="14" r:id="Rd3fc450bf3194e42"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel Placement" sheetId="15" r:id="R3ad84b88f5044b43"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements Trace" sheetId="16" r:id="Rdf298c35d9c74913"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Coverage" sheetId="17" r:id="R6e504f7491df49db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Requests" sheetId="18" r:id="Rdb13e664a0854704"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Gates" sheetId="19" r:id="R163815556b6a4e97"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="20" r:id="Rbf1f6f2496ad40f7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Siemens Hardware" sheetId="1" r:id="rId4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PLC I-O" sheetId="2" r:id="rId5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Drive PZD" sheetId="3" r:id="rId6"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HMI Tags" sheetId="4" r:id="rId7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alarms" sheetId="5" r:id="rId8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VFD Parameters" sheetId="6" r:id="rId9"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA Interface" sheetId="7" r:id="rId10"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Nodes" sheetId="8" r:id="rId11"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Terminal Plan" sheetId="9" r:id="rId12"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Point-to-Point" sheetId="10" r:id="rId13"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cable Schedule" sheetId="11" r:id="rId14"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire List" sheetId="12" r:id="rId15"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="13" r:id="rId16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Budget" sheetId="14" r:id="rId17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel Placement" sheetId="15" r:id="rId18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements Trace" sheetId="16" r:id="rId19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Coverage" sheetId="17" r:id="rId20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Requests" sheetId="18" r:id="rId21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Gates" sheetId="19" r:id="rId22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="20" r:id="rId23"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -32,7 +32,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="8">
+  <x:fonts count="9">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -58,6 +58,12 @@
       <x:b/>
       <x:sz val="10"/>
       <x:color rgb="FF324B5C"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="8"/>
+      <x:color rgb="FF8B1E2D"/>
       <x:name val="Carlito"/>
     </x:font>
     <x:font>
@@ -97,17 +103,17 @@
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFF1F1"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
         <x:fgColor rgb="FF1F6F9F"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FFC43D3D"/>
-      </x:patternFill>
-    </x:fill>
-    <x:fill>
-      <x:patternFill patternType="solid">
-        <x:fgColor rgb="FFFFF1F1"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -118,7 +124,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="43">
+  <x:cellXfs count="47">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -177,23 +183,31 @@
     <x:xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -401,8 +415,8 @@
 </file>
 
 <file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="InputRequestsTable" displayName="InputRequestsTable" ref="A1:G21" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:G21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="InputRequestsTable" displayName="InputRequestsTable" ref="A1:G28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:G28"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="request_id"/>
     <x:tableColumn id="2" name="required_input"/>
@@ -486,8 +500,8 @@
 </file>
 
 <file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="AlarmsTable" displayName="AlarmsTable" ref="A1:F36" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="5" name="AlarmsTable" displayName="AlarmsTable" ref="A1:F40" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F40"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="alarm_id"/>
     <x:tableColumn id="2" name="message"/>
@@ -514,8 +528,8 @@
 </file>
 
 <file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NVIDIAInterfaceTable" displayName="NVIDIAInterfaceTable" ref="A1:F22" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="7" name="NVIDIAInterfaceTable" displayName="NVIDIAInterfaceTable" ref="A1:F28" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F28"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="signal"/>
     <x:tableColumn id="2" name="data_type"/>
@@ -1328,7 +1342,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8b644a5d0dd14175"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -1472,9 +1486,7 @@
       </x:c>
       <x:c r="Q2" s="6" t="str"/>
       <x:c r="R2" s="6" t="str"/>
-      <x:c r="S2" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S2" s="6" t="str"/>
       <x:c r="T2" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -1482,7 +1494,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V2" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="27" customHeight="1">
@@ -1528,9 +1540,7 @@
       </x:c>
       <x:c r="Q3" s="6" t="str"/>
       <x:c r="R3" s="6" t="str"/>
-      <x:c r="S3" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S3" s="6" t="str"/>
       <x:c r="T3" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -1538,7 +1548,7 @@
         <x:v>=FC01+CP01-A102:0</x:v>
       </x:c>
       <x:c r="V3" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
@@ -1590,9 +1600,7 @@
       </x:c>
       <x:c r="Q4" s="6" t="str"/>
       <x:c r="R4" s="6" t="str"/>
-      <x:c r="S4" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S4" s="6" t="str"/>
       <x:c r="T4" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -1600,7 +1608,7 @@
         <x:v>=FC01+CP01-A102:1</x:v>
       </x:c>
       <x:c r="V4" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -1652,9 +1660,7 @@
       </x:c>
       <x:c r="Q5" s="6" t="str"/>
       <x:c r="R5" s="6" t="str"/>
-      <x:c r="S5" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S5" s="6" t="str"/>
       <x:c r="T5" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -1662,7 +1668,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V5" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
@@ -1714,9 +1720,7 @@
       </x:c>
       <x:c r="Q6" s="6" t="str"/>
       <x:c r="R6" s="6" t="str"/>
-      <x:c r="S6" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S6" s="6" t="str"/>
       <x:c r="T6" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -1724,7 +1728,7 @@
         <x:v>=FC01+CP01-A102:2</x:v>
       </x:c>
       <x:c r="V6" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
@@ -1776,9 +1780,7 @@
       </x:c>
       <x:c r="Q7" s="6" t="str"/>
       <x:c r="R7" s="6" t="str"/>
-      <x:c r="S7" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S7" s="6" t="str"/>
       <x:c r="T7" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -1786,7 +1788,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V7" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
@@ -1840,9 +1842,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R8" s="6" t="str"/>
-      <x:c r="S8" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S8" s="6" t="str"/>
       <x:c r="T8" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -1850,7 +1850,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V8" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
@@ -1902,9 +1902,7 @@
       </x:c>
       <x:c r="Q9" s="6" t="str"/>
       <x:c r="R9" s="6" t="str"/>
-      <x:c r="S9" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S9" s="6" t="str"/>
       <x:c r="T9" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -1912,7 +1910,7 @@
         <x:v>=FC01+CP01-A102:3</x:v>
       </x:c>
       <x:c r="V9" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
@@ -1964,9 +1962,7 @@
       </x:c>
       <x:c r="Q10" s="6" t="str"/>
       <x:c r="R10" s="6" t="str"/>
-      <x:c r="S10" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S10" s="6" t="str"/>
       <x:c r="T10" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -1974,7 +1970,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V10" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
@@ -2028,9 +2024,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R11" s="6" t="str"/>
-      <x:c r="S11" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S11" s="6" t="str"/>
       <x:c r="T11" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -2038,7 +2032,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V11" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
@@ -2090,9 +2084,7 @@
       </x:c>
       <x:c r="Q12" s="6" t="str"/>
       <x:c r="R12" s="6" t="str"/>
-      <x:c r="S12" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S12" s="6" t="str"/>
       <x:c r="T12" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -2100,7 +2092,7 @@
         <x:v>=FC01+CP01-A102:10</x:v>
       </x:c>
       <x:c r="V12" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
@@ -2152,9 +2144,7 @@
       </x:c>
       <x:c r="Q13" s="6" t="str"/>
       <x:c r="R13" s="6" t="str"/>
-      <x:c r="S13" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S13" s="6" t="str"/>
       <x:c r="T13" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -2162,7 +2152,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V13" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
@@ -2216,9 +2206,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R14" s="6" t="str"/>
-      <x:c r="S14" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S14" s="6" t="str"/>
       <x:c r="T14" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -2226,7 +2214,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V14" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
@@ -2278,9 +2266,7 @@
       </x:c>
       <x:c r="Q15" s="6" t="str"/>
       <x:c r="R15" s="6" t="str"/>
-      <x:c r="S15" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S15" s="6" t="str"/>
       <x:c r="T15" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -2288,7 +2274,7 @@
         <x:v>=FC01+CP01-A102:11</x:v>
       </x:c>
       <x:c r="V15" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
@@ -2340,9 +2326,7 @@
       </x:c>
       <x:c r="Q16" s="6" t="str"/>
       <x:c r="R16" s="6" t="str"/>
-      <x:c r="S16" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S16" s="6" t="str"/>
       <x:c r="T16" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -2350,7 +2334,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V16" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
@@ -2404,9 +2388,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R17" s="6" t="str"/>
-      <x:c r="S17" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S17" s="6" t="str"/>
       <x:c r="T17" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -2414,7 +2396,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V17" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
@@ -2466,9 +2448,7 @@
       </x:c>
       <x:c r="Q18" s="6" t="str"/>
       <x:c r="R18" s="6" t="str"/>
-      <x:c r="S18" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S18" s="6" t="str"/>
       <x:c r="T18" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -2476,7 +2456,7 @@
         <x:v>=FC01+CP01-A102:12</x:v>
       </x:c>
       <x:c r="V18" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
@@ -2528,9 +2508,7 @@
       </x:c>
       <x:c r="Q19" s="6" t="str"/>
       <x:c r="R19" s="6" t="str"/>
-      <x:c r="S19" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S19" s="6" t="str"/>
       <x:c r="T19" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -2538,7 +2516,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V19" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
@@ -2592,9 +2570,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R20" s="6" t="str"/>
-      <x:c r="S20" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S20" s="6" t="str"/>
       <x:c r="T20" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -2602,7 +2578,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V20" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
@@ -2654,9 +2630,7 @@
       </x:c>
       <x:c r="Q21" s="6" t="str"/>
       <x:c r="R21" s="6" t="str"/>
-      <x:c r="S21" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S21" s="6" t="str"/>
       <x:c r="T21" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -2664,7 +2638,7 @@
         <x:v>=FC01+CP01-A102:13</x:v>
       </x:c>
       <x:c r="V21" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
@@ -2716,9 +2690,7 @@
       </x:c>
       <x:c r="Q22" s="6" t="str"/>
       <x:c r="R22" s="6" t="str"/>
-      <x:c r="S22" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S22" s="6" t="str"/>
       <x:c r="T22" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -2726,7 +2698,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V22" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
@@ -2780,9 +2752,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R23" s="6" t="str"/>
-      <x:c r="S23" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S23" s="6" t="str"/>
       <x:c r="T23" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -2790,7 +2760,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V23" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="27" customHeight="1">
@@ -2842,9 +2812,7 @@
       </x:c>
       <x:c r="Q24" s="6" t="str"/>
       <x:c r="R24" s="6" t="str"/>
-      <x:c r="S24" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S24" s="6" t="str"/>
       <x:c r="T24" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -2852,7 +2820,7 @@
         <x:v>=FC01+CP01-A102:14</x:v>
       </x:c>
       <x:c r="V24" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
@@ -2904,9 +2872,7 @@
       </x:c>
       <x:c r="Q25" s="6" t="str"/>
       <x:c r="R25" s="6" t="str"/>
-      <x:c r="S25" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S25" s="6" t="str"/>
       <x:c r="T25" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -2914,7 +2880,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V25" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
@@ -2968,9 +2934,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R26" s="6" t="str"/>
-      <x:c r="S26" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S26" s="6" t="str"/>
       <x:c r="T26" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -2978,7 +2942,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V26" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
@@ -3030,9 +2994,7 @@
       </x:c>
       <x:c r="Q27" s="6" t="str"/>
       <x:c r="R27" s="6" t="str"/>
-      <x:c r="S27" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S27" s="6" t="str"/>
       <x:c r="T27" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3040,7 +3002,7 @@
         <x:v>=FC01+CP01-A102:15</x:v>
       </x:c>
       <x:c r="V27" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="27" customHeight="1">
@@ -3092,9 +3054,7 @@
       </x:c>
       <x:c r="Q28" s="6" t="str"/>
       <x:c r="R28" s="6" t="str"/>
-      <x:c r="S28" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S28" s="6" t="str"/>
       <x:c r="T28" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -3102,7 +3062,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V28" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="27" customHeight="1">
@@ -3156,9 +3116,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R29" s="6" t="str"/>
-      <x:c r="S29" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S29" s="6" t="str"/>
       <x:c r="T29" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -3166,7 +3124,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V29" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="27" customHeight="1">
@@ -3218,9 +3176,7 @@
       </x:c>
       <x:c r="Q30" s="6" t="str"/>
       <x:c r="R30" s="6" t="str"/>
-      <x:c r="S30" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S30" s="6" t="str"/>
       <x:c r="T30" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3228,7 +3184,7 @@
         <x:v>=FC01+CP01-A102:16</x:v>
       </x:c>
       <x:c r="V30" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="27" customHeight="1">
@@ -3280,9 +3236,7 @@
       </x:c>
       <x:c r="Q31" s="6" t="str"/>
       <x:c r="R31" s="6" t="str"/>
-      <x:c r="S31" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S31" s="6" t="str"/>
       <x:c r="T31" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -3290,7 +3244,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V31" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="27" customHeight="1">
@@ -3344,9 +3298,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R32" s="6" t="str"/>
-      <x:c r="S32" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S32" s="6" t="str"/>
       <x:c r="T32" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -3354,7 +3306,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V32" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="27" customHeight="1">
@@ -3406,9 +3358,7 @@
       </x:c>
       <x:c r="Q33" s="6" t="str"/>
       <x:c r="R33" s="6" t="str"/>
-      <x:c r="S33" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S33" s="6" t="str"/>
       <x:c r="T33" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3416,7 +3366,7 @@
         <x:v>=FC01+CP01-A102:17</x:v>
       </x:c>
       <x:c r="V33" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="27" customHeight="1">
@@ -3468,9 +3418,7 @@
       </x:c>
       <x:c r="Q34" s="6" t="str"/>
       <x:c r="R34" s="6" t="str"/>
-      <x:c r="S34" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S34" s="6" t="str"/>
       <x:c r="T34" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -3478,7 +3426,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V34" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="27" customHeight="1">
@@ -3532,9 +3480,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R35" s="6" t="str"/>
-      <x:c r="S35" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S35" s="6" t="str"/>
       <x:c r="T35" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -3542,7 +3488,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V35" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="27" customHeight="1">
@@ -3594,9 +3540,7 @@
       </x:c>
       <x:c r="Q36" s="6" t="str"/>
       <x:c r="R36" s="6" t="str"/>
-      <x:c r="S36" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S36" s="6" t="str"/>
       <x:c r="T36" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3604,7 +3548,7 @@
         <x:v>=FC01+CP01-A102:18</x:v>
       </x:c>
       <x:c r="V36" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="27" customHeight="1">
@@ -3656,9 +3600,7 @@
       </x:c>
       <x:c r="Q37" s="6" t="str"/>
       <x:c r="R37" s="6" t="str"/>
-      <x:c r="S37" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S37" s="6" t="str"/>
       <x:c r="T37" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -3666,7 +3608,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V37" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="27" customHeight="1">
@@ -3720,9 +3662,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R38" s="6" t="str"/>
-      <x:c r="S38" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S38" s="6" t="str"/>
       <x:c r="T38" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -3730,7 +3670,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V38" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="27" customHeight="1">
@@ -3782,9 +3722,7 @@
       </x:c>
       <x:c r="Q39" s="6" t="str"/>
       <x:c r="R39" s="6" t="str"/>
-      <x:c r="S39" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S39" s="6" t="str"/>
       <x:c r="T39" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3792,7 +3730,7 @@
         <x:v>=FC01+CP01-A102:19</x:v>
       </x:c>
       <x:c r="V39" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="27" customHeight="1">
@@ -3844,9 +3782,7 @@
       </x:c>
       <x:c r="Q40" s="6" t="str"/>
       <x:c r="R40" s="6" t="str"/>
-      <x:c r="S40" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S40" s="6" t="str"/>
       <x:c r="T40" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3854,7 +3790,7 @@
         <x:v>=FC01+CP01-A102:20</x:v>
       </x:c>
       <x:c r="V40" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="27" customHeight="1">
@@ -3906,9 +3842,7 @@
       </x:c>
       <x:c r="Q41" s="6" t="str"/>
       <x:c r="R41" s="6" t="str"/>
-      <x:c r="S41" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S41" s="6" t="str"/>
       <x:c r="T41" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3916,7 +3850,7 @@
         <x:v>=FC01+CP01-A102:21</x:v>
       </x:c>
       <x:c r="V41" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="27" customHeight="1">
@@ -3968,9 +3902,7 @@
       </x:c>
       <x:c r="Q42" s="6" t="str"/>
       <x:c r="R42" s="6" t="str"/>
-      <x:c r="S42" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S42" s="6" t="str"/>
       <x:c r="T42" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -3978,7 +3910,7 @@
         <x:v>=FC01+CP01-A102:22</x:v>
       </x:c>
       <x:c r="V42" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="27" customHeight="1">
@@ -4030,9 +3962,7 @@
       </x:c>
       <x:c r="Q43" s="6" t="str"/>
       <x:c r="R43" s="6" t="str"/>
-      <x:c r="S43" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S43" s="6" t="str"/>
       <x:c r="T43" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -4040,7 +3970,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V43" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="27" customHeight="1">
@@ -4094,9 +4024,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R44" s="6" t="str"/>
-      <x:c r="S44" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S44" s="6" t="str"/>
       <x:c r="T44" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -4104,7 +4032,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V44" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="27" customHeight="1">
@@ -4156,9 +4084,7 @@
       </x:c>
       <x:c r="Q45" s="6" t="str"/>
       <x:c r="R45" s="6" t="str"/>
-      <x:c r="S45" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S45" s="6" t="str"/>
       <x:c r="T45" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -4166,7 +4092,7 @@
         <x:v>=FC01+CP01-A102:23</x:v>
       </x:c>
       <x:c r="V45" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="27" customHeight="1">
@@ -4218,9 +4144,7 @@
       </x:c>
       <x:c r="Q46" s="6" t="str"/>
       <x:c r="R46" s="6" t="str"/>
-      <x:c r="S46" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S46" s="6" t="str"/>
       <x:c r="T46" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -4228,7 +4152,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V46" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="27" customHeight="1">
@@ -4282,9 +4206,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R47" s="6" t="str"/>
-      <x:c r="S47" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S47" s="6" t="str"/>
       <x:c r="T47" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -4292,7 +4214,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V47" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="27" customHeight="1">
@@ -4340,9 +4262,7 @@
       </x:c>
       <x:c r="Q48" s="6" t="str"/>
       <x:c r="R48" s="6" t="str"/>
-      <x:c r="S48" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S48" s="6" t="str"/>
       <x:c r="T48" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -4350,7 +4270,7 @@
         <x:v>=FC01+CP01-A103:2</x:v>
       </x:c>
       <x:c r="V48" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="27" customHeight="1">
@@ -4400,9 +4320,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R49" s="6" t="str"/>
-      <x:c r="S49" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S49" s="6" t="str"/>
       <x:c r="T49" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -4410,7 +4328,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V49" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="27" customHeight="1">
@@ -4458,9 +4376,7 @@
       </x:c>
       <x:c r="Q50" s="6" t="str"/>
       <x:c r="R50" s="6" t="str"/>
-      <x:c r="S50" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S50" s="6" t="str"/>
       <x:c r="T50" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -4468,7 +4384,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V50" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="27" customHeight="1">
@@ -4522,9 +4438,7 @@
       </x:c>
       <x:c r="Q51" s="6" t="str"/>
       <x:c r="R51" s="6" t="str"/>
-      <x:c r="S51" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S51" s="6" t="str"/>
       <x:c r="T51" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -4532,7 +4446,7 @@
         <x:v>=FC01+CP01-K202:14</x:v>
       </x:c>
       <x:c r="V51" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="27" customHeight="1">
@@ -4588,9 +4502,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R52" s="6" t="str"/>
-      <x:c r="S52" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S52" s="6" t="str"/>
       <x:c r="T52" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -4598,7 +4510,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V52" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="27" customHeight="1">
@@ -4646,9 +4558,7 @@
       </x:c>
       <x:c r="Q53" s="6" t="str"/>
       <x:c r="R53" s="6" t="str"/>
-      <x:c r="S53" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S53" s="6" t="str"/>
       <x:c r="T53" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -4656,7 +4566,7 @@
         <x:v>=FC01+CP01-A103:3</x:v>
       </x:c>
       <x:c r="V53" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="27" customHeight="1">
@@ -4706,9 +4616,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R54" s="6" t="str"/>
-      <x:c r="S54" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S54" s="6" t="str"/>
       <x:c r="T54" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -4716,7 +4624,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V54" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="27" customHeight="1">
@@ -4764,9 +4672,7 @@
       </x:c>
       <x:c r="Q55" s="6" t="str"/>
       <x:c r="R55" s="6" t="str"/>
-      <x:c r="S55" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S55" s="6" t="str"/>
       <x:c r="T55" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -4774,7 +4680,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V55" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="27" customHeight="1">
@@ -4828,9 +4734,7 @@
       </x:c>
       <x:c r="Q56" s="6" t="str"/>
       <x:c r="R56" s="6" t="str"/>
-      <x:c r="S56" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S56" s="6" t="str"/>
       <x:c r="T56" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -4838,7 +4742,7 @@
         <x:v>=FC01+CP01-K203:14</x:v>
       </x:c>
       <x:c r="V56" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="27" customHeight="1">
@@ -4894,9 +4798,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R57" s="6" t="str"/>
-      <x:c r="S57" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S57" s="6" t="str"/>
       <x:c r="T57" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -4904,7 +4806,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V57" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="27" customHeight="1">
@@ -4952,9 +4854,7 @@
       </x:c>
       <x:c r="Q58" s="6" t="str"/>
       <x:c r="R58" s="6" t="str"/>
-      <x:c r="S58" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S58" s="6" t="str"/>
       <x:c r="T58" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -4962,7 +4862,7 @@
         <x:v>=FC01+CP01-A103:4</x:v>
       </x:c>
       <x:c r="V58" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="27" customHeight="1">
@@ -5012,9 +4912,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R59" s="6" t="str"/>
-      <x:c r="S59" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S59" s="6" t="str"/>
       <x:c r="T59" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -5022,7 +4920,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V59" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="27" customHeight="1">
@@ -5070,9 +4968,7 @@
       </x:c>
       <x:c r="Q60" s="6" t="str"/>
       <x:c r="R60" s="6" t="str"/>
-      <x:c r="S60" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S60" s="6" t="str"/>
       <x:c r="T60" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -5080,7 +4976,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V60" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="27" customHeight="1">
@@ -5134,9 +5030,7 @@
       </x:c>
       <x:c r="Q61" s="6" t="str"/>
       <x:c r="R61" s="6" t="str"/>
-      <x:c r="S61" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S61" s="6" t="str"/>
       <x:c r="T61" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -5144,7 +5038,7 @@
         <x:v>=FC01+CP01-K204:14</x:v>
       </x:c>
       <x:c r="V61" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="27" customHeight="1">
@@ -5200,9 +5094,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R62" s="6" t="str"/>
-      <x:c r="S62" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S62" s="6" t="str"/>
       <x:c r="T62" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -5210,7 +5102,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V62" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="27" customHeight="1">
@@ -5258,9 +5150,7 @@
       </x:c>
       <x:c r="Q63" s="6" t="str"/>
       <x:c r="R63" s="6" t="str"/>
-      <x:c r="S63" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S63" s="6" t="str"/>
       <x:c r="T63" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -5268,7 +5158,7 @@
         <x:v>=FC01+CP01-A103:5</x:v>
       </x:c>
       <x:c r="V63" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="27" customHeight="1">
@@ -5318,9 +5208,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R64" s="6" t="str"/>
-      <x:c r="S64" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S64" s="6" t="str"/>
       <x:c r="T64" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -5328,7 +5216,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V64" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="27" customHeight="1">
@@ -5376,9 +5264,7 @@
       </x:c>
       <x:c r="Q65" s="6" t="str"/>
       <x:c r="R65" s="6" t="str"/>
-      <x:c r="S65" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S65" s="6" t="str"/>
       <x:c r="T65" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -5386,7 +5272,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V65" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="27" customHeight="1">
@@ -5440,9 +5326,7 @@
       </x:c>
       <x:c r="Q66" s="6" t="str"/>
       <x:c r="R66" s="6" t="str"/>
-      <x:c r="S66" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S66" s="6" t="str"/>
       <x:c r="T66" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -5450,7 +5334,7 @@
         <x:v>=FC01+CP01-K205:14</x:v>
       </x:c>
       <x:c r="V66" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="27" customHeight="1">
@@ -5506,9 +5390,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R67" s="6" t="str"/>
-      <x:c r="S67" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S67" s="6" t="str"/>
       <x:c r="T67" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -5516,7 +5398,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V67" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="27" customHeight="1">
@@ -5564,9 +5446,7 @@
       </x:c>
       <x:c r="Q68" s="6" t="str"/>
       <x:c r="R68" s="6" t="str"/>
-      <x:c r="S68" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S68" s="6" t="str"/>
       <x:c r="T68" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -5574,7 +5454,7 @@
         <x:v>=FC01+CP01-A103:6</x:v>
       </x:c>
       <x:c r="V68" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="27" customHeight="1">
@@ -5624,9 +5504,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R69" s="6" t="str"/>
-      <x:c r="S69" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S69" s="6" t="str"/>
       <x:c r="T69" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -5634,7 +5512,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V69" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="27" customHeight="1">
@@ -5682,9 +5560,7 @@
       </x:c>
       <x:c r="Q70" s="6" t="str"/>
       <x:c r="R70" s="6" t="str"/>
-      <x:c r="S70" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S70" s="6" t="str"/>
       <x:c r="T70" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -5692,7 +5568,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V70" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="27" customHeight="1">
@@ -5746,9 +5622,7 @@
       </x:c>
       <x:c r="Q71" s="6" t="str"/>
       <x:c r="R71" s="6" t="str"/>
-      <x:c r="S71" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S71" s="6" t="str"/>
       <x:c r="T71" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -5756,7 +5630,7 @@
         <x:v>=FC01+CP01-K206:14</x:v>
       </x:c>
       <x:c r="V71" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="27" customHeight="1">
@@ -5812,9 +5686,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R72" s="6" t="str"/>
-      <x:c r="S72" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S72" s="6" t="str"/>
       <x:c r="T72" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -5822,7 +5694,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V72" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="27" customHeight="1">
@@ -5870,9 +5742,7 @@
       </x:c>
       <x:c r="Q73" s="6" t="str"/>
       <x:c r="R73" s="6" t="str"/>
-      <x:c r="S73" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S73" s="6" t="str"/>
       <x:c r="T73" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -5880,7 +5750,7 @@
         <x:v>=FC01+CP01-A103:7</x:v>
       </x:c>
       <x:c r="V73" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="27" customHeight="1">
@@ -5930,9 +5800,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R74" s="6" t="str"/>
-      <x:c r="S74" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S74" s="6" t="str"/>
       <x:c r="T74" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -5940,7 +5808,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V74" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="27" customHeight="1">
@@ -5988,9 +5856,7 @@
       </x:c>
       <x:c r="Q75" s="6" t="str"/>
       <x:c r="R75" s="6" t="str"/>
-      <x:c r="S75" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S75" s="6" t="str"/>
       <x:c r="T75" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -5998,7 +5864,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V75" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="27" customHeight="1">
@@ -6052,9 +5918,7 @@
       </x:c>
       <x:c r="Q76" s="6" t="str"/>
       <x:c r="R76" s="6" t="str"/>
-      <x:c r="S76" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S76" s="6" t="str"/>
       <x:c r="T76" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -6062,7 +5926,7 @@
         <x:v>=FC01+CP01-K207:14</x:v>
       </x:c>
       <x:c r="V76" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="27" customHeight="1">
@@ -6118,9 +5982,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R77" s="6" t="str"/>
-      <x:c r="S77" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S77" s="6" t="str"/>
       <x:c r="T77" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -6128,7 +5990,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V77" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="27" customHeight="1">
@@ -6176,9 +6038,7 @@
       </x:c>
       <x:c r="Q78" s="6" t="str"/>
       <x:c r="R78" s="6" t="str"/>
-      <x:c r="S78" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S78" s="6" t="str"/>
       <x:c r="T78" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -6186,7 +6046,7 @@
         <x:v>=FC01+CP01-A103:8</x:v>
       </x:c>
       <x:c r="V78" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="27" customHeight="1">
@@ -6236,9 +6096,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R79" s="6" t="str"/>
-      <x:c r="S79" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S79" s="6" t="str"/>
       <x:c r="T79" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -6246,7 +6104,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V79" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="27" customHeight="1">
@@ -6294,9 +6152,7 @@
       </x:c>
       <x:c r="Q80" s="6" t="str"/>
       <x:c r="R80" s="6" t="str"/>
-      <x:c r="S80" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S80" s="6" t="str"/>
       <x:c r="T80" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -6304,7 +6160,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V80" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="27" customHeight="1">
@@ -6358,9 +6214,7 @@
       </x:c>
       <x:c r="Q81" s="6" t="str"/>
       <x:c r="R81" s="6" t="str"/>
-      <x:c r="S81" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S81" s="6" t="str"/>
       <x:c r="T81" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -6368,7 +6222,7 @@
         <x:v>=FC01+CP01-K208:14</x:v>
       </x:c>
       <x:c r="V81" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="27" customHeight="1">
@@ -6424,9 +6278,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R82" s="6" t="str"/>
-      <x:c r="S82" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S82" s="6" t="str"/>
       <x:c r="T82" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -6434,7 +6286,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V82" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="27" customHeight="1">
@@ -6482,9 +6334,7 @@
       </x:c>
       <x:c r="Q83" s="6" t="str"/>
       <x:c r="R83" s="6" t="str"/>
-      <x:c r="S83" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S83" s="6" t="str"/>
       <x:c r="T83" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -6492,7 +6342,7 @@
         <x:v>=FC01+CP01-A103:9</x:v>
       </x:c>
       <x:c r="V83" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="27" customHeight="1">
@@ -6542,9 +6392,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R84" s="6" t="str"/>
-      <x:c r="S84" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S84" s="6" t="str"/>
       <x:c r="T84" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -6552,7 +6400,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V84" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="27" customHeight="1">
@@ -6600,9 +6448,7 @@
       </x:c>
       <x:c r="Q85" s="6" t="str"/>
       <x:c r="R85" s="6" t="str"/>
-      <x:c r="S85" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S85" s="6" t="str"/>
       <x:c r="T85" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -6610,7 +6456,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V85" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="27" customHeight="1">
@@ -6664,9 +6510,7 @@
       </x:c>
       <x:c r="Q86" s="6" t="str"/>
       <x:c r="R86" s="6" t="str"/>
-      <x:c r="S86" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S86" s="6" t="str"/>
       <x:c r="T86" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -6674,7 +6518,7 @@
         <x:v>=FC01+CP01-K209:14</x:v>
       </x:c>
       <x:c r="V86" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="27" customHeight="1">
@@ -6730,9 +6574,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R87" s="6" t="str"/>
-      <x:c r="S87" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S87" s="6" t="str"/>
       <x:c r="T87" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -6740,7 +6582,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V87" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="27" customHeight="1">
@@ -6788,9 +6630,7 @@
       </x:c>
       <x:c r="Q88" s="6" t="str"/>
       <x:c r="R88" s="6" t="str"/>
-      <x:c r="S88" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S88" s="6" t="str"/>
       <x:c r="T88" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -6798,7 +6638,7 @@
         <x:v>=FC01+CP01-A103:10</x:v>
       </x:c>
       <x:c r="V88" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="27" customHeight="1">
@@ -6848,9 +6688,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R89" s="6" t="str"/>
-      <x:c r="S89" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S89" s="6" t="str"/>
       <x:c r="T89" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -6858,7 +6696,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V89" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="27" customHeight="1">
@@ -6906,9 +6744,7 @@
       </x:c>
       <x:c r="Q90" s="6" t="str"/>
       <x:c r="R90" s="6" t="str"/>
-      <x:c r="S90" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S90" s="6" t="str"/>
       <x:c r="T90" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -6916,7 +6752,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V90" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="27" customHeight="1">
@@ -6970,9 +6806,7 @@
       </x:c>
       <x:c r="Q91" s="6" t="str"/>
       <x:c r="R91" s="6" t="str"/>
-      <x:c r="S91" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S91" s="6" t="str"/>
       <x:c r="T91" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -6980,7 +6814,7 @@
         <x:v>=FC01+CP01-K210:14</x:v>
       </x:c>
       <x:c r="V91" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="27" customHeight="1">
@@ -7036,9 +6870,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R92" s="6" t="str"/>
-      <x:c r="S92" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S92" s="6" t="str"/>
       <x:c r="T92" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -7046,7 +6878,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V92" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="27" customHeight="1">
@@ -7094,9 +6926,7 @@
       </x:c>
       <x:c r="Q93" s="6" t="str"/>
       <x:c r="R93" s="6" t="str"/>
-      <x:c r="S93" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S93" s="6" t="str"/>
       <x:c r="T93" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -7104,7 +6934,7 @@
         <x:v>=FC01+CP01-A103:11</x:v>
       </x:c>
       <x:c r="V93" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="27" customHeight="1">
@@ -7154,9 +6984,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R94" s="6" t="str"/>
-      <x:c r="S94" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S94" s="6" t="str"/>
       <x:c r="T94" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -7164,7 +6992,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V94" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="27" customHeight="1">
@@ -7212,9 +7040,7 @@
       </x:c>
       <x:c r="Q95" s="6" t="str"/>
       <x:c r="R95" s="6" t="str"/>
-      <x:c r="S95" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S95" s="6" t="str"/>
       <x:c r="T95" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -7222,7 +7048,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V95" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="27" customHeight="1">
@@ -7276,9 +7102,7 @@
       </x:c>
       <x:c r="Q96" s="6" t="str"/>
       <x:c r="R96" s="6" t="str"/>
-      <x:c r="S96" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S96" s="6" t="str"/>
       <x:c r="T96" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -7286,7 +7110,7 @@
         <x:v>=FC01+CP01-K211:14</x:v>
       </x:c>
       <x:c r="V96" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="27" customHeight="1">
@@ -7342,9 +7166,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R97" s="6" t="str"/>
-      <x:c r="S97" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S97" s="6" t="str"/>
       <x:c r="T97" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -7352,7 +7174,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V97" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="27" customHeight="1">
@@ -7400,9 +7222,7 @@
       </x:c>
       <x:c r="Q98" s="6" t="str"/>
       <x:c r="R98" s="6" t="str"/>
-      <x:c r="S98" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S98" s="6" t="str"/>
       <x:c r="T98" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -7410,7 +7230,7 @@
         <x:v>=FC01+CP01-A103:12</x:v>
       </x:c>
       <x:c r="V98" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="27" customHeight="1">
@@ -7460,9 +7280,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R99" s="6" t="str"/>
-      <x:c r="S99" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S99" s="6" t="str"/>
       <x:c r="T99" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -7470,7 +7288,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V99" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="27" customHeight="1">
@@ -7518,9 +7336,7 @@
       </x:c>
       <x:c r="Q100" s="6" t="str"/>
       <x:c r="R100" s="6" t="str"/>
-      <x:c r="S100" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S100" s="6" t="str"/>
       <x:c r="T100" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -7528,7 +7344,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V100" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="27" customHeight="1">
@@ -7582,9 +7398,7 @@
       </x:c>
       <x:c r="Q101" s="6" t="str"/>
       <x:c r="R101" s="6" t="str"/>
-      <x:c r="S101" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S101" s="6" t="str"/>
       <x:c r="T101" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -7592,7 +7406,7 @@
         <x:v>=FC01+CP01-K212:14</x:v>
       </x:c>
       <x:c r="V101" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="27" customHeight="1">
@@ -7648,9 +7462,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R102" s="6" t="str"/>
-      <x:c r="S102" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S102" s="6" t="str"/>
       <x:c r="T102" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -7658,7 +7470,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V102" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="27" customHeight="1">
@@ -7706,9 +7518,7 @@
       </x:c>
       <x:c r="Q103" s="6" t="str"/>
       <x:c r="R103" s="6" t="str"/>
-      <x:c r="S103" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S103" s="6" t="str"/>
       <x:c r="T103" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -7716,7 +7526,7 @@
         <x:v>=FC01+CP01-A103:13</x:v>
       </x:c>
       <x:c r="V103" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="27" customHeight="1">
@@ -7766,9 +7576,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R104" s="6" t="str"/>
-      <x:c r="S104" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S104" s="6" t="str"/>
       <x:c r="T104" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -7776,7 +7584,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V104" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="27" customHeight="1">
@@ -7824,9 +7632,7 @@
       </x:c>
       <x:c r="Q105" s="6" t="str"/>
       <x:c r="R105" s="6" t="str"/>
-      <x:c r="S105" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S105" s="6" t="str"/>
       <x:c r="T105" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -7834,7 +7640,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V105" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="27" customHeight="1">
@@ -7888,9 +7694,7 @@
       </x:c>
       <x:c r="Q106" s="6" t="str"/>
       <x:c r="R106" s="6" t="str"/>
-      <x:c r="S106" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S106" s="6" t="str"/>
       <x:c r="T106" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -7898,7 +7702,7 @@
         <x:v>=FC01+CP01-K213:14</x:v>
       </x:c>
       <x:c r="V106" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="27" customHeight="1">
@@ -7954,9 +7758,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R107" s="6" t="str"/>
-      <x:c r="S107" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S107" s="6" t="str"/>
       <x:c r="T107" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -7964,7 +7766,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V107" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="27" customHeight="1">
@@ -8016,9 +7818,7 @@
       </x:c>
       <x:c r="Q108" s="6" t="str"/>
       <x:c r="R108" s="6" t="str"/>
-      <x:c r="S108" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S108" s="6" t="str"/>
       <x:c r="T108" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -8026,7 +7826,7 @@
         <x:v>=FC01+CP01-A104:0 AI+</x:v>
       </x:c>
       <x:c r="V108" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="27" customHeight="1">
@@ -8078,9 +7878,7 @@
       </x:c>
       <x:c r="Q109" s="6" t="str"/>
       <x:c r="R109" s="6" t="str"/>
-      <x:c r="S109" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S109" s="6" t="str"/>
       <x:c r="T109" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -8088,7 +7886,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V109" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="27" customHeight="1">
@@ -8139,12 +7937,10 @@
         <x:v>0V analog</x:v>
       </x:c>
       <x:c r="Q110" s="6" t="str">
-        <x:v>X0:0V</x:v>
+        <x:v>X0:MANA</x:v>
       </x:c>
       <x:c r="R110" s="6" t="str"/>
-      <x:c r="S110" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S110" s="6" t="str"/>
       <x:c r="T110" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -8152,7 +7948,7 @@
         <x:v>=FC01+CP01-A104:0 MANA</x:v>
       </x:c>
       <x:c r="V110" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="27" customHeight="1">
@@ -8175,7 +7971,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="G111" s="6" t="str">
-        <x:v>4</x:v>
+        <x:v>SH</x:v>
       </x:c>
       <x:c r="H111" s="6" t="str">
         <x:v>-FT100:SH</x:v>
@@ -8206,17 +8002,13 @@
       <x:c r="R111" s="6" t="str">
         <x:v>SC100 panel-end only</x:v>
       </x:c>
-      <x:c r="S111" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="T111" s="6" t="str">
-        <x:v>GN</x:v>
-      </x:c>
+      <x:c r="S111" s="6" t="str"/>
+      <x:c r="T111" s="6" t="str"/>
       <x:c r="U111" s="6" t="str">
         <x:v>=FC01+CP01-SC100:1</x:v>
       </x:c>
       <x:c r="V111" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="27" customHeight="1">
@@ -8268,9 +8060,7 @@
       </x:c>
       <x:c r="Q112" s="6" t="str"/>
       <x:c r="R112" s="6" t="str"/>
-      <x:c r="S112" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S112" s="6" t="str"/>
       <x:c r="T112" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -8278,7 +8068,7 @@
         <x:v>=FC01+CP01-A104:1 AI+</x:v>
       </x:c>
       <x:c r="V112" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="27" customHeight="1">
@@ -8330,9 +8120,7 @@
       </x:c>
       <x:c r="Q113" s="6" t="str"/>
       <x:c r="R113" s="6" t="str"/>
-      <x:c r="S113" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S113" s="6" t="str"/>
       <x:c r="T113" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -8340,7 +8128,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V113" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="27" customHeight="1">
@@ -8391,12 +8179,10 @@
         <x:v>0V analog</x:v>
       </x:c>
       <x:c r="Q114" s="6" t="str">
-        <x:v>X0:0V</x:v>
+        <x:v>X0:MANA</x:v>
       </x:c>
       <x:c r="R114" s="6" t="str"/>
-      <x:c r="S114" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S114" s="6" t="str"/>
       <x:c r="T114" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -8404,7 +8190,7 @@
         <x:v>=FC01+CP01-A104:1 MANA</x:v>
       </x:c>
       <x:c r="V114" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="27" customHeight="1">
@@ -8427,7 +8213,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="G115" s="6" t="str">
-        <x:v>4</x:v>
+        <x:v>SH</x:v>
       </x:c>
       <x:c r="H115" s="6" t="str">
         <x:v>-FT101:SH</x:v>
@@ -8458,17 +8244,13 @@
       <x:c r="R115" s="6" t="str">
         <x:v>SC100 panel-end only</x:v>
       </x:c>
-      <x:c r="S115" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="T115" s="6" t="str">
-        <x:v>GN</x:v>
-      </x:c>
+      <x:c r="S115" s="6" t="str"/>
+      <x:c r="T115" s="6" t="str"/>
       <x:c r="U115" s="6" t="str">
         <x:v>=FC01+CP01-SC100:1</x:v>
       </x:c>
       <x:c r="V115" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="27" customHeight="1">
@@ -8491,7 +8273,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="G116" s="6" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H116" s="6" t="str">
         <x:v>-FT100:PULSE</x:v>
@@ -8520,9 +8302,7 @@
       </x:c>
       <x:c r="Q116" s="6" t="str"/>
       <x:c r="R116" s="6" t="str"/>
-      <x:c r="S116" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S116" s="6" t="str"/>
       <x:c r="T116" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -8530,7 +8310,7 @@
         <x:v>=FC01+CP01-A101:CH0 A CLK</x:v>
       </x:c>
       <x:c r="V116" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="27" customHeight="1">
@@ -8553,7 +8333,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="G117" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H117" s="6" t="str">
         <x:v>-FT100:0V</x:v>
@@ -8584,9 +8364,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R117" s="6" t="str"/>
-      <x:c r="S117" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S117" s="6" t="str"/>
       <x:c r="T117" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -8594,7 +8372,7 @@
         <x:v>=FC01+CP01-A101:CH0 A M</x:v>
       </x:c>
       <x:c r="V117" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="27" customHeight="1">
@@ -8617,7 +8395,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="G118" s="6" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H118" s="6" t="str">
         <x:v>-FT101:PULSE</x:v>
@@ -8646,9 +8424,7 @@
       </x:c>
       <x:c r="Q118" s="6" t="str"/>
       <x:c r="R118" s="6" t="str"/>
-      <x:c r="S118" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S118" s="6" t="str"/>
       <x:c r="T118" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -8656,7 +8432,7 @@
         <x:v>=FC01+CP01-A101:CH1 A CLK</x:v>
       </x:c>
       <x:c r="V118" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="27" customHeight="1">
@@ -8679,7 +8455,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="G119" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H119" s="6" t="str">
         <x:v>-FT101:0V</x:v>
@@ -8710,9 +8486,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R119" s="6" t="str"/>
-      <x:c r="S119" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S119" s="6" t="str"/>
       <x:c r="T119" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -8720,13 +8494,13 @@
         <x:v>=FC01+CP01-A101:CH1 A M</x:v>
       </x:c>
       <x:c r="V119" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R338d6bc62f6a495a"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -8816,13 +8590,13 @@
         <x:v>1-2</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K2" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="27" customHeight="1">
@@ -8854,13 +8628,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K3" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L3" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
@@ -8892,13 +8666,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K4" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L4" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -8930,13 +8704,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J5" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K5" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L5" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
@@ -8968,13 +8742,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K6" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L6" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
@@ -9006,13 +8780,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J7" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K7" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L7" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
@@ -9044,13 +8818,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J8" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K8" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L8" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
@@ -9082,13 +8856,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J9" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K9" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L9" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
@@ -9120,13 +8894,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J10" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K10" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L10" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
@@ -9158,13 +8932,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J11" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K11" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L11" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
@@ -9196,13 +8970,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K12" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L12" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
@@ -9234,13 +9008,13 @@
         <x:v>1-8</x:v>
       </x:c>
       <x:c r="J13" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K13" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L13" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
@@ -9272,13 +9046,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J14" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L14" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
@@ -9310,13 +9084,13 @@
         <x:v>1-3</x:v>
       </x:c>
       <x:c r="J15" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K15" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L15" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
@@ -9348,13 +9122,13 @@
         <x:v>1-2</x:v>
       </x:c>
       <x:c r="J16" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K16" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L16" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
@@ -9386,13 +9160,13 @@
         <x:v>1-2</x:v>
       </x:c>
       <x:c r="J17" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K17" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L17" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
@@ -9424,13 +9198,13 @@
         <x:v>1-4</x:v>
       </x:c>
       <x:c r="J18" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K18" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L18" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
@@ -9462,13 +9236,13 @@
         <x:v>1-4</x:v>
       </x:c>
       <x:c r="J19" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K19" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L19" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
@@ -9500,13 +9274,13 @@
         <x:v>1-8</x:v>
       </x:c>
       <x:c r="J20" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K20" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L20" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
@@ -9538,13 +9312,13 @@
         <x:v>1-2</x:v>
       </x:c>
       <x:c r="J21" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>None scheduled</x:v>
       </x:c>
       <x:c r="K21" s="6" t="str">
         <x:v>24 VDC control</x:v>
       </x:c>
       <x:c r="L21" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
@@ -9567,22 +9341,22 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H22" s="6" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I22" s="6" t="str">
-        <x:v>1-6</x:v>
+        <x:v>1-5</x:v>
       </x:c>
       <x:c r="J22" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>Separate overall shield/drain to SC100; not counted as an insulated core</x:v>
       </x:c>
       <x:c r="K22" s="6" t="str">
         <x:v>Analog/instrument</x:v>
       </x:c>
       <x:c r="L22" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
@@ -9605,28 +9379,28 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H23" s="6" t="str">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="I23" s="6" t="str">
-        <x:v>1-6</x:v>
+        <x:v>1-5</x:v>
       </x:c>
       <x:c r="J23" s="6" t="str">
-        <x:v>Panel-end clamp only where scheduled</x:v>
+        <x:v>Separate overall shield/drain to SC100; not counted as an insulated core</x:v>
       </x:c>
       <x:c r="K23" s="6" t="str">
         <x:v>Analog/instrument</x:v>
       </x:c>
       <x:c r="L23" s="6" t="str">
-        <x:v>Length and final cable family open</x:v>
+        <x:v>Length, conductor size, installation method and final cable family open</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rc801aaa0fede4478"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -9770,9 +9544,7 @@
       </x:c>
       <x:c r="Q2" s="6" t="str"/>
       <x:c r="R2" s="6" t="str"/>
-      <x:c r="S2" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S2" s="6" t="str"/>
       <x:c r="T2" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -9780,7 +9552,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V2" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="27" customHeight="1">
@@ -9826,9 +9598,7 @@
       </x:c>
       <x:c r="Q3" s="6" t="str"/>
       <x:c r="R3" s="6" t="str"/>
-      <x:c r="S3" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S3" s="6" t="str"/>
       <x:c r="T3" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -9836,7 +9606,7 @@
         <x:v>=FC01+CP01-A102:0</x:v>
       </x:c>
       <x:c r="V3" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
@@ -9888,9 +9658,7 @@
       </x:c>
       <x:c r="Q4" s="6" t="str"/>
       <x:c r="R4" s="6" t="str"/>
-      <x:c r="S4" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S4" s="6" t="str"/>
       <x:c r="T4" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -9898,7 +9666,7 @@
         <x:v>=FC01+CP01-A102:1</x:v>
       </x:c>
       <x:c r="V4" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -9950,9 +9718,7 @@
       </x:c>
       <x:c r="Q5" s="6" t="str"/>
       <x:c r="R5" s="6" t="str"/>
-      <x:c r="S5" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S5" s="6" t="str"/>
       <x:c r="T5" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -9960,7 +9726,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V5" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
@@ -10012,9 +9778,7 @@
       </x:c>
       <x:c r="Q6" s="6" t="str"/>
       <x:c r="R6" s="6" t="str"/>
-      <x:c r="S6" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S6" s="6" t="str"/>
       <x:c r="T6" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -10022,7 +9786,7 @@
         <x:v>=FC01+CP01-A102:2</x:v>
       </x:c>
       <x:c r="V6" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
@@ -10074,9 +9838,7 @@
       </x:c>
       <x:c r="Q7" s="6" t="str"/>
       <x:c r="R7" s="6" t="str"/>
-      <x:c r="S7" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S7" s="6" t="str"/>
       <x:c r="T7" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -10084,7 +9846,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V7" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
@@ -10138,9 +9900,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R8" s="6" t="str"/>
-      <x:c r="S8" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S8" s="6" t="str"/>
       <x:c r="T8" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -10148,7 +9908,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V8" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
@@ -10200,9 +9960,7 @@
       </x:c>
       <x:c r="Q9" s="6" t="str"/>
       <x:c r="R9" s="6" t="str"/>
-      <x:c r="S9" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S9" s="6" t="str"/>
       <x:c r="T9" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -10210,7 +9968,7 @@
         <x:v>=FC01+CP01-A102:3</x:v>
       </x:c>
       <x:c r="V9" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
@@ -10262,9 +10020,7 @@
       </x:c>
       <x:c r="Q10" s="6" t="str"/>
       <x:c r="R10" s="6" t="str"/>
-      <x:c r="S10" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S10" s="6" t="str"/>
       <x:c r="T10" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -10272,7 +10028,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V10" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
@@ -10326,9 +10082,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R11" s="6" t="str"/>
-      <x:c r="S11" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S11" s="6" t="str"/>
       <x:c r="T11" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -10336,7 +10090,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V11" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
@@ -10388,9 +10142,7 @@
       </x:c>
       <x:c r="Q12" s="6" t="str"/>
       <x:c r="R12" s="6" t="str"/>
-      <x:c r="S12" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S12" s="6" t="str"/>
       <x:c r="T12" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -10398,7 +10150,7 @@
         <x:v>=FC01+CP01-A102:10</x:v>
       </x:c>
       <x:c r="V12" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
@@ -10450,9 +10202,7 @@
       </x:c>
       <x:c r="Q13" s="6" t="str"/>
       <x:c r="R13" s="6" t="str"/>
-      <x:c r="S13" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S13" s="6" t="str"/>
       <x:c r="T13" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -10460,7 +10210,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V13" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
@@ -10514,9 +10264,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R14" s="6" t="str"/>
-      <x:c r="S14" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S14" s="6" t="str"/>
       <x:c r="T14" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -10524,7 +10272,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V14" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
@@ -10576,9 +10324,7 @@
       </x:c>
       <x:c r="Q15" s="6" t="str"/>
       <x:c r="R15" s="6" t="str"/>
-      <x:c r="S15" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S15" s="6" t="str"/>
       <x:c r="T15" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -10586,7 +10332,7 @@
         <x:v>=FC01+CP01-A102:11</x:v>
       </x:c>
       <x:c r="V15" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
@@ -10638,9 +10384,7 @@
       </x:c>
       <x:c r="Q16" s="6" t="str"/>
       <x:c r="R16" s="6" t="str"/>
-      <x:c r="S16" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S16" s="6" t="str"/>
       <x:c r="T16" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -10648,7 +10392,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V16" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
@@ -10702,9 +10446,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R17" s="6" t="str"/>
-      <x:c r="S17" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S17" s="6" t="str"/>
       <x:c r="T17" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -10712,7 +10454,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V17" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
@@ -10764,9 +10506,7 @@
       </x:c>
       <x:c r="Q18" s="6" t="str"/>
       <x:c r="R18" s="6" t="str"/>
-      <x:c r="S18" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S18" s="6" t="str"/>
       <x:c r="T18" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -10774,7 +10514,7 @@
         <x:v>=FC01+CP01-A102:12</x:v>
       </x:c>
       <x:c r="V18" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
@@ -10826,9 +10566,7 @@
       </x:c>
       <x:c r="Q19" s="6" t="str"/>
       <x:c r="R19" s="6" t="str"/>
-      <x:c r="S19" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S19" s="6" t="str"/>
       <x:c r="T19" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -10836,7 +10574,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V19" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
@@ -10890,9 +10628,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R20" s="6" t="str"/>
-      <x:c r="S20" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S20" s="6" t="str"/>
       <x:c r="T20" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -10900,7 +10636,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V20" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
@@ -10952,9 +10688,7 @@
       </x:c>
       <x:c r="Q21" s="6" t="str"/>
       <x:c r="R21" s="6" t="str"/>
-      <x:c r="S21" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S21" s="6" t="str"/>
       <x:c r="T21" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -10962,7 +10696,7 @@
         <x:v>=FC01+CP01-A102:13</x:v>
       </x:c>
       <x:c r="V21" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
@@ -11014,9 +10748,7 @@
       </x:c>
       <x:c r="Q22" s="6" t="str"/>
       <x:c r="R22" s="6" t="str"/>
-      <x:c r="S22" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S22" s="6" t="str"/>
       <x:c r="T22" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -11024,7 +10756,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V22" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
@@ -11078,9 +10810,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R23" s="6" t="str"/>
-      <x:c r="S23" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S23" s="6" t="str"/>
       <x:c r="T23" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -11088,7 +10818,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V23" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="27" customHeight="1">
@@ -11140,9 +10870,7 @@
       </x:c>
       <x:c r="Q24" s="6" t="str"/>
       <x:c r="R24" s="6" t="str"/>
-      <x:c r="S24" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S24" s="6" t="str"/>
       <x:c r="T24" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -11150,7 +10878,7 @@
         <x:v>=FC01+CP01-A102:14</x:v>
       </x:c>
       <x:c r="V24" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
@@ -11202,9 +10930,7 @@
       </x:c>
       <x:c r="Q25" s="6" t="str"/>
       <x:c r="R25" s="6" t="str"/>
-      <x:c r="S25" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S25" s="6" t="str"/>
       <x:c r="T25" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -11212,7 +10938,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V25" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
@@ -11266,9 +10992,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R26" s="6" t="str"/>
-      <x:c r="S26" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S26" s="6" t="str"/>
       <x:c r="T26" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -11276,7 +11000,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V26" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
@@ -11328,9 +11052,7 @@
       </x:c>
       <x:c r="Q27" s="6" t="str"/>
       <x:c r="R27" s="6" t="str"/>
-      <x:c r="S27" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S27" s="6" t="str"/>
       <x:c r="T27" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -11338,7 +11060,7 @@
         <x:v>=FC01+CP01-A102:15</x:v>
       </x:c>
       <x:c r="V27" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="27" customHeight="1">
@@ -11390,9 +11112,7 @@
       </x:c>
       <x:c r="Q28" s="6" t="str"/>
       <x:c r="R28" s="6" t="str"/>
-      <x:c r="S28" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S28" s="6" t="str"/>
       <x:c r="T28" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -11400,7 +11120,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V28" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="27" customHeight="1">
@@ -11454,9 +11174,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R29" s="6" t="str"/>
-      <x:c r="S29" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S29" s="6" t="str"/>
       <x:c r="T29" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -11464,7 +11182,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V29" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="27" customHeight="1">
@@ -11516,9 +11234,7 @@
       </x:c>
       <x:c r="Q30" s="6" t="str"/>
       <x:c r="R30" s="6" t="str"/>
-      <x:c r="S30" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S30" s="6" t="str"/>
       <x:c r="T30" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -11526,7 +11242,7 @@
         <x:v>=FC01+CP01-A102:16</x:v>
       </x:c>
       <x:c r="V30" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="27" customHeight="1">
@@ -11578,9 +11294,7 @@
       </x:c>
       <x:c r="Q31" s="6" t="str"/>
       <x:c r="R31" s="6" t="str"/>
-      <x:c r="S31" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S31" s="6" t="str"/>
       <x:c r="T31" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -11588,7 +11302,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V31" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="27" customHeight="1">
@@ -11642,9 +11356,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R32" s="6" t="str"/>
-      <x:c r="S32" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S32" s="6" t="str"/>
       <x:c r="T32" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -11652,7 +11364,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V32" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="27" customHeight="1">
@@ -11704,9 +11416,7 @@
       </x:c>
       <x:c r="Q33" s="6" t="str"/>
       <x:c r="R33" s="6" t="str"/>
-      <x:c r="S33" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S33" s="6" t="str"/>
       <x:c r="T33" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -11714,7 +11424,7 @@
         <x:v>=FC01+CP01-A102:17</x:v>
       </x:c>
       <x:c r="V33" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="27" customHeight="1">
@@ -11766,9 +11476,7 @@
       </x:c>
       <x:c r="Q34" s="6" t="str"/>
       <x:c r="R34" s="6" t="str"/>
-      <x:c r="S34" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S34" s="6" t="str"/>
       <x:c r="T34" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -11776,7 +11484,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V34" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="27" customHeight="1">
@@ -11830,9 +11538,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R35" s="6" t="str"/>
-      <x:c r="S35" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S35" s="6" t="str"/>
       <x:c r="T35" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -11840,7 +11546,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V35" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="27" customHeight="1">
@@ -11892,9 +11598,7 @@
       </x:c>
       <x:c r="Q36" s="6" t="str"/>
       <x:c r="R36" s="6" t="str"/>
-      <x:c r="S36" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S36" s="6" t="str"/>
       <x:c r="T36" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -11902,7 +11606,7 @@
         <x:v>=FC01+CP01-A102:18</x:v>
       </x:c>
       <x:c r="V36" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="27" customHeight="1">
@@ -11954,9 +11658,7 @@
       </x:c>
       <x:c r="Q37" s="6" t="str"/>
       <x:c r="R37" s="6" t="str"/>
-      <x:c r="S37" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S37" s="6" t="str"/>
       <x:c r="T37" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -11964,7 +11666,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V37" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="27" customHeight="1">
@@ -12018,9 +11720,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R38" s="6" t="str"/>
-      <x:c r="S38" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S38" s="6" t="str"/>
       <x:c r="T38" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -12028,7 +11728,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V38" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="27" customHeight="1">
@@ -12080,9 +11780,7 @@
       </x:c>
       <x:c r="Q39" s="6" t="str"/>
       <x:c r="R39" s="6" t="str"/>
-      <x:c r="S39" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S39" s="6" t="str"/>
       <x:c r="T39" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12090,7 +11788,7 @@
         <x:v>=FC01+CP01-A102:19</x:v>
       </x:c>
       <x:c r="V39" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="27" customHeight="1">
@@ -12142,9 +11840,7 @@
       </x:c>
       <x:c r="Q40" s="6" t="str"/>
       <x:c r="R40" s="6" t="str"/>
-      <x:c r="S40" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S40" s="6" t="str"/>
       <x:c r="T40" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12152,7 +11848,7 @@
         <x:v>=FC01+CP01-A102:20</x:v>
       </x:c>
       <x:c r="V40" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="27" customHeight="1">
@@ -12204,9 +11900,7 @@
       </x:c>
       <x:c r="Q41" s="6" t="str"/>
       <x:c r="R41" s="6" t="str"/>
-      <x:c r="S41" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S41" s="6" t="str"/>
       <x:c r="T41" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12214,7 +11908,7 @@
         <x:v>=FC01+CP01-A102:21</x:v>
       </x:c>
       <x:c r="V41" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="27" customHeight="1">
@@ -12266,9 +11960,7 @@
       </x:c>
       <x:c r="Q42" s="6" t="str"/>
       <x:c r="R42" s="6" t="str"/>
-      <x:c r="S42" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S42" s="6" t="str"/>
       <x:c r="T42" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12276,7 +11968,7 @@
         <x:v>=FC01+CP01-A102:22</x:v>
       </x:c>
       <x:c r="V42" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="27" customHeight="1">
@@ -12328,9 +12020,7 @@
       </x:c>
       <x:c r="Q43" s="6" t="str"/>
       <x:c r="R43" s="6" t="str"/>
-      <x:c r="S43" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S43" s="6" t="str"/>
       <x:c r="T43" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -12338,7 +12028,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V43" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="27" customHeight="1">
@@ -12392,9 +12082,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R44" s="6" t="str"/>
-      <x:c r="S44" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S44" s="6" t="str"/>
       <x:c r="T44" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -12402,7 +12090,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V44" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="27" customHeight="1">
@@ -12454,9 +12142,7 @@
       </x:c>
       <x:c r="Q45" s="6" t="str"/>
       <x:c r="R45" s="6" t="str"/>
-      <x:c r="S45" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S45" s="6" t="str"/>
       <x:c r="T45" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12464,7 +12150,7 @@
         <x:v>=FC01+CP01-A102:23</x:v>
       </x:c>
       <x:c r="V45" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="27" customHeight="1">
@@ -12516,9 +12202,7 @@
       </x:c>
       <x:c r="Q46" s="6" t="str"/>
       <x:c r="R46" s="6" t="str"/>
-      <x:c r="S46" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S46" s="6" t="str"/>
       <x:c r="T46" s="6" t="str">
         <x:v>BN</x:v>
       </x:c>
@@ -12526,7 +12210,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V46" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="27" customHeight="1">
@@ -12580,9 +12264,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R47" s="6" t="str"/>
-      <x:c r="S47" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S47" s="6" t="str"/>
       <x:c r="T47" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -12590,7 +12272,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V47" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="27" customHeight="1">
@@ -12638,9 +12320,7 @@
       </x:c>
       <x:c r="Q48" s="6" t="str"/>
       <x:c r="R48" s="6" t="str"/>
-      <x:c r="S48" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S48" s="6" t="str"/>
       <x:c r="T48" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12648,7 +12328,7 @@
         <x:v>=FC01+CP01-A103:2</x:v>
       </x:c>
       <x:c r="V48" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="27" customHeight="1">
@@ -12698,9 +12378,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R49" s="6" t="str"/>
-      <x:c r="S49" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S49" s="6" t="str"/>
       <x:c r="T49" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -12708,7 +12386,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V49" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="27" customHeight="1">
@@ -12756,9 +12434,7 @@
       </x:c>
       <x:c r="Q50" s="6" t="str"/>
       <x:c r="R50" s="6" t="str"/>
-      <x:c r="S50" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S50" s="6" t="str"/>
       <x:c r="T50" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -12766,7 +12442,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V50" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="27" customHeight="1">
@@ -12820,9 +12496,7 @@
       </x:c>
       <x:c r="Q51" s="6" t="str"/>
       <x:c r="R51" s="6" t="str"/>
-      <x:c r="S51" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S51" s="6" t="str"/>
       <x:c r="T51" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12830,7 +12504,7 @@
         <x:v>=FC01+CP01-K202:14</x:v>
       </x:c>
       <x:c r="V51" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="27" customHeight="1">
@@ -12886,9 +12560,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R52" s="6" t="str"/>
-      <x:c r="S52" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S52" s="6" t="str"/>
       <x:c r="T52" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -12896,7 +12568,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V52" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="27" customHeight="1">
@@ -12944,9 +12616,7 @@
       </x:c>
       <x:c r="Q53" s="6" t="str"/>
       <x:c r="R53" s="6" t="str"/>
-      <x:c r="S53" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S53" s="6" t="str"/>
       <x:c r="T53" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -12954,7 +12624,7 @@
         <x:v>=FC01+CP01-A103:3</x:v>
       </x:c>
       <x:c r="V53" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="27" customHeight="1">
@@ -13004,9 +12674,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R54" s="6" t="str"/>
-      <x:c r="S54" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S54" s="6" t="str"/>
       <x:c r="T54" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -13014,7 +12682,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V54" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="27" customHeight="1">
@@ -13062,9 +12730,7 @@
       </x:c>
       <x:c r="Q55" s="6" t="str"/>
       <x:c r="R55" s="6" t="str"/>
-      <x:c r="S55" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S55" s="6" t="str"/>
       <x:c r="T55" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -13072,7 +12738,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V55" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="27" customHeight="1">
@@ -13126,9 +12792,7 @@
       </x:c>
       <x:c r="Q56" s="6" t="str"/>
       <x:c r="R56" s="6" t="str"/>
-      <x:c r="S56" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S56" s="6" t="str"/>
       <x:c r="T56" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -13136,7 +12800,7 @@
         <x:v>=FC01+CP01-K203:14</x:v>
       </x:c>
       <x:c r="V56" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="27" customHeight="1">
@@ -13192,9 +12856,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R57" s="6" t="str"/>
-      <x:c r="S57" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S57" s="6" t="str"/>
       <x:c r="T57" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -13202,7 +12864,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V57" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="27" customHeight="1">
@@ -13250,9 +12912,7 @@
       </x:c>
       <x:c r="Q58" s="6" t="str"/>
       <x:c r="R58" s="6" t="str"/>
-      <x:c r="S58" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S58" s="6" t="str"/>
       <x:c r="T58" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -13260,7 +12920,7 @@
         <x:v>=FC01+CP01-A103:4</x:v>
       </x:c>
       <x:c r="V58" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="27" customHeight="1">
@@ -13310,9 +12970,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R59" s="6" t="str"/>
-      <x:c r="S59" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S59" s="6" t="str"/>
       <x:c r="T59" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -13320,7 +12978,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V59" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="27" customHeight="1">
@@ -13368,9 +13026,7 @@
       </x:c>
       <x:c r="Q60" s="6" t="str"/>
       <x:c r="R60" s="6" t="str"/>
-      <x:c r="S60" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S60" s="6" t="str"/>
       <x:c r="T60" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -13378,7 +13034,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V60" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="27" customHeight="1">
@@ -13432,9 +13088,7 @@
       </x:c>
       <x:c r="Q61" s="6" t="str"/>
       <x:c r="R61" s="6" t="str"/>
-      <x:c r="S61" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S61" s="6" t="str"/>
       <x:c r="T61" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -13442,7 +13096,7 @@
         <x:v>=FC01+CP01-K204:14</x:v>
       </x:c>
       <x:c r="V61" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="27" customHeight="1">
@@ -13498,9 +13152,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R62" s="6" t="str"/>
-      <x:c r="S62" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S62" s="6" t="str"/>
       <x:c r="T62" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -13508,7 +13160,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V62" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="27" customHeight="1">
@@ -13556,9 +13208,7 @@
       </x:c>
       <x:c r="Q63" s="6" t="str"/>
       <x:c r="R63" s="6" t="str"/>
-      <x:c r="S63" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S63" s="6" t="str"/>
       <x:c r="T63" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -13566,7 +13216,7 @@
         <x:v>=FC01+CP01-A103:5</x:v>
       </x:c>
       <x:c r="V63" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="27" customHeight="1">
@@ -13616,9 +13266,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R64" s="6" t="str"/>
-      <x:c r="S64" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S64" s="6" t="str"/>
       <x:c r="T64" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -13626,7 +13274,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V64" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="27" customHeight="1">
@@ -13674,9 +13322,7 @@
       </x:c>
       <x:c r="Q65" s="6" t="str"/>
       <x:c r="R65" s="6" t="str"/>
-      <x:c r="S65" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S65" s="6" t="str"/>
       <x:c r="T65" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -13684,7 +13330,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V65" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="27" customHeight="1">
@@ -13738,9 +13384,7 @@
       </x:c>
       <x:c r="Q66" s="6" t="str"/>
       <x:c r="R66" s="6" t="str"/>
-      <x:c r="S66" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S66" s="6" t="str"/>
       <x:c r="T66" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -13748,7 +13392,7 @@
         <x:v>=FC01+CP01-K205:14</x:v>
       </x:c>
       <x:c r="V66" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="27" customHeight="1">
@@ -13804,9 +13448,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R67" s="6" t="str"/>
-      <x:c r="S67" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S67" s="6" t="str"/>
       <x:c r="T67" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -13814,7 +13456,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V67" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="27" customHeight="1">
@@ -13862,9 +13504,7 @@
       </x:c>
       <x:c r="Q68" s="6" t="str"/>
       <x:c r="R68" s="6" t="str"/>
-      <x:c r="S68" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S68" s="6" t="str"/>
       <x:c r="T68" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -13872,7 +13512,7 @@
         <x:v>=FC01+CP01-A103:6</x:v>
       </x:c>
       <x:c r="V68" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="27" customHeight="1">
@@ -13922,9 +13562,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R69" s="6" t="str"/>
-      <x:c r="S69" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S69" s="6" t="str"/>
       <x:c r="T69" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -13932,7 +13570,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V69" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="27" customHeight="1">
@@ -13980,9 +13618,7 @@
       </x:c>
       <x:c r="Q70" s="6" t="str"/>
       <x:c r="R70" s="6" t="str"/>
-      <x:c r="S70" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S70" s="6" t="str"/>
       <x:c r="T70" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -13990,7 +13626,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V70" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="27" customHeight="1">
@@ -14044,9 +13680,7 @@
       </x:c>
       <x:c r="Q71" s="6" t="str"/>
       <x:c r="R71" s="6" t="str"/>
-      <x:c r="S71" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S71" s="6" t="str"/>
       <x:c r="T71" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -14054,7 +13688,7 @@
         <x:v>=FC01+CP01-K206:14</x:v>
       </x:c>
       <x:c r="V71" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="27" customHeight="1">
@@ -14110,9 +13744,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R72" s="6" t="str"/>
-      <x:c r="S72" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S72" s="6" t="str"/>
       <x:c r="T72" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -14120,7 +13752,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V72" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="27" customHeight="1">
@@ -14168,9 +13800,7 @@
       </x:c>
       <x:c r="Q73" s="6" t="str"/>
       <x:c r="R73" s="6" t="str"/>
-      <x:c r="S73" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S73" s="6" t="str"/>
       <x:c r="T73" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -14178,7 +13808,7 @@
         <x:v>=FC01+CP01-A103:7</x:v>
       </x:c>
       <x:c r="V73" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="27" customHeight="1">
@@ -14228,9 +13858,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R74" s="6" t="str"/>
-      <x:c r="S74" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S74" s="6" t="str"/>
       <x:c r="T74" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -14238,7 +13866,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V74" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="27" customHeight="1">
@@ -14286,9 +13914,7 @@
       </x:c>
       <x:c r="Q75" s="6" t="str"/>
       <x:c r="R75" s="6" t="str"/>
-      <x:c r="S75" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S75" s="6" t="str"/>
       <x:c r="T75" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -14296,7 +13922,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V75" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="27" customHeight="1">
@@ -14350,9 +13976,7 @@
       </x:c>
       <x:c r="Q76" s="6" t="str"/>
       <x:c r="R76" s="6" t="str"/>
-      <x:c r="S76" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S76" s="6" t="str"/>
       <x:c r="T76" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -14360,7 +13984,7 @@
         <x:v>=FC01+CP01-K207:14</x:v>
       </x:c>
       <x:c r="V76" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="27" customHeight="1">
@@ -14416,9 +14040,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R77" s="6" t="str"/>
-      <x:c r="S77" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S77" s="6" t="str"/>
       <x:c r="T77" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -14426,7 +14048,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V77" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="27" customHeight="1">
@@ -14474,9 +14096,7 @@
       </x:c>
       <x:c r="Q78" s="6" t="str"/>
       <x:c r="R78" s="6" t="str"/>
-      <x:c r="S78" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S78" s="6" t="str"/>
       <x:c r="T78" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -14484,7 +14104,7 @@
         <x:v>=FC01+CP01-A103:8</x:v>
       </x:c>
       <x:c r="V78" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="27" customHeight="1">
@@ -14534,9 +14154,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R79" s="6" t="str"/>
-      <x:c r="S79" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S79" s="6" t="str"/>
       <x:c r="T79" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -14544,7 +14162,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V79" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="27" customHeight="1">
@@ -14592,9 +14210,7 @@
       </x:c>
       <x:c r="Q80" s="6" t="str"/>
       <x:c r="R80" s="6" t="str"/>
-      <x:c r="S80" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S80" s="6" t="str"/>
       <x:c r="T80" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -14602,7 +14218,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V80" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="27" customHeight="1">
@@ -14656,9 +14272,7 @@
       </x:c>
       <x:c r="Q81" s="6" t="str"/>
       <x:c r="R81" s="6" t="str"/>
-      <x:c r="S81" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S81" s="6" t="str"/>
       <x:c r="T81" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -14666,7 +14280,7 @@
         <x:v>=FC01+CP01-K208:14</x:v>
       </x:c>
       <x:c r="V81" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="27" customHeight="1">
@@ -14722,9 +14336,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R82" s="6" t="str"/>
-      <x:c r="S82" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S82" s="6" t="str"/>
       <x:c r="T82" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -14732,7 +14344,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V82" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="27" customHeight="1">
@@ -14780,9 +14392,7 @@
       </x:c>
       <x:c r="Q83" s="6" t="str"/>
       <x:c r="R83" s="6" t="str"/>
-      <x:c r="S83" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S83" s="6" t="str"/>
       <x:c r="T83" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -14790,7 +14400,7 @@
         <x:v>=FC01+CP01-A103:9</x:v>
       </x:c>
       <x:c r="V83" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="27" customHeight="1">
@@ -14840,9 +14450,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R84" s="6" t="str"/>
-      <x:c r="S84" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S84" s="6" t="str"/>
       <x:c r="T84" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -14850,7 +14458,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V84" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="27" customHeight="1">
@@ -14898,9 +14506,7 @@
       </x:c>
       <x:c r="Q85" s="6" t="str"/>
       <x:c r="R85" s="6" t="str"/>
-      <x:c r="S85" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S85" s="6" t="str"/>
       <x:c r="T85" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -14908,7 +14514,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V85" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="86" ht="27" customHeight="1">
@@ -14962,9 +14568,7 @@
       </x:c>
       <x:c r="Q86" s="6" t="str"/>
       <x:c r="R86" s="6" t="str"/>
-      <x:c r="S86" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S86" s="6" t="str"/>
       <x:c r="T86" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -14972,7 +14576,7 @@
         <x:v>=FC01+CP01-K209:14</x:v>
       </x:c>
       <x:c r="V86" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="87" ht="27" customHeight="1">
@@ -15028,9 +14632,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R87" s="6" t="str"/>
-      <x:c r="S87" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S87" s="6" t="str"/>
       <x:c r="T87" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -15038,7 +14640,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V87" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="88" ht="27" customHeight="1">
@@ -15086,9 +14688,7 @@
       </x:c>
       <x:c r="Q88" s="6" t="str"/>
       <x:c r="R88" s="6" t="str"/>
-      <x:c r="S88" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S88" s="6" t="str"/>
       <x:c r="T88" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -15096,7 +14696,7 @@
         <x:v>=FC01+CP01-A103:10</x:v>
       </x:c>
       <x:c r="V88" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="89" ht="27" customHeight="1">
@@ -15146,9 +14746,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R89" s="6" t="str"/>
-      <x:c r="S89" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S89" s="6" t="str"/>
       <x:c r="T89" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -15156,7 +14754,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V89" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="90" ht="27" customHeight="1">
@@ -15204,9 +14802,7 @@
       </x:c>
       <x:c r="Q90" s="6" t="str"/>
       <x:c r="R90" s="6" t="str"/>
-      <x:c r="S90" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S90" s="6" t="str"/>
       <x:c r="T90" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -15214,7 +14810,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V90" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="91" ht="27" customHeight="1">
@@ -15268,9 +14864,7 @@
       </x:c>
       <x:c r="Q91" s="6" t="str"/>
       <x:c r="R91" s="6" t="str"/>
-      <x:c r="S91" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S91" s="6" t="str"/>
       <x:c r="T91" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -15278,7 +14872,7 @@
         <x:v>=FC01+CP01-K210:14</x:v>
       </x:c>
       <x:c r="V91" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="92" ht="27" customHeight="1">
@@ -15334,9 +14928,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R92" s="6" t="str"/>
-      <x:c r="S92" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S92" s="6" t="str"/>
       <x:c r="T92" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -15344,7 +14936,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V92" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="93" ht="27" customHeight="1">
@@ -15392,9 +14984,7 @@
       </x:c>
       <x:c r="Q93" s="6" t="str"/>
       <x:c r="R93" s="6" t="str"/>
-      <x:c r="S93" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S93" s="6" t="str"/>
       <x:c r="T93" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -15402,7 +14992,7 @@
         <x:v>=FC01+CP01-A103:11</x:v>
       </x:c>
       <x:c r="V93" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="94" ht="27" customHeight="1">
@@ -15452,9 +15042,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R94" s="6" t="str"/>
-      <x:c r="S94" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S94" s="6" t="str"/>
       <x:c r="T94" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -15462,7 +15050,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V94" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="95" ht="27" customHeight="1">
@@ -15510,9 +15098,7 @@
       </x:c>
       <x:c r="Q95" s="6" t="str"/>
       <x:c r="R95" s="6" t="str"/>
-      <x:c r="S95" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S95" s="6" t="str"/>
       <x:c r="T95" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -15520,7 +15106,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V95" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="96" ht="27" customHeight="1">
@@ -15574,9 +15160,7 @@
       </x:c>
       <x:c r="Q96" s="6" t="str"/>
       <x:c r="R96" s="6" t="str"/>
-      <x:c r="S96" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S96" s="6" t="str"/>
       <x:c r="T96" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -15584,7 +15168,7 @@
         <x:v>=FC01+CP01-K211:14</x:v>
       </x:c>
       <x:c r="V96" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="97" ht="27" customHeight="1">
@@ -15640,9 +15224,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R97" s="6" t="str"/>
-      <x:c r="S97" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S97" s="6" t="str"/>
       <x:c r="T97" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -15650,7 +15232,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V97" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="98" ht="27" customHeight="1">
@@ -15698,9 +15280,7 @@
       </x:c>
       <x:c r="Q98" s="6" t="str"/>
       <x:c r="R98" s="6" t="str"/>
-      <x:c r="S98" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S98" s="6" t="str"/>
       <x:c r="T98" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -15708,7 +15288,7 @@
         <x:v>=FC01+CP01-A103:12</x:v>
       </x:c>
       <x:c r="V98" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="99" ht="27" customHeight="1">
@@ -15758,9 +15338,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R99" s="6" t="str"/>
-      <x:c r="S99" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S99" s="6" t="str"/>
       <x:c r="T99" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -15768,7 +15346,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V99" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="100" ht="27" customHeight="1">
@@ -15816,9 +15394,7 @@
       </x:c>
       <x:c r="Q100" s="6" t="str"/>
       <x:c r="R100" s="6" t="str"/>
-      <x:c r="S100" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S100" s="6" t="str"/>
       <x:c r="T100" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -15826,7 +15402,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V100" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="101" ht="27" customHeight="1">
@@ -15880,9 +15456,7 @@
       </x:c>
       <x:c r="Q101" s="6" t="str"/>
       <x:c r="R101" s="6" t="str"/>
-      <x:c r="S101" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S101" s="6" t="str"/>
       <x:c r="T101" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -15890,7 +15464,7 @@
         <x:v>=FC01+CP01-K212:14</x:v>
       </x:c>
       <x:c r="V101" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="102" ht="27" customHeight="1">
@@ -15946,9 +15520,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R102" s="6" t="str"/>
-      <x:c r="S102" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S102" s="6" t="str"/>
       <x:c r="T102" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -15956,7 +15528,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V102" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="103" ht="27" customHeight="1">
@@ -16004,9 +15576,7 @@
       </x:c>
       <x:c r="Q103" s="6" t="str"/>
       <x:c r="R103" s="6" t="str"/>
-      <x:c r="S103" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S103" s="6" t="str"/>
       <x:c r="T103" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -16014,7 +15584,7 @@
         <x:v>=FC01+CP01-A103:13</x:v>
       </x:c>
       <x:c r="V103" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="104" ht="27" customHeight="1">
@@ -16064,9 +15634,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R104" s="6" t="str"/>
-      <x:c r="S104" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S104" s="6" t="str"/>
       <x:c r="T104" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -16074,7 +15642,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V104" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="105" ht="27" customHeight="1">
@@ -16122,9 +15690,7 @@
       </x:c>
       <x:c r="Q105" s="6" t="str"/>
       <x:c r="R105" s="6" t="str"/>
-      <x:c r="S105" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S105" s="6" t="str"/>
       <x:c r="T105" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -16132,7 +15698,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V105" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="106" ht="27" customHeight="1">
@@ -16186,9 +15752,7 @@
       </x:c>
       <x:c r="Q106" s="6" t="str"/>
       <x:c r="R106" s="6" t="str"/>
-      <x:c r="S106" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S106" s="6" t="str"/>
       <x:c r="T106" s="6" t="str">
         <x:v>BK</x:v>
       </x:c>
@@ -16196,7 +15760,7 @@
         <x:v>=FC01+CP01-K213:14</x:v>
       </x:c>
       <x:c r="V106" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="107" ht="27" customHeight="1">
@@ -16252,9 +15816,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R107" s="6" t="str"/>
-      <x:c r="S107" s="6" t="str">
-        <x:v>0.75</x:v>
-      </x:c>
+      <x:c r="S107" s="6" t="str"/>
       <x:c r="T107" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -16262,7 +15824,7 @@
         <x:v>=FC01+CP01-X0:0V</x:v>
       </x:c>
       <x:c r="V107" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="108" ht="27" customHeight="1">
@@ -16314,9 +15876,7 @@
       </x:c>
       <x:c r="Q108" s="6" t="str"/>
       <x:c r="R108" s="6" t="str"/>
-      <x:c r="S108" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S108" s="6" t="str"/>
       <x:c r="T108" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -16324,7 +15884,7 @@
         <x:v>=FC01+CP01-A104:0 AI+</x:v>
       </x:c>
       <x:c r="V108" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="109" ht="27" customHeight="1">
@@ -16376,9 +15936,7 @@
       </x:c>
       <x:c r="Q109" s="6" t="str"/>
       <x:c r="R109" s="6" t="str"/>
-      <x:c r="S109" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S109" s="6" t="str"/>
       <x:c r="T109" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -16386,7 +15944,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V109" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="110" ht="27" customHeight="1">
@@ -16437,12 +15995,10 @@
         <x:v>0V analog</x:v>
       </x:c>
       <x:c r="Q110" s="6" t="str">
-        <x:v>X0:0V</x:v>
+        <x:v>X0:MANA</x:v>
       </x:c>
       <x:c r="R110" s="6" t="str"/>
-      <x:c r="S110" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S110" s="6" t="str"/>
       <x:c r="T110" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -16450,7 +16006,7 @@
         <x:v>=FC01+CP01-A104:0 MANA</x:v>
       </x:c>
       <x:c r="V110" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="111" ht="27" customHeight="1">
@@ -16473,7 +16029,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="G111" s="6" t="str">
-        <x:v>4</x:v>
+        <x:v>SH</x:v>
       </x:c>
       <x:c r="H111" s="6" t="str">
         <x:v>-FT100:SH</x:v>
@@ -16504,17 +16060,13 @@
       <x:c r="R111" s="6" t="str">
         <x:v>SC100 panel-end only</x:v>
       </x:c>
-      <x:c r="S111" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="T111" s="6" t="str">
-        <x:v>GN</x:v>
-      </x:c>
+      <x:c r="S111" s="6" t="str"/>
+      <x:c r="T111" s="6" t="str"/>
       <x:c r="U111" s="6" t="str">
         <x:v>=FC01+CP01-SC100:1</x:v>
       </x:c>
       <x:c r="V111" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="112" ht="27" customHeight="1">
@@ -16566,9 +16118,7 @@
       </x:c>
       <x:c r="Q112" s="6" t="str"/>
       <x:c r="R112" s="6" t="str"/>
-      <x:c r="S112" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S112" s="6" t="str"/>
       <x:c r="T112" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -16576,7 +16126,7 @@
         <x:v>=FC01+CP01-A104:1 AI+</x:v>
       </x:c>
       <x:c r="V112" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="113" ht="27" customHeight="1">
@@ -16628,9 +16178,7 @@
       </x:c>
       <x:c r="Q113" s="6" t="str"/>
       <x:c r="R113" s="6" t="str"/>
-      <x:c r="S113" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S113" s="6" t="str"/>
       <x:c r="T113" s="6" t="str">
         <x:v>RD</x:v>
       </x:c>
@@ -16638,7 +16186,7 @@
         <x:v>=FC01+CP01-X24:+24V</x:v>
       </x:c>
       <x:c r="V113" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="114" ht="27" customHeight="1">
@@ -16689,12 +16237,10 @@
         <x:v>0V analog</x:v>
       </x:c>
       <x:c r="Q114" s="6" t="str">
-        <x:v>X0:0V</x:v>
+        <x:v>X0:MANA</x:v>
       </x:c>
       <x:c r="R114" s="6" t="str"/>
-      <x:c r="S114" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S114" s="6" t="str"/>
       <x:c r="T114" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -16702,7 +16248,7 @@
         <x:v>=FC01+CP01-A104:1 MANA</x:v>
       </x:c>
       <x:c r="V114" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="115" ht="27" customHeight="1">
@@ -16725,7 +16271,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="G115" s="6" t="str">
-        <x:v>4</x:v>
+        <x:v>SH</x:v>
       </x:c>
       <x:c r="H115" s="6" t="str">
         <x:v>-FT101:SH</x:v>
@@ -16756,17 +16302,13 @@
       <x:c r="R115" s="6" t="str">
         <x:v>SC100 panel-end only</x:v>
       </x:c>
-      <x:c r="S115" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
-      <x:c r="T115" s="6" t="str">
-        <x:v>GN</x:v>
-      </x:c>
+      <x:c r="S115" s="6" t="str"/>
+      <x:c r="T115" s="6" t="str"/>
       <x:c r="U115" s="6" t="str">
         <x:v>=FC01+CP01-SC100:1</x:v>
       </x:c>
       <x:c r="V115" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="116" ht="27" customHeight="1">
@@ -16789,7 +16331,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="G116" s="6" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H116" s="6" t="str">
         <x:v>-FT100:PULSE</x:v>
@@ -16818,9 +16360,7 @@
       </x:c>
       <x:c r="Q116" s="6" t="str"/>
       <x:c r="R116" s="6" t="str"/>
-      <x:c r="S116" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S116" s="6" t="str"/>
       <x:c r="T116" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -16828,7 +16368,7 @@
         <x:v>=FC01+CP01-A101:CH0 A CLK</x:v>
       </x:c>
       <x:c r="V116" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="117" ht="27" customHeight="1">
@@ -16851,7 +16391,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="G117" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H117" s="6" t="str">
         <x:v>-FT100:0V</x:v>
@@ -16882,9 +16422,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R117" s="6" t="str"/>
-      <x:c r="S117" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S117" s="6" t="str"/>
       <x:c r="T117" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -16892,7 +16430,7 @@
         <x:v>=FC01+CP01-A101:CH0 A M</x:v>
       </x:c>
       <x:c r="V117" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="118" ht="27" customHeight="1">
@@ -16915,7 +16453,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="G118" s="6" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="H118" s="6" t="str">
         <x:v>-FT101:PULSE</x:v>
@@ -16944,9 +16482,7 @@
       </x:c>
       <x:c r="Q118" s="6" t="str"/>
       <x:c r="R118" s="6" t="str"/>
-      <x:c r="S118" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S118" s="6" t="str"/>
       <x:c r="T118" s="6" t="str">
         <x:v>WH</x:v>
       </x:c>
@@ -16954,7 +16490,7 @@
         <x:v>=FC01+CP01-A101:CH1 A CLK</x:v>
       </x:c>
       <x:c r="V118" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="119" ht="27" customHeight="1">
@@ -16977,7 +16513,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="G119" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="H119" s="6" t="str">
         <x:v>-FT101:0V</x:v>
@@ -17008,9 +16544,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="R119" s="6" t="str"/>
-      <x:c r="S119" s="6" t="str">
-        <x:v>0.5</x:v>
-      </x:c>
+      <x:c r="S119" s="6" t="str"/>
       <x:c r="T119" s="6" t="str">
         <x:v>BU</x:v>
       </x:c>
@@ -17018,13 +16552,13 @@
         <x:v>=FC01+CP01-A101:CH1 A M</x:v>
       </x:c>
       <x:c r="V119" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ed5e8849c8141ab"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -17077,7 +16611,7 @@
         <x:v>full_designation</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>BOM-001</x:v>
       </x:c>
@@ -17109,7 +16643,7 @@
         <x:v>=FC01+CP01-A100</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>BOM-002</x:v>
       </x:c>
@@ -17141,7 +16675,7 @@
         <x:v>=FC01+CP01-A101</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>BOM-003</x:v>
       </x:c>
@@ -17173,7 +16707,7 @@
         <x:v>=FC01+CP01-A102</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>BOM-004</x:v>
       </x:c>
@@ -17205,7 +16739,7 @@
         <x:v>=FC01+CP01-A103</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>BOM-005</x:v>
       </x:c>
@@ -17237,7 +16771,7 @@
         <x:v>=FC01+CP01-A104</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>BOM-006</x:v>
       </x:c>
@@ -17269,7 +16803,7 @@
         <x:v>=FC01+CP01-H100</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>BOM-007</x:v>
       </x:c>
@@ -17301,7 +16835,7 @@
         <x:v>=FC01+CP01-U100</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>BOM-008</x:v>
       </x:c>
@@ -17333,7 +16867,7 @@
         <x:v>=FC01+CP01-U101</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>BOM-009</x:v>
       </x:c>
@@ -17365,7 +16899,7 @@
         <x:v>=FC01+CP01-SW100</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>BOM-010</x:v>
       </x:c>
@@ -17397,7 +16931,7 @@
         <x:v>=FC01+CP01-FW100</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>BOM-011</x:v>
       </x:c>
@@ -17427,7 +16961,7 @@
         <x:v>=FC01+CP01-PC200</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>BOM-012</x:v>
       </x:c>
@@ -17457,7 +16991,7 @@
         <x:v>=FC01+CP01-MC100</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>BOM-013</x:v>
       </x:c>
@@ -17487,7 +17021,7 @@
         <x:v>=FC01+CP01-RA100</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>BOM-014</x:v>
       </x:c>
@@ -17517,7 +17051,7 @@
         <x:v>=FC01+CP01-FC100</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" customHeight="1">
+    <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>BOM-015</x:v>
       </x:c>
@@ -17547,7 +17081,7 @@
         <x:v>=FC01+CP01-FC101</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="27" customHeight="1">
+    <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>BOM-016</x:v>
       </x:c>
@@ -17577,7 +17111,7 @@
         <x:v>=FC01+CP01-FC102</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>BOM-017</x:v>
       </x:c>
@@ -17607,7 +17141,7 @@
         <x:v>=FC01+CP01-FC103</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" customHeight="1">
+    <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>BOM-018</x:v>
       </x:c>
@@ -17635,7 +17169,7 @@
         <x:v>=FC01+CP01-QS100</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" customHeight="1">
+    <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>BOM-019</x:v>
       </x:c>
@@ -17663,7 +17197,7 @@
         <x:v>=FC01+CP01-QF100</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="27" customHeight="1">
+    <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>BOM-020</x:v>
       </x:c>
@@ -17691,7 +17225,7 @@
         <x:v>=FC01+CP01-PS100</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="27" customHeight="1">
+    <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>BOM-021</x:v>
       </x:c>
@@ -17719,7 +17253,7 @@
         <x:v>=FC01+CP01-QF110</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="27" customHeight="1">
+    <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>BOM-022</x:v>
       </x:c>
@@ -17747,7 +17281,7 @@
         <x:v>=FC01+CP01-K100</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="27" customHeight="1">
+    <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="6" t="str">
         <x:v>BOM-023</x:v>
       </x:c>
@@ -17775,7 +17309,7 @@
         <x:v>=FC01+CP01-K202..-K213</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="27" customHeight="1">
+    <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="6" t="str">
         <x:v>BOM-024</x:v>
       </x:c>
@@ -17803,7 +17337,7 @@
         <x:v>=FC01+CP01-D202..-D213</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="27" customHeight="1">
+    <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="6" t="str">
         <x:v>BOM-025</x:v>
       </x:c>
@@ -17831,7 +17365,7 @@
         <x:v>=FC01+CP01-X100..-X199</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="27" customHeight="1">
+    <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="6" t="str">
         <x:v>BOM-026</x:v>
       </x:c>
@@ -17859,7 +17393,7 @@
         <x:v>=FC01+CP01-PE100</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="27" customHeight="1">
+    <x:row r="28" ht="54" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>BOM-027</x:v>
       </x:c>
@@ -17887,7 +17421,7 @@
         <x:v>=FC01+CP01-SC100</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="27" customHeight="1">
+    <x:row r="29" ht="54" customHeight="1">
       <x:c r="A29" s="6" t="str">
         <x:v>BOM-028</x:v>
       </x:c>
@@ -17915,7 +17449,7 @@
         <x:v>=FC01+CP01-ENC100</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="27" customHeight="1">
+    <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="6" t="str">
         <x:v>BOM-029</x:v>
       </x:c>
@@ -17943,7 +17477,7 @@
         <x:v>=FC01+CP01-WD100</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="27" customHeight="1">
+    <x:row r="31" ht="54" customHeight="1">
       <x:c r="A31" s="6" t="str">
         <x:v>BOM-030</x:v>
       </x:c>
@@ -17971,7 +17505,7 @@
         <x:v>=FC01+CP01-DR100</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="27" customHeight="1">
+    <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="6" t="str">
         <x:v>BOM-031</x:v>
       </x:c>
@@ -17999,7 +17533,7 @@
         <x:v>=FC01+FLD-GL100</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="27" customHeight="1">
+    <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="6" t="str">
         <x:v>BOM-032</x:v>
       </x:c>
@@ -18027,7 +17561,7 @@
         <x:v>=FC01+CP01-FAN100</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="27" customHeight="1">
+    <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="6" t="str">
         <x:v>BOM-033</x:v>
       </x:c>
@@ -18055,7 +17589,7 @@
         <x:v>=FC01+FLD-M100</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="27" customHeight="1">
+    <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="6" t="str">
         <x:v>BOM-034</x:v>
       </x:c>
@@ -18083,7 +17617,7 @@
         <x:v>=FC01+FLD-M101</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="27" customHeight="1">
+    <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="6" t="str">
         <x:v>BOM-035</x:v>
       </x:c>
@@ -18111,7 +17645,7 @@
         <x:v>=FC01+FLD-YV100</x:v>
       </x:c>
     </x:row>
-    <x:row r="37" ht="27" customHeight="1">
+    <x:row r="37" ht="54" customHeight="1">
       <x:c r="A37" s="6" t="str">
         <x:v>BOM-036</x:v>
       </x:c>
@@ -18139,7 +17673,7 @@
         <x:v>=FC01+FLD-YV101</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" ht="27" customHeight="1">
+    <x:row r="38" ht="54" customHeight="1">
       <x:c r="A38" s="6" t="str">
         <x:v>BOM-037</x:v>
       </x:c>
@@ -18167,7 +17701,7 @@
         <x:v>=FC01+FLD-YV102</x:v>
       </x:c>
     </x:row>
-    <x:row r="39" ht="27" customHeight="1">
+    <x:row r="39" ht="54" customHeight="1">
       <x:c r="A39" s="6" t="str">
         <x:v>BOM-038</x:v>
       </x:c>
@@ -18195,7 +17729,7 @@
         <x:v>=FC01+FLD-YV103</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" ht="27" customHeight="1">
+    <x:row r="40" ht="54" customHeight="1">
       <x:c r="A40" s="6" t="str">
         <x:v>BOM-039</x:v>
       </x:c>
@@ -18223,7 +17757,7 @@
         <x:v>=FC01+FLD-FT100</x:v>
       </x:c>
     </x:row>
-    <x:row r="41" ht="27" customHeight="1">
+    <x:row r="41" ht="54" customHeight="1">
       <x:c r="A41" s="6" t="str">
         <x:v>BOM-040</x:v>
       </x:c>
@@ -18251,7 +17785,7 @@
         <x:v>=FC01+FLD-FT101</x:v>
       </x:c>
     </x:row>
-    <x:row r="42" ht="27" customHeight="1">
+    <x:row r="42" ht="54" customHeight="1">
       <x:c r="A42" s="6" t="str">
         <x:v>BOM-041</x:v>
       </x:c>
@@ -18279,7 +17813,7 @@
         <x:v>=FC01+FLD-S100</x:v>
       </x:c>
     </x:row>
-    <x:row r="43" ht="27" customHeight="1">
+    <x:row r="43" ht="54" customHeight="1">
       <x:c r="A43" s="6" t="str">
         <x:v>BOM-042</x:v>
       </x:c>
@@ -18307,7 +17841,7 @@
         <x:v>=FC01+FLD-S101</x:v>
       </x:c>
     </x:row>
-    <x:row r="44" ht="27" customHeight="1">
+    <x:row r="44" ht="54" customHeight="1">
       <x:c r="A44" s="6" t="str">
         <x:v>BOM-043</x:v>
       </x:c>
@@ -18335,7 +17869,7 @@
         <x:v>=FC01+FLD-S102</x:v>
       </x:c>
     </x:row>
-    <x:row r="45" ht="27" customHeight="1">
+    <x:row r="45" ht="54" customHeight="1">
       <x:c r="A45" s="6" t="str">
         <x:v>BOM-044</x:v>
       </x:c>
@@ -18363,7 +17897,7 @@
         <x:v>=FC01+FLD-H101</x:v>
       </x:c>
     </x:row>
-    <x:row r="46" ht="27" customHeight="1">
+    <x:row r="46" ht="54" customHeight="1">
       <x:c r="A46" s="6" t="str">
         <x:v>BOM-045</x:v>
       </x:c>
@@ -18391,7 +17925,7 @@
         <x:v>=FC01+FLD-IF140</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" ht="27" customHeight="1">
+    <x:row r="47" ht="54" customHeight="1">
       <x:c r="A47" s="6" t="str">
         <x:v>BOM-046</x:v>
       </x:c>
@@ -18419,7 +17953,7 @@
         <x:v>=FC01+FLD-CAM200</x:v>
       </x:c>
     </x:row>
-    <x:row r="48" ht="27" customHeight="1">
+    <x:row r="48" ht="54" customHeight="1">
       <x:c r="A48" s="6" t="str">
         <x:v>BOM-047</x:v>
       </x:c>
@@ -18447,7 +17981,7 @@
         <x:v>=FC01+FLD-LENS200</x:v>
       </x:c>
     </x:row>
-    <x:row r="49" ht="27" customHeight="1">
+    <x:row r="49" ht="54" customHeight="1">
       <x:c r="A49" s="6" t="str">
         <x:v>BOM-048</x:v>
       </x:c>
@@ -18475,7 +18009,7 @@
         <x:v>=FC01+FLD-LT200</x:v>
       </x:c>
     </x:row>
-    <x:row r="50" ht="27" customHeight="1">
+    <x:row r="50" ht="54" customHeight="1">
       <x:c r="A50" s="6" t="str">
         <x:v>BOM-049</x:v>
       </x:c>
@@ -18503,7 +18037,7 @@
         <x:v>=FC01+FLD-CB200</x:v>
       </x:c>
     </x:row>
-    <x:row r="51" ht="27" customHeight="1">
+    <x:row r="51" ht="54" customHeight="1">
       <x:c r="A51" s="6" t="str">
         <x:v>BOM-050</x:v>
       </x:c>
@@ -18531,7 +18065,7 @@
         <x:v>=FC01+FLD-W900</x:v>
       </x:c>
     </x:row>
-    <x:row r="52" ht="27" customHeight="1">
+    <x:row r="52" ht="54" customHeight="1">
       <x:c r="A52" s="6" t="str">
         <x:v>BOM-051</x:v>
       </x:c>
@@ -18559,7 +18093,7 @@
         <x:v>=FC01+FLD-W901</x:v>
       </x:c>
     </x:row>
-    <x:row r="53" ht="27" customHeight="1">
+    <x:row r="53" ht="54" customHeight="1">
       <x:c r="A53" s="6" t="str">
         <x:v>BOM-052</x:v>
       </x:c>
@@ -18587,7 +18121,7 @@
         <x:v>=FC01+FLD-CONS100</x:v>
       </x:c>
     </x:row>
-    <x:row r="54" ht="27" customHeight="1">
+    <x:row r="54" ht="54" customHeight="1">
       <x:c r="A54" s="6" t="str">
         <x:v>BOM-053</x:v>
       </x:c>
@@ -18615,7 +18149,7 @@
         <x:v>=FC01+FLD-B100</x:v>
       </x:c>
     </x:row>
-    <x:row r="55" ht="27" customHeight="1">
+    <x:row r="55" ht="54" customHeight="1">
       <x:c r="A55" s="6" t="str">
         <x:v>BOM-054</x:v>
       </x:c>
@@ -18643,7 +18177,7 @@
         <x:v>=FC01+FLD-B101</x:v>
       </x:c>
     </x:row>
-    <x:row r="56" ht="27" customHeight="1">
+    <x:row r="56" ht="54" customHeight="1">
       <x:c r="A56" s="6" t="str">
         <x:v>BOM-055</x:v>
       </x:c>
@@ -18671,7 +18205,7 @@
         <x:v>=FC01+FLD-B110</x:v>
       </x:c>
     </x:row>
-    <x:row r="57" ht="27" customHeight="1">
+    <x:row r="57" ht="54" customHeight="1">
       <x:c r="A57" s="6" t="str">
         <x:v>BOM-056</x:v>
       </x:c>
@@ -18699,7 +18233,7 @@
         <x:v>=FC01+FLD-B111</x:v>
       </x:c>
     </x:row>
-    <x:row r="58" ht="27" customHeight="1">
+    <x:row r="58" ht="54" customHeight="1">
       <x:c r="A58" s="6" t="str">
         <x:v>BOM-057</x:v>
       </x:c>
@@ -18727,7 +18261,7 @@
         <x:v>=FC01+FLD-B120</x:v>
       </x:c>
     </x:row>
-    <x:row r="59" ht="27" customHeight="1">
+    <x:row r="59" ht="54" customHeight="1">
       <x:c r="A59" s="6" t="str">
         <x:v>BOM-058</x:v>
       </x:c>
@@ -18755,7 +18289,7 @@
         <x:v>=FC01+FLD-B121</x:v>
       </x:c>
     </x:row>
-    <x:row r="60" ht="27" customHeight="1">
+    <x:row r="60" ht="54" customHeight="1">
       <x:c r="A60" s="6" t="str">
         <x:v>BOM-059</x:v>
       </x:c>
@@ -18783,7 +18317,7 @@
         <x:v>=FC01+FLD-B122</x:v>
       </x:c>
     </x:row>
-    <x:row r="61" ht="27" customHeight="1">
+    <x:row r="61" ht="54" customHeight="1">
       <x:c r="A61" s="6" t="str">
         <x:v>BOM-060</x:v>
       </x:c>
@@ -18811,7 +18345,7 @@
         <x:v>=FC01+FLD-B123</x:v>
       </x:c>
     </x:row>
-    <x:row r="62" ht="27" customHeight="1">
+    <x:row r="62" ht="54" customHeight="1">
       <x:c r="A62" s="6" t="str">
         <x:v>BOM-061</x:v>
       </x:c>
@@ -18839,7 +18373,7 @@
         <x:v>=FC01+FLD-B130</x:v>
       </x:c>
     </x:row>
-    <x:row r="63" ht="27" customHeight="1">
+    <x:row r="63" ht="54" customHeight="1">
       <x:c r="A63" s="6" t="str">
         <x:v>BOM-062</x:v>
       </x:c>
@@ -18870,7 +18404,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd8f8191f23b645cf"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -18907,7 +18441,7 @@
         <x:v>basis</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>PLC CPU and I/O</x:v>
       </x:c>
@@ -18927,7 +18461,7 @@
         <x:v>Preliminary allowance; verify Siemens configuration</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>HMI</x:v>
       </x:c>
@@ -18947,7 +18481,7 @@
         <x:v>Maximum-current allowance from product data</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>Relays, sensors and solenoids</x:v>
       </x:c>
@@ -18967,7 +18501,7 @@
         <x:v>Duty-cycle allowance; inrush not finalized</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>Vision edge + camera + lighting</x:v>
       </x:c>
@@ -18987,7 +18521,7 @@
         <x:v>Placeholder pending selected carrier/camera</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>24 VDC subtotal</x:v>
       </x:c>
@@ -18998,16 +18532,16 @@
         <x:v>329</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>1.0</x:v>
+        <x:v>N/A</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
         <x:v>299</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
-        <x:v>12.46 A demand; retain &gt;=25% margin; provisional 20 A PSU after inrush check</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+        <x:v>12.458 A demand; 20 A concept leaves 7.542 A (37.71% of rating) unused; minimum 15.573 A for 25% demand margin before inrush/derating</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>Conveyor drive</x:v>
       </x:c>
@@ -19027,7 +18561,7 @@
         <x:v>Motor nameplate not supplied</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>Pump drive</x:v>
       </x:c>
@@ -19050,7 +18584,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R6d35a5bf90e64472"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19127,12 +18661,12 @@
         <x:v>full_designation</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>-A100</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
         <x:v>90</x:v>
@@ -19177,12 +18711,12 @@
         <x:v>=FC01+CP01-A100</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>-A101</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>130</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
         <x:v>90</x:v>
@@ -19227,12 +18761,12 @@
         <x:v>=FC01+CP01-A101</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>-A102</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>170</x:v>
+        <x:v>250</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
         <x:v>90</x:v>
@@ -19277,12 +18811,12 @@
         <x:v>=FC01+CP01-A102</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>-A103</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>210</x:v>
+        <x:v>315</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
         <x:v>90</x:v>
@@ -19327,12 +18861,12 @@
         <x:v>=FC01+CP01-A103</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>-A104</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>250</x:v>
+        <x:v>380</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
         <x:v>90</x:v>
@@ -19377,7 +18911,7 @@
         <x:v>=FC01+CP01-A104</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>-H100</x:v>
       </x:c>
@@ -19427,12 +18961,12 @@
         <x:v>=FC01+CP01-H100</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>-U100</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
         <x:v>430</x:v>
@@ -19471,12 +19005,12 @@
         <x:v>=FC01+CP01-U100</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>-U101</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>340</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
         <x:v>430</x:v>
@@ -19515,12 +19049,12 @@
         <x:v>=FC01+CP01-U101</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>-SW100</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
-        <x:v>330</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
         <x:v>90</x:v>
@@ -19565,12 +19099,12 @@
         <x:v>=FC01+CP01-SW100</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>-FW100</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>400</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
         <x:v>90</x:v>
@@ -19613,12 +19147,12 @@
         <x:v>=FC01+CP01-FW100</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>-PC200</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>560</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
         <x:v>250</x:v>
@@ -19657,18 +19191,18 @@
         <x:v>=FC01+CP01-PC200</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>-PE100</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>70</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>730</x:v>
+        <x:v>755</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>650</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
         <x:v>25</x:v>
@@ -19707,18 +19241,18 @@
         <x:v>=FC01+CP01-PE100</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>-X100..-X199</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
-        <x:v>70</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
         <x:v>650</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>680</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
         <x:v>50</x:v>
@@ -19739,7 +19273,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str">
-        <x:v>40</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="L14" s="6" t="str">
         <x:v>20</x:v>
@@ -19757,7 +19291,7 @@
         <x:v>=FC01+CP01-X100..-X199</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>-WD100</x:v>
       </x:c>
@@ -19771,7 +19305,7 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>650</x:v>
+        <x:v>540</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
         <x:v>60</x:v>
@@ -19810,7 +19344,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9012c0e7fe3f43a2"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -19825,7 +19359,7 @@
     <x:col min="4" max="4" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="10.630000114440918" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="33.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31.5" customHeight="1">
@@ -19851,7 +19385,7 @@
         <x:v>evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>SYS-001</x:v>
       </x:c>
@@ -19874,7 +19408,7 @@
         <x:v>normal and missing-bottle traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>SYS-002</x:v>
       </x:c>
@@ -19897,7 +19431,7 @@
         <x:v>bottle-sensor fault traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>SYS-003</x:v>
       </x:c>
@@ -19920,7 +19454,7 @@
         <x:v>normal and conveyor-fault traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>SYS-004</x:v>
       </x:c>
@@ -19943,7 +19477,7 @@
         <x:v>actuator timeout/contradiction traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>SYS-005</x:v>
       </x:c>
@@ -19966,7 +19500,7 @@
         <x:v>no-pulse and pulse/analog traces; native TM Count binding remains open</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>SYS-006</x:v>
       </x:c>
@@ -19989,7 +19523,7 @@
         <x:v>pump/utilities fault traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>SYS-007</x:v>
       </x:c>
@@ -20012,7 +19546,7 @@
         <x:v>normal, overfill and valve-close traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>SYS-008</x:v>
       </x:c>
@@ -20035,7 +19569,7 @@
         <x:v>pulse/analog disagreement trace; native AI diagnostics remain open</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>SYS-009</x:v>
       </x:c>
@@ -20058,7 +19592,7 @@
         <x:v>five fill-fault traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>SYS-010</x:v>
       </x:c>
@@ -20081,7 +19615,7 @@
         <x:v>normal trace includes drip-settle state</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>SYS-011</x:v>
       </x:c>
@@ -20104,7 +19638,7 @@
         <x:v>normal and stale-ID traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>SYS-012</x:v>
       </x:c>
@@ -20127,7 +19661,7 @@
         <x:v>vision timeout and stale-ID traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>SYS-013</x:v>
       </x:c>
@@ -20150,7 +19684,7 @@
         <x:v>vision uncertainty/failure traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>SYS-014</x:v>
       </x:c>
@@ -20173,7 +19707,7 @@
         <x:v>normal release and quality-hold traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" customHeight="1">
+    <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>SYS-015</x:v>
       </x:c>
@@ -20196,7 +19730,7 @@
         <x:v>capper not-ready/busy/fault traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="27" customHeight="1">
+    <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>SYS-016</x:v>
       </x:c>
@@ -20219,7 +19753,7 @@
         <x:v>power-loss/restoration/reset traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>SYS-017</x:v>
       </x:c>
@@ -20242,7 +19776,7 @@
         <x:v>normal/recovery/manual traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" customHeight="1">
+    <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>SYS-018</x:v>
       </x:c>
@@ -20259,13 +19793,13 @@
         <x:v>04_controls_siemens/scl/00_types.scl; 04_controls_siemens/scl/FB_CellMain.scl</x:v>
       </x:c>
       <x:c r="F19" s="6" t="str">
-        <x:v>VAL-C-STATIC</x:v>
+        <x:v>VAL-D-STATIC</x:v>
       </x:c>
       <x:c r="G19" s="6" t="str">
         <x:v>automated_validation_report.md source/data checks</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" customHeight="1">
+    <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>SYS-019</x:v>
       </x:c>
@@ -20288,7 +19822,7 @@
         <x:v>power-loss trace; qualified safety validation remains blocked</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="27" customHeight="1">
+    <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>SYS-020</x:v>
       </x:c>
@@ -20311,7 +19845,7 @@
         <x:v>first-out fault traces across equipment classes</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="27" customHeight="1">
+    <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>SYS-021</x:v>
       </x:c>
@@ -20334,7 +19868,7 @@
         <x:v>HMI-loss and manual-interlock traces</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="27" customHeight="1">
+    <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>SYS-022</x:v>
       </x:c>
@@ -20357,7 +19891,7 @@
         <x:v>32 scenario traces and 20 unit/property tests</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="27" customHeight="1">
+    <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="6" t="str">
         <x:v>SYS-023</x:v>
       </x:c>
@@ -20374,13 +19908,13 @@
         <x:v>00_project_control/canonical_model.json; scripts/validate_project.py</x:v>
       </x:c>
       <x:c r="F24" s="6" t="str">
-        <x:v>VAL-C-STATIC</x:v>
+        <x:v>VAL-D-STATIC</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>Revision-C canonical/source/schedule validation suite; the executed report records the current check count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" ht="27" customHeight="1">
+        <x:v>Revision-D canonical/source/schedule validation suite; the executed report records the current check count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="6" t="str">
         <x:v>SYS-024</x:v>
       </x:c>
@@ -20403,7 +19937,7 @@
         <x:v>restore execution remains open; final deterministic manifest verification required</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="27" customHeight="1">
+    <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="6" t="str">
         <x:v>SYS-025</x:v>
       </x:c>
@@ -20429,7 +19963,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rb9e2613fb7534557"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -20443,7 +19977,7 @@
     <x:col min="3" max="3" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="33.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="33.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31.5" customHeight="1">
@@ -20466,7 +20000,7 @@
         <x:v>evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>TC-001</x:v>
       </x:c>
@@ -20480,13 +20014,13 @@
         <x:v>Exactly one pair releases only after independent fill completion, matched passing vision result and capper completion; no invariant violation</x:v>
       </x:c>
       <x:c r="E2" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F2" s="6" t="str">
         <x:v>11_simulation/outputs/traces/normal_two_bottle_cycle.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>TC-002</x:v>
       </x:c>
@@ -20500,13 +20034,13 @@
         <x:v>Inject single missing bottle; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
         <x:v>11_simulation/outputs/traces/single_missing_bottle.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>TC-003</x:v>
       </x:c>
@@ -20520,13 +20054,13 @@
         <x:v>Inject both bottles missing; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E4" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F4" s="6" t="str">
         <x:v>11_simulation/outputs/traces/both_bottles_missing.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>TC-004</x:v>
       </x:c>
@@ -20540,13 +20074,13 @@
         <x:v>Inject bottle sensor stuck on; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E5" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F5" s="6" t="str">
         <x:v>11_simulation/outputs/traces/bottle_sensor_stuck_on.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>TC-005</x:v>
       </x:c>
@@ -20560,13 +20094,13 @@
         <x:v>Inject bottle sensor stuck off; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E6" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F6" s="6" t="str">
         <x:v>11_simulation/outputs/traces/bottle_sensor_stuck_off.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>TC-006</x:v>
       </x:c>
@@ -20580,13 +20114,13 @@
         <x:v>Inject gate timeout; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
         <x:v>11_simulation/outputs/traces/gate_timeout.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>TC-007</x:v>
       </x:c>
@@ -20600,13 +20134,13 @@
         <x:v>Inject clamp timeout; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E8" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F8" s="6" t="str">
         <x:v>11_simulation/outputs/traces/clamp_timeout.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>TC-008</x:v>
       </x:c>
@@ -20620,13 +20154,13 @@
         <x:v>Inject contradictory actuator feedback; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E9" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F9" s="6" t="str">
         <x:v>11_simulation/outputs/traces/contradictory_actuator_feedback.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>TC-009</x:v>
       </x:c>
@@ -20640,13 +20174,13 @@
         <x:v>Inject flow channel no pulse; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E10" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F10" s="6" t="str">
         <x:v>11_simulation/outputs/traces/flow_channel_no_pulse.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>TC-010</x:v>
       </x:c>
@@ -20660,13 +20194,13 @@
         <x:v>Inject flow analog pulse disagreement; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E11" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F11" s="6" t="str">
         <x:v>11_simulation/outputs/traces/flow_analog_pulse_disagreement.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>TC-011</x:v>
       </x:c>
@@ -20680,13 +20214,13 @@
         <x:v>Inject underfill; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E12" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F12" s="6" t="str">
         <x:v>11_simulation/outputs/traces/underfill.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>TC-012</x:v>
       </x:c>
@@ -20700,13 +20234,13 @@
         <x:v>Inject overfill; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
         <x:v>11_simulation/outputs/traces/overfill.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>TC-013</x:v>
       </x:c>
@@ -20720,13 +20254,13 @@
         <x:v>Inject valve fails to close; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
         <x:v>11_simulation/outputs/traces/valve_fails_to_close.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>TC-014</x:v>
       </x:c>
@@ -20740,13 +20274,13 @@
         <x:v>Inject pump vfd fault; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
         <x:v>11_simulation/outputs/traces/pump_vfd_fault.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" customHeight="1">
+    <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>TC-015</x:v>
       </x:c>
@@ -20760,13 +20294,13 @@
         <x:v>Inject conveyor vfd fault; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E16" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F16" s="6" t="str">
         <x:v>11_simulation/outputs/traces/conveyor_vfd_fault.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="27" customHeight="1">
+    <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>TC-016</x:v>
       </x:c>
@@ -20780,13 +20314,13 @@
         <x:v>Inject air pressure loss; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E17" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F17" s="6" t="str">
         <x:v>11_simulation/outputs/traces/air_pressure_loss.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>TC-017</x:v>
       </x:c>
@@ -20800,13 +20334,13 @@
         <x:v>Inject product supply loss; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E18" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F18" s="6" t="str">
         <x:v>11_simulation/outputs/traces/product_supply_loss.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" customHeight="1">
+    <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>TC-018</x:v>
       </x:c>
@@ -20820,13 +20354,13 @@
         <x:v>Inject capper not ready; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E19" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F19" s="6" t="str">
         <x:v>11_simulation/outputs/traces/capper_not_ready.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" customHeight="1">
+    <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>TC-019</x:v>
       </x:c>
@@ -20840,13 +20374,13 @@
         <x:v>Inject capper busy timeout; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E20" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F20" s="6" t="str">
         <x:v>11_simulation/outputs/traces/capper_busy_timeout.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="27" customHeight="1">
+    <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>TC-020</x:v>
       </x:c>
@@ -20860,13 +20394,13 @@
         <x:v>Inject capper fault; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E21" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F21" s="6" t="str">
         <x:v>11_simulation/outputs/traces/capper_fault.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="27" customHeight="1">
+    <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>TC-021</x:v>
       </x:c>
@@ -20880,13 +20414,13 @@
         <x:v>Inject hmi communications loss; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E22" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F22" s="6" t="str">
         <x:v>11_simulation/outputs/traces/hmi_communications_loss.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="27" customHeight="1">
+    <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>TC-022</x:v>
       </x:c>
@@ -20900,13 +20434,13 @@
         <x:v>Inject vision not ready; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E23" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F23" s="6" t="str">
         <x:v>11_simulation/outputs/traces/vision_not_ready.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="27" customHeight="1">
+    <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="6" t="str">
         <x:v>TC-023</x:v>
       </x:c>
@@ -20920,13 +20454,13 @@
         <x:v>Inject vision result timeout; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E24" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F24" s="6" t="str">
         <x:v>11_simulation/outputs/traces/vision_result_timeout.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="27" customHeight="1">
+    <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="6" t="str">
         <x:v>TC-024</x:v>
       </x:c>
@@ -20940,13 +20474,13 @@
         <x:v>Inject stale inspection id; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E25" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F25" s="6" t="str">
         <x:v>11_simulation/outputs/traces/stale_inspection_id.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="27" customHeight="1">
+    <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="6" t="str">
         <x:v>TC-025</x:v>
       </x:c>
@@ -20960,13 +20494,13 @@
         <x:v>Inject low confidence inspection; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E26" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F26" s="6" t="str">
         <x:v>11_simulation/outputs/traces/low_confidence_inspection.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="27" customHeight="1">
+    <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="6" t="str">
         <x:v>TC-026</x:v>
       </x:c>
@@ -20980,13 +20514,13 @@
         <x:v>Inject one bottle fails; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E27" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F27" s="6" t="str">
         <x:v>11_simulation/outputs/traces/one_bottle_fails.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="27" customHeight="1">
+    <x:row r="28" ht="54" customHeight="1">
       <x:c r="A28" s="6" t="str">
         <x:v>TC-027</x:v>
       </x:c>
@@ -21000,13 +20534,13 @@
         <x:v>Inject vision heartbeat loss; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E28" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F28" s="6" t="str">
         <x:v>11_simulation/outputs/traces/vision_heartbeat_loss.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="27" customHeight="1">
+    <x:row r="29" ht="54" customHeight="1">
       <x:c r="A29" s="6" t="str">
         <x:v>TC-028</x:v>
       </x:c>
@@ -21020,13 +20554,13 @@
         <x:v>Inject plc heartbeat loss; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E29" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F29" s="6" t="str">
         <x:v>11_simulation/outputs/traces/plc_heartbeat_loss.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="27" customHeight="1">
+    <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="6" t="str">
         <x:v>TC-029</x:v>
       </x:c>
@@ -21040,13 +20574,13 @@
         <x:v>Inject power loss during filling; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E30" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F30" s="6" t="str">
         <x:v>11_simulation/outputs/traces/power_loss_during_filling.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="27" customHeight="1">
+    <x:row r="31" ht="54" customHeight="1">
       <x:c r="A31" s="6" t="str">
         <x:v>TC-030</x:v>
       </x:c>
@@ -21060,13 +20594,13 @@
         <x:v>Inject power restoration; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E31" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F31" s="6" t="str">
         <x:v>11_simulation/outputs/traces/power_restoration.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="27" customHeight="1">
+    <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="6" t="str">
         <x:v>TC-031</x:v>
       </x:c>
@@ -21080,13 +20614,13 @@
         <x:v>Inject reset no restart; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E32" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F32" s="6" t="str">
         <x:v>11_simulation/outputs/traces/reset_no_restart.csv; 11_simulation/outputs/scenario_results.csv</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="27" customHeight="1">
+    <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="6" t="str">
         <x:v>TC-032</x:v>
       </x:c>
@@ -21100,7 +20634,7 @@
         <x:v>Inject manual mode interlocks; no product release, pump/valves decommand on first-out condition, controlled HOLD/FAULT outcome and no automatic restart</x:v>
       </x:c>
       <x:c r="E33" s="6" t="str">
-        <x:v>NOT RUN</x:v>
+        <x:v>INDEPENDENT PYTHON PASS; NATIVE PLCSIM NOT RUN</x:v>
       </x:c>
       <x:c r="F33" s="6" t="str">
         <x:v>11_simulation/outputs/traces/manual_mode_interlocks.csv; 11_simulation/outputs/scenario_results.csv</x:v>
@@ -21109,7 +20643,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra02b56c45b944a20"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21124,7 +20658,7 @@
     <x:col min="4" max="4" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="22.5" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="33.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31.5" customHeight="1">
@@ -21150,7 +20684,7 @@
         <x:v>evidence_required</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>IR-001</x:v>
       </x:c>
@@ -21173,7 +20707,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>IR-002</x:v>
       </x:c>
@@ -21196,7 +20730,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>IR-003</x:v>
       </x:c>
@@ -21219,7 +20753,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>IR-004</x:v>
       </x:c>
@@ -21242,7 +20776,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>IR-005</x:v>
       </x:c>
@@ -21265,7 +20799,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>IR-006</x:v>
       </x:c>
@@ -21288,7 +20822,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>IR-007</x:v>
       </x:c>
@@ -21311,7 +20845,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>IR-008</x:v>
       </x:c>
@@ -21334,7 +20868,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>IR-009</x:v>
       </x:c>
@@ -21357,7 +20891,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>IR-010</x:v>
       </x:c>
@@ -21380,7 +20914,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>IR-011</x:v>
       </x:c>
@@ -21403,7 +20937,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>IR-012</x:v>
       </x:c>
@@ -21426,7 +20960,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>IR-013</x:v>
       </x:c>
@@ -21449,7 +20983,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>IR-014</x:v>
       </x:c>
@@ -21472,7 +21006,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" customHeight="1">
+    <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>IR-015</x:v>
       </x:c>
@@ -21495,7 +21029,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="27" customHeight="1">
+    <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>IR-016</x:v>
       </x:c>
@@ -21518,7 +21052,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>IR-017</x:v>
       </x:c>
@@ -21541,7 +21075,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" customHeight="1">
+    <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>IR-018</x:v>
       </x:c>
@@ -21564,7 +21098,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" customHeight="1">
+    <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>IR-019</x:v>
       </x:c>
@@ -21575,7 +21109,7 @@
         <x:v>Electrical owner</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Revision-C FCStd/exchange validation</x:v>
+        <x:v>Revision-D FCStd/exchange validation</x:v>
       </x:c>
       <x:c r="E20" s="6" t="str">
         <x:v>OPEN</x:v>
@@ -21587,7 +21121,7 @@
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="27" customHeight="1">
+    <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>IR-020</x:v>
       </x:c>
@@ -21607,13 +21141,174 @@
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="G21" s="6" t="str">
+        <x:v>Approved source document or native evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="54" customHeight="1">
+      <x:c r="A22" s="6" t="str">
+        <x:v>IR-021</x:v>
+      </x:c>
+      <x:c r="B22" s="6" t="str">
+        <x:v>Usable QElectroTech installation and qualified electrical schematic reviewer</x:v>
+      </x:c>
+      <x:c r="C22" s="6" t="str">
+        <x:v>Electrical owner</x:v>
+      </x:c>
+      <x:c r="D22" s="6" t="str">
+        <x:v>Revision-D schematic authoring, reopen, export and review</x:v>
+      </x:c>
+      <x:c r="E22" s="6" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F22" s="6" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="G22" s="6" t="str">
+        <x:v>Approved source document or native evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>IR-022</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>Field cable route lengths, installation method, grouping, ambient and approved cable families</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>Site electrical engineer</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>Conductor loading, voltage drop, fill and cable release</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="G23" s="6" t="str">
+        <x:v>Approved source document or native evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="54" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>IR-023</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>24 V branch load currents, inrush profiles and selected protection-device data</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>Electrical/vendor</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>PSU transient margin and branch protection coordination</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="G24" s="6" t="str">
+        <x:v>Approved source document or native evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>IR-024</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>Enclosure material/size/IP, ambient/altitude/solar exposure and verified device loss data</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>Site/mechanical/vendor</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>Panel thermal assessment and fan/filter selection</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="G25" s="6" t="str">
+        <x:v>Approved source document or native evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="54" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>IR-025</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>Approved terminal family, jumpers, test/disconnect, PE and spare-position policy</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>Electrical owner</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>Terminal quantity, width, bridges and placement release</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="G26" s="6" t="str">
+        <x:v>Approved source document or native evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="54" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>IR-026</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>Approved PE/FE/0 V/MANA bonding and EMC-zone/shield termination policy</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>Site electrical/EMC authority</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>Bonding topology and shield/return release</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="G27" s="6" t="str">
+        <x:v>Approved source document or native evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="54" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>IR-027</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>Source transformer/impedance and component interrupt/SCCR data</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>Site electrical engineer</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>Prospective fault current and assembly SCCR assessment</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>OPEN</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>2026-08-02</x:v>
+      </x:c>
+      <x:c r="G28" s="6" t="str">
         <x:v>Approved source document or native evidence</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R79c754a371a54d41"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -21625,7 +21320,7 @@
     <x:col min="1" max="1" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="22.5" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="33.75" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="31.5" customHeight="1">
@@ -21642,7 +21337,7 @@
         <x:v>evidence_or_blocker</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>1</x:v>
       </x:c>
@@ -21656,7 +21351,7 @@
         <x:v>Controlled model and tests present; owner approval absent</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>2</x:v>
       </x:c>
@@ -21667,10 +21362,10 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>VAL-C-STATIC passed 238/238 checks; independent package audit found zero mismatches across all 19 schedules</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+        <x:v>Revision-D deterministic validator and source-parity checks pass; see current automated report for count</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>3</x:v>
       </x:c>
@@ -21684,7 +21379,7 @@
         <x:v>V20/FW4.0 design baseline documented; native catalog and delivered state open</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>4</x:v>
       </x:c>
@@ -21698,7 +21393,7 @@
         <x:v>No genuine AP20 project created</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>5</x:v>
       </x:c>
@@ -21712,7 +21407,7 @@
         <x:v>No genuine ZAP20 archive created</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>6</x:v>
       </x:c>
@@ -21726,7 +21421,7 @@
         <x:v>Static source lint only; native compile not run</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>7</x:v>
       </x:c>
@@ -21740,7 +21435,7 @@
         <x:v>WinCC project not created</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>8</x:v>
       </x:c>
@@ -21754,7 +21449,7 @@
         <x:v>Startdrive not installed and motor data absent</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>9</x:v>
       </x:c>
@@ -21768,21 +21463,21 @@
         <x:v>PLCSIM not installed; Python simulator is independent evidence</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>Revision-C QET reopens and reconciles</x:v>
+        <x:v>Revision-D QET reopens and reconciles</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>Historical revision-A native baseline only</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+        <x:v>No runnable QElectroTech found; historical revision-A native baseline only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>11</x:v>
       </x:c>
@@ -21793,24 +21488,24 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>Revision-C schematics not yet created</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+        <x:v>Revision-D native schematics do not exist</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>Revision-C FCStd reopens</x:v>
+        <x:v>Revision-D FCStd reopens</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>Historical baseline only</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+        <x:v>No runnable FreeCAD found; historical baseline only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>13</x:v>
       </x:c>
@@ -21821,10 +21516,10 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>Revision-C exchange files not created</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+        <x:v>Revision-D exchange files do not exist and FreeCAD is absent</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>14</x:v>
       </x:c>
@@ -21838,7 +21533,7 @@
         <x:v>Expanded controlled schedules; unresolved selections and native CAD remain open</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" customHeight="1">
+    <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>15</x:v>
       </x:c>
@@ -21852,7 +21547,7 @@
         <x:v>Site supply, fault current, loads and environmental inputs missing</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="27" customHeight="1">
+    <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>16</x:v>
       </x:c>
@@ -21866,7 +21561,7 @@
         <x:v>No real dataset supplied</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>17</x:v>
       </x:c>
@@ -21880,7 +21575,7 @@
         <x:v>No dataset or TAO runtime</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" customHeight="1">
+    <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>18</x:v>
       </x:c>
@@ -21894,7 +21589,7 @@
         <x:v>No selected target carrier/runtime</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" customHeight="1">
+    <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>19</x:v>
       </x:c>
@@ -21905,10 +21600,10 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Local source-design scope: 20 simulator tests, 32 scenarios, 11 edge tests and 6 interface-harness tests pass; native integration remains blocked under gates 9 and 18</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" ht="27" customHeight="1">
+        <x:v>Local source-design scope: simulator, 32 scenarios, edge service, interface harness and Revision-D independent interface-oracle tests pass; native integration remains blocked under gates 9 and 18</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>20</x:v>
       </x:c>
@@ -21922,7 +21617,7 @@
         <x:v>Procedures issued, never executed</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="27" customHeight="1">
+    <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>21</x:v>
       </x:c>
@@ -21936,7 +21631,7 @@
         <x:v>External qualified work required</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="27" customHeight="1">
+    <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>22</x:v>
       </x:c>
@@ -21953,7 +21648,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R359d540a872b4a5f"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24151,7 +23846,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R335dd3878f6d41d7"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -24160,7 +23855,7 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
-    <x:col min="1" max="1" width="27.5" hidden="0" customWidth="1"/>
+    <x:col min="1" max="1" width="32.5" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="13.75" hidden="0" customWidth="1"/>
@@ -24193,7 +23888,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="24" t="str">
-        <x:v>FICTIONAL ENGINEERING PROJECT — NOT FOR CONSTRUCTION | Revision C | Overall status: PARTIALLY COMPLETE</x:v>
+        <x:v>FICTIONAL ENGINEERING PROJECT — NOT FOR CONSTRUCTION | Revision D | Professional controlled engineering-development package</x:v>
       </x:c>
       <x:c r="B3" s="24"/>
       <x:c r="C3" s="24"/>
@@ -24203,139 +23898,170 @@
       <x:c r="G3" s="24"/>
       <x:c r="H3" s="24"/>
     </x:row>
+    <x:row r="4">
+      <x:c r="A4" s="30" t="str">
+        <x:v>CONCEPTUAL SAFETY ARCHITECTURE — REQUIRES PROJECT-SPECIFIC RISK ASSESSMENT, DESIGN, VERIFICATION AND VALIDATION BY A QUALIFIED MACHINERY-SAFETY ENGINEER. NO PERFORMANCE LEVEL, SIL, CATEGORY, CE CONFORMITY OR REGULATORY COMPLIANCE IS CLAIMED.</x:v>
+      </x:c>
+      <x:c r="B4" s="30"/>
+      <x:c r="C4" s="30"/>
+      <x:c r="D4" s="30"/>
+      <x:c r="E4" s="30"/>
+      <x:c r="F4" s="30"/>
+      <x:c r="G4" s="30"/>
+      <x:c r="H4" s="30"/>
+    </x:row>
     <x:row r="5">
-      <x:c r="A5" s="28" t="str">
+      <x:c r="A5" s="34" t="str">
         <x:v>Controlled metric</x:v>
       </x:c>
-      <x:c r="B5" s="28" t="str">
+      <x:c r="B5" s="34" t="str">
         <x:v>Value</x:v>
       </x:c>
-      <x:c r="D5" s="34" t="str">
+      <x:c r="D5" s="40" t="str">
         <x:v>Release boundary</x:v>
       </x:c>
-      <x:c r="E5" s="34"/>
-      <x:c r="F5" s="34"/>
-      <x:c r="G5" s="34"/>
-      <x:c r="H5" s="34"/>
+      <x:c r="E5" s="40"/>
+      <x:c r="F5" s="40"/>
+      <x:c r="G5" s="40"/>
+      <x:c r="H5" s="40"/>
     </x:row>
     <x:row r="6">
-      <x:c r="A6" s="30" t="str">
+      <x:c r="A6" s="36" t="str">
         <x:v>PLC I/O rows</x:v>
       </x:c>
       <x:c r="B6" t="n">
         <x:f>COUNTA('PLC I-O'!A2:A200)</x:f>
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D6" s="42" t="str">
-        <x:v>Native TIA/WinCC/Startdrive/PLCSIM, trained NVIDIA model, revision-C QElectroTech upgrade and revision-C panel CAD remain blocked. Historical native electrical/CAD files are quarantined baselines. No construction, safety, native compile, FAT, SAT or model-performance claim is made.</x:v>
-      </x:c>
-      <x:c r="E6" s="42"/>
-      <x:c r="F6" s="42"/>
-      <x:c r="G6" s="42"/>
-      <x:c r="H6" s="42"/>
+      <x:c r="D6" s="46" t="str">
+        <x:v>Native TIA/WinCC/Startdrive/PLCSIM, trained NVIDIA model, Revision-D QElectroTech and Revision-D panel CAD remain blocked. Historical native electrical/CAD files are quarantined baselines. No construction, safety, native compile, FAT, SAT or model-performance claim is made.</x:v>
+      </x:c>
+      <x:c r="E6" s="46"/>
+      <x:c r="F6" s="46"/>
+      <x:c r="G6" s="46"/>
+      <x:c r="H6" s="46"/>
     </x:row>
     <x:row r="7">
-      <x:c r="A7" s="30" t="str">
+      <x:c r="A7" s="36" t="str">
         <x:v>Physical DI</x:v>
       </x:c>
       <x:c r="B7" t="n">
         <x:f>COUNTIF('PLC I-O'!B2:B200,"DI")</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D7" s="42"/>
-      <x:c r="E7" s="42"/>
-      <x:c r="F7" s="42"/>
-      <x:c r="G7" s="42"/>
-      <x:c r="H7" s="42"/>
+      <x:c r="D7" s="46"/>
+      <x:c r="E7" s="46"/>
+      <x:c r="F7" s="46"/>
+      <x:c r="G7" s="46"/>
+      <x:c r="H7" s="46"/>
     </x:row>
     <x:row r="8">
-      <x:c r="A8" s="30" t="str">
+      <x:c r="A8" s="36" t="str">
         <x:v>Physical DO</x:v>
       </x:c>
       <x:c r="B8" t="n">
         <x:f>COUNTIF('PLC I-O'!B2:B200,"DO")</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D8" s="42"/>
-      <x:c r="E8" s="42"/>
-      <x:c r="F8" s="42"/>
-      <x:c r="G8" s="42"/>
-      <x:c r="H8" s="42"/>
+      <x:c r="D8" s="46"/>
+      <x:c r="E8" s="46"/>
+      <x:c r="F8" s="46"/>
+      <x:c r="G8" s="46"/>
+      <x:c r="H8" s="46"/>
     </x:row>
     <x:row r="9">
-      <x:c r="A9" s="30" t="str">
+      <x:c r="A9" s="36" t="str">
         <x:v>Analog inputs</x:v>
       </x:c>
       <x:c r="B9" t="n">
         <x:f>COUNTIF('PLC I-O'!B2:B200,"AI")</x:f>
         <x:v>8</x:v>
       </x:c>
-      <x:c r="D9" s="42"/>
-      <x:c r="E9" s="42"/>
-      <x:c r="F9" s="42"/>
-      <x:c r="G9" s="42"/>
-      <x:c r="H9" s="42"/>
+      <x:c r="D9" s="46"/>
+      <x:c r="E9" s="46"/>
+      <x:c r="F9" s="46"/>
+      <x:c r="G9" s="46"/>
+      <x:c r="H9" s="46"/>
     </x:row>
     <x:row r="10">
-      <x:c r="A10" s="30" t="str">
+      <x:c r="A10" s="36" t="str">
         <x:v>High-speed counters</x:v>
       </x:c>
       <x:c r="B10" t="n">
         <x:f>COUNTIF('PLC I-O'!B2:B200,"HSC")</x:f>
         <x:v>2</x:v>
       </x:c>
-      <x:c r="D10" s="42"/>
-      <x:c r="E10" s="42"/>
-      <x:c r="F10" s="42"/>
-      <x:c r="G10" s="42"/>
-      <x:c r="H10" s="42"/>
+      <x:c r="D10" s="46"/>
+      <x:c r="E10" s="46"/>
+      <x:c r="F10" s="46"/>
+      <x:c r="G10" s="46"/>
+      <x:c r="H10" s="46"/>
     </x:row>
     <x:row r="11">
-      <x:c r="A11" s="30" t="str">
+      <x:c r="A11" s="36" t="str">
         <x:v>Vision contract signals</x:v>
       </x:c>
       <x:c r="B11" t="n">
         <x:f>COUNTA('NVIDIA Interface'!A2:A100)</x:f>
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D11" s="42"/>
-      <x:c r="E11" s="42"/>
-      <x:c r="F11" s="42"/>
-      <x:c r="G11" s="42"/>
-      <x:c r="H11" s="42"/>
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D11" s="46"/>
+      <x:c r="E11" s="46"/>
+      <x:c r="F11" s="46"/>
+      <x:c r="G11" s="46"/>
+      <x:c r="H11" s="46"/>
     </x:row>
     <x:row r="12">
-      <x:c r="A12" s="30" t="str">
+      <x:c r="A12" s="36" t="str">
         <x:v>Controlled tests</x:v>
       </x:c>
       <x:c r="B12" t="n">
         <x:f>COUNTA('Test Coverage'!A2:A100)</x:f>
         <x:v>32</x:v>
       </x:c>
-      <x:c r="D12" s="42"/>
-      <x:c r="E12" s="42"/>
-      <x:c r="F12" s="42"/>
-      <x:c r="G12" s="42"/>
-      <x:c r="H12" s="42"/>
+      <x:c r="D12" s="46"/>
+      <x:c r="E12" s="46"/>
+      <x:c r="F12" s="46"/>
+      <x:c r="G12" s="46"/>
+      <x:c r="H12" s="46"/>
     </x:row>
     <x:row r="13">
-      <x:c r="A13" s="30" t="str">
+      <x:c r="A13" s="36" t="str">
         <x:v>Open/blocked gates</x:v>
       </x:c>
       <x:c r="B13" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"BLOCKED")+COUNTIF('Acceptance Gates'!C2:C100,"OPEN")</x:f>
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D13" s="42"/>
-      <x:c r="E13" s="42"/>
-      <x:c r="F13" s="42"/>
-      <x:c r="G13" s="42"/>
-      <x:c r="H13" s="42"/>
+      <x:c r="D13" s="46"/>
+      <x:c r="E13" s="46"/>
+      <x:c r="F13" s="46"/>
+      <x:c r="G13" s="46"/>
+      <x:c r="H13" s="46"/>
+    </x:row>
+    <x:row r="14">
+      <x:c r="A14" s="36" t="str">
+        <x:v>24 VDC demand (W)</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:f>55+24+120+100</x:f>
+        <x:v>299</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="36" t="str">
+        <x:v>Minimum current for 25% margin (A)</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:f>(55+24+120+100)/24*1.25</x:f>
+        <x:v>15.572916666666668</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:H2"/>
     <x:mergeCell ref="A3:H3"/>
+    <x:mergeCell ref="A4:H4"/>
     <x:mergeCell ref="D5:H5"/>
     <x:mergeCell ref="D6:H13"/>
   </x:mergeCells>
@@ -24650,7 +24376,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf40ef427cb3e4c72"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26516,7 +26242,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra91398c861934175"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -26553,7 +26279,7 @@
         <x:v>reset_condition</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>1001</x:v>
       </x:c>
@@ -26573,7 +26299,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>1002</x:v>
       </x:c>
@@ -26593,7 +26319,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>1003</x:v>
       </x:c>
@@ -26613,7 +26339,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>1004</x:v>
       </x:c>
@@ -26633,7 +26359,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>1101</x:v>
       </x:c>
@@ -26653,7 +26379,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>1102</x:v>
       </x:c>
@@ -26673,7 +26399,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>1201</x:v>
       </x:c>
@@ -26693,7 +26419,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>1202</x:v>
       </x:c>
@@ -26713,7 +26439,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>1301</x:v>
       </x:c>
@@ -26733,7 +26459,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>1303</x:v>
       </x:c>
@@ -26753,7 +26479,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>1304</x:v>
       </x:c>
@@ -26773,7 +26499,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>1305</x:v>
       </x:c>
@@ -26793,7 +26519,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>1306</x:v>
       </x:c>
@@ -26813,7 +26539,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>1307</x:v>
       </x:c>
@@ -26833,7 +26559,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" customHeight="1">
+    <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>1308</x:v>
       </x:c>
@@ -26853,7 +26579,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="27" customHeight="1">
+    <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>1309</x:v>
       </x:c>
@@ -26873,7 +26599,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>1310</x:v>
       </x:c>
@@ -26893,7 +26619,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" customHeight="1">
+    <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>1311</x:v>
       </x:c>
@@ -26913,7 +26639,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" customHeight="1">
+    <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>1313</x:v>
       </x:c>
@@ -26933,7 +26659,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="27" customHeight="1">
+    <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>1314</x:v>
       </x:c>
@@ -26953,7 +26679,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="27" customHeight="1">
+    <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>1315</x:v>
       </x:c>
@@ -26973,7 +26699,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="23" ht="27" customHeight="1">
+    <x:row r="23" ht="54" customHeight="1">
       <x:c r="A23" s="6" t="str">
         <x:v>1316</x:v>
       </x:c>
@@ -26993,7 +26719,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="27" customHeight="1">
+    <x:row r="24" ht="54" customHeight="1">
       <x:c r="A24" s="6" t="str">
         <x:v>1317</x:v>
       </x:c>
@@ -27013,7 +26739,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="25" ht="27" customHeight="1">
+    <x:row r="25" ht="54" customHeight="1">
       <x:c r="A25" s="6" t="str">
         <x:v>1318</x:v>
       </x:c>
@@ -27033,7 +26759,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="26" ht="27" customHeight="1">
+    <x:row r="26" ht="54" customHeight="1">
       <x:c r="A26" s="6" t="str">
         <x:v>1319</x:v>
       </x:c>
@@ -27053,7 +26779,7 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="27" ht="27" customHeight="1">
+    <x:row r="27" ht="54" customHeight="1">
       <x:c r="A27" s="6" t="str">
         <x:v>1320</x:v>
       </x:c>
@@ -27073,18 +26799,18 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" ht="27" customHeight="1">
+    <x:row r="28" ht="54" customHeight="1">
       <x:c r="A28" s="6" t="str">
-        <x:v>1401</x:v>
+        <x:v>1321</x:v>
       </x:c>
       <x:c r="B28" s="6" t="str">
-        <x:v>Capper not ready, acceptance timeout or completion timeout</x:v>
+        <x:v>Fill channel 1 pulse channel missing while analog flow is present</x:v>
       </x:c>
       <x:c r="C28" s="6" t="str">
         <x:v>Fault</x:v>
       </x:c>
       <x:c r="D28" s="6" t="str">
-        <x:v>Keep pair controlled; operator disposition</x:v>
+        <x:v>Close affected channel; remove its pump request; quality hold</x:v>
       </x:c>
       <x:c r="E28" s="6" t="str">
         <x:v>Yes</x:v>
@@ -27093,18 +26819,18 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" ht="27" customHeight="1">
+    <x:row r="29" ht="54" customHeight="1">
       <x:c r="A29" s="6" t="str">
-        <x:v>1402</x:v>
+        <x:v>1322</x:v>
       </x:c>
       <x:c r="B29" s="6" t="str">
-        <x:v>Capper reported fault or invalid handshake order</x:v>
+        <x:v>Fill channel 1 analog no-flow while pulse flow is present</x:v>
       </x:c>
       <x:c r="C29" s="6" t="str">
         <x:v>Fault</x:v>
       </x:c>
       <x:c r="D29" s="6" t="str">
-        <x:v>Keep pair controlled; operator disposition</x:v>
+        <x:v>Close affected channel; remove its pump request; quality hold</x:v>
       </x:c>
       <x:c r="E29" s="6" t="str">
         <x:v>Yes</x:v>
@@ -27113,18 +26839,18 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="30" ht="27" customHeight="1">
+    <x:row r="30" ht="54" customHeight="1">
       <x:c r="A30" s="6" t="str">
-        <x:v>1501</x:v>
+        <x:v>1323</x:v>
       </x:c>
       <x:c r="B30" s="6" t="str">
-        <x:v>Vision not ready</x:v>
+        <x:v>Fill channel 2 pulse channel missing while analog flow is present</x:v>
       </x:c>
       <x:c r="C30" s="6" t="str">
         <x:v>Fault</x:v>
       </x:c>
       <x:c r="D30" s="6" t="str">
-        <x:v>Do not transfer; quality hold</x:v>
+        <x:v>Close affected channel; remove its pump request; quality hold</x:v>
       </x:c>
       <x:c r="E30" s="6" t="str">
         <x:v>Yes</x:v>
@@ -27133,18 +26859,18 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="31" ht="27" customHeight="1">
+    <x:row r="31" ht="54" customHeight="1">
       <x:c r="A31" s="6" t="str">
-        <x:v>1502</x:v>
+        <x:v>1324</x:v>
       </x:c>
       <x:c r="B31" s="6" t="str">
-        <x:v>Vision result timeout</x:v>
+        <x:v>Fill channel 2 analog no-flow while pulse flow is present</x:v>
       </x:c>
       <x:c r="C31" s="6" t="str">
         <x:v>Fault</x:v>
       </x:c>
       <x:c r="D31" s="6" t="str">
-        <x:v>Do not transfer; quality hold</x:v>
+        <x:v>Close affected channel; remove its pump request; quality hold</x:v>
       </x:c>
       <x:c r="E31" s="6" t="str">
         <x:v>Yes</x:v>
@@ -27153,18 +26879,18 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="32" ht="27" customHeight="1">
+    <x:row r="32" ht="54" customHeight="1">
       <x:c r="A32" s="6" t="str">
-        <x:v>1503</x:v>
+        <x:v>1401</x:v>
       </x:c>
       <x:c r="B32" s="6" t="str">
-        <x:v>Vision stale/mismatched result ID</x:v>
+        <x:v>Capper not ready, acceptance timeout or completion timeout</x:v>
       </x:c>
       <x:c r="C32" s="6" t="str">
         <x:v>Fault</x:v>
       </x:c>
       <x:c r="D32" s="6" t="str">
-        <x:v>Do not transfer; quality hold</x:v>
+        <x:v>Keep pair controlled; operator disposition</x:v>
       </x:c>
       <x:c r="E32" s="6" t="str">
         <x:v>Yes</x:v>
@@ -27173,18 +26899,18 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="33" ht="27" customHeight="1">
+    <x:row r="33" ht="54" customHeight="1">
       <x:c r="A33" s="6" t="str">
-        <x:v>1504</x:v>
+        <x:v>1402</x:v>
       </x:c>
       <x:c r="B33" s="6" t="str">
-        <x:v>Vision blocking quality result or low confidence</x:v>
+        <x:v>Capper reported fault or invalid handshake order</x:v>
       </x:c>
       <x:c r="C33" s="6" t="str">
         <x:v>Fault</x:v>
       </x:c>
       <x:c r="D33" s="6" t="str">
-        <x:v>Do not transfer; quality hold</x:v>
+        <x:v>Keep pair controlled; operator disposition</x:v>
       </x:c>
       <x:c r="E33" s="6" t="str">
         <x:v>Yes</x:v>
@@ -27193,12 +26919,12 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" ht="27" customHeight="1">
+    <x:row r="34" ht="54" customHeight="1">
       <x:c r="A34" s="6" t="str">
-        <x:v>1505</x:v>
+        <x:v>1501</x:v>
       </x:c>
       <x:c r="B34" s="6" t="str">
-        <x:v>Vision heartbeat lost</x:v>
+        <x:v>Vision not ready</x:v>
       </x:c>
       <x:c r="C34" s="6" t="str">
         <x:v>Fault</x:v>
@@ -27213,12 +26939,12 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" ht="27" customHeight="1">
+    <x:row r="35" ht="54" customHeight="1">
       <x:c r="A35" s="6" t="str">
-        <x:v>1506</x:v>
+        <x:v>1502</x:v>
       </x:c>
       <x:c r="B35" s="6" t="str">
-        <x:v>Vision protocol contradiction</x:v>
+        <x:v>Vision result timeout</x:v>
       </x:c>
       <x:c r="C35" s="6" t="str">
         <x:v>Fault</x:v>
@@ -27233,30 +26959,110 @@
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" ht="27" customHeight="1">
+    <x:row r="36" ht="54" customHeight="1">
       <x:c r="A36" s="6" t="str">
-        <x:v>1601</x:v>
+        <x:v>1503</x:v>
       </x:c>
       <x:c r="B36" s="6" t="str">
-        <x:v>HMI command heartbeat lost</x:v>
+        <x:v>Vision stale/mismatched result ID</x:v>
       </x:c>
       <x:c r="C36" s="6" t="str">
         <x:v>Fault</x:v>
       </x:c>
       <x:c r="D36" s="6" t="str">
-        <x:v>Reject new HMI commands and enter controlled fault handling</x:v>
+        <x:v>Do not transfer; quality hold</x:v>
       </x:c>
       <x:c r="E36" s="6" t="str">
         <x:v>Yes</x:v>
       </x:c>
       <x:c r="F36" s="6" t="str">
+        <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="54" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>1504</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>Vision blocking quality result or low confidence</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="str">
+        <x:v>Fault</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
+        <x:v>Do not transfer; quality hold</x:v>
+      </x:c>
+      <x:c r="E37" s="6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="54" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>1505</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>Vision heartbeat lost</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>Fault</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>Do not transfer; quality hold</x:v>
+      </x:c>
+      <x:c r="E38" s="6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="54" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>1506</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>Vision protocol contradiction</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>Fault</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>Do not transfer; quality hold</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="54" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>1601</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>HMI command heartbeat lost</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>Fault</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>Reject new HMI commands and enter controlled fault handling</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="str">
+        <x:v>Yes</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
         <x:v>Cause cleared and explicit reset; never automatic restart</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R17fdeb6163824b25"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27372,7 +27178,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf442572143b04640"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -27409,7 +27215,7 @@
         <x:v>timeout_ms</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" ht="27" customHeight="1">
+    <x:row r="2" ht="54" customHeight="1">
       <x:c r="A2" s="6" t="str">
         <x:v>VISION_ENABLE</x:v>
       </x:c>
@@ -27429,7 +27235,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" ht="27" customHeight="1">
+    <x:row r="3" ht="54" customHeight="1">
       <x:c r="A3" s="6" t="str">
         <x:v>INSPECTION_TRIGGER</x:v>
       </x:c>
@@ -27449,7 +27255,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" ht="27" customHeight="1">
+    <x:row r="4" ht="54" customHeight="1">
       <x:c r="A4" s="6" t="str">
         <x:v>INSPECTION_ID</x:v>
       </x:c>
@@ -27469,7 +27275,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="5" ht="27" customHeight="1">
+    <x:row r="5" ht="54" customHeight="1">
       <x:c r="A5" s="6" t="str">
         <x:v>RECIPE_ID</x:v>
       </x:c>
@@ -27489,7 +27295,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" ht="27" customHeight="1">
+    <x:row r="6" ht="54" customHeight="1">
       <x:c r="A6" s="6" t="str">
         <x:v>EXPECTED_BOTTLES</x:v>
       </x:c>
@@ -27509,7 +27315,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" ht="27" customHeight="1">
+    <x:row r="7" ht="54" customHeight="1">
       <x:c r="A7" s="6" t="str">
         <x:v>TARGET_FILL_LEVEL</x:v>
       </x:c>
@@ -27529,7 +27335,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="8" ht="27" customHeight="1">
+    <x:row r="8" ht="54" customHeight="1">
       <x:c r="A8" s="6" t="str">
         <x:v>PLC_HEARTBEAT</x:v>
       </x:c>
@@ -27549,7 +27355,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" ht="27" customHeight="1">
+    <x:row r="9" ht="54" customHeight="1">
       <x:c r="A9" s="6" t="str">
         <x:v>VISION_READY</x:v>
       </x:c>
@@ -27569,7 +27375,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="10" ht="27" customHeight="1">
+    <x:row r="10" ht="54" customHeight="1">
       <x:c r="A10" s="6" t="str">
         <x:v>VISION_BUSY</x:v>
       </x:c>
@@ -27589,7 +27395,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="11" ht="27" customHeight="1">
+    <x:row r="11" ht="54" customHeight="1">
       <x:c r="A11" s="6" t="str">
         <x:v>RESULT_VALID</x:v>
       </x:c>
@@ -27609,7 +27415,7 @@
         <x:v>1000</x:v>
       </x:c>
     </x:row>
-    <x:row r="12" ht="27" customHeight="1">
+    <x:row r="12" ht="54" customHeight="1">
       <x:c r="A12" s="6" t="str">
         <x:v>RESULT_ID</x:v>
       </x:c>
@@ -27629,7 +27435,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" ht="27" customHeight="1">
+    <x:row r="13" ht="54" customHeight="1">
       <x:c r="A13" s="6" t="str">
         <x:v>BOTTLE_1_PASS</x:v>
       </x:c>
@@ -27649,7 +27455,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="14" ht="27" customHeight="1">
+    <x:row r="14" ht="54" customHeight="1">
       <x:c r="A14" s="6" t="str">
         <x:v>BOTTLE_2_PASS</x:v>
       </x:c>
@@ -27669,7 +27475,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" ht="27" customHeight="1">
+    <x:row r="15" ht="54" customHeight="1">
       <x:c r="A15" s="6" t="str">
         <x:v>FILL_1_STATUS</x:v>
       </x:c>
@@ -27689,7 +27495,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" ht="27" customHeight="1">
+    <x:row r="16" ht="54" customHeight="1">
       <x:c r="A16" s="6" t="str">
         <x:v>FILL_2_STATUS</x:v>
       </x:c>
@@ -27709,7 +27515,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" ht="27" customHeight="1">
+    <x:row r="17" ht="54" customHeight="1">
       <x:c r="A17" s="6" t="str">
         <x:v>LEAK_OR_SPILL_DETECTED</x:v>
       </x:c>
@@ -27729,7 +27535,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" ht="27" customHeight="1">
+    <x:row r="18" ht="54" customHeight="1">
       <x:c r="A18" s="6" t="str">
         <x:v>LOW_CONFIDENCE</x:v>
       </x:c>
@@ -27749,7 +27555,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" ht="27" customHeight="1">
+    <x:row r="19" ht="54" customHeight="1">
       <x:c r="A19" s="6" t="str">
         <x:v>VISION_WARNING</x:v>
       </x:c>
@@ -27769,7 +27575,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="20" ht="27" customHeight="1">
+    <x:row r="20" ht="54" customHeight="1">
       <x:c r="A20" s="6" t="str">
         <x:v>VISION_FAULT</x:v>
       </x:c>
@@ -27789,7 +27595,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="21" ht="27" customHeight="1">
+    <x:row r="21" ht="54" customHeight="1">
       <x:c r="A21" s="6" t="str">
         <x:v>INFERENCE_TIME</x:v>
       </x:c>
@@ -27809,7 +27615,7 @@
         <x:v>0</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" ht="27" customHeight="1">
+    <x:row r="22" ht="54" customHeight="1">
       <x:c r="A22" s="6" t="str">
         <x:v>VISION_HEARTBEAT</x:v>
       </x:c>
@@ -27827,12 +27633,132 @@
       </x:c>
       <x:c r="F22" s="6" t="str">
         <x:v>1000</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="54" customHeight="1">
+      <x:c r="A23" s="6" t="str">
+        <x:v>VISION_RESULT_ACK_ID</x:v>
+      </x:c>
+      <x:c r="B23" s="6" t="str">
+        <x:v>UDINT</x:v>
+      </x:c>
+      <x:c r="C23" s="6" t="str">
+        <x:v>PLC</x:v>
+      </x:c>
+      <x:c r="D23" s="6" t="str">
+        <x:v>Acknowledges the immutable published result; edge clears RESULT_VALID only on exact match</x:v>
+      </x:c>
+      <x:c r="E23" s="6" t="str">
+        <x:v>OPC UA subscribed node</x:v>
+      </x:c>
+      <x:c r="F23" s="6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="54" customHeight="1">
+      <x:c r="A24" s="6" t="str">
+        <x:v>VISION_SESSION_EPOCH</x:v>
+      </x:c>
+      <x:c r="B24" s="6" t="str">
+        <x:v>UDINT</x:v>
+      </x:c>
+      <x:c r="C24" s="6" t="str">
+        <x:v>PLC</x:v>
+      </x:c>
+      <x:c r="D24" s="6" t="str">
+        <x:v>PLC startup/session correlation; reconnect must not replay a prior-session release</x:v>
+      </x:c>
+      <x:c r="E24" s="6" t="str">
+        <x:v>OPC UA subscribed node</x:v>
+      </x:c>
+      <x:c r="F24" s="6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="54" customHeight="1">
+      <x:c r="A25" s="6" t="str">
+        <x:v>VISION_RESULT_SESSION_EPOCH</x:v>
+      </x:c>
+      <x:c r="B25" s="6" t="str">
+        <x:v>UDINT</x:v>
+      </x:c>
+      <x:c r="C25" s="6" t="str">
+        <x:v>NVIDIA</x:v>
+      </x:c>
+      <x:c r="D25" s="6" t="str">
+        <x:v>Echoes the request session epoch in the immutable result; PLC rejects cross-session publication</x:v>
+      </x:c>
+      <x:c r="E25" s="6" t="str">
+        <x:v>OPC UA published result payload</x:v>
+      </x:c>
+      <x:c r="F25" s="6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="54" customHeight="1">
+      <x:c r="A26" s="6" t="str">
+        <x:v>VISION_DIAG_REASON</x:v>
+      </x:c>
+      <x:c r="B26" s="6" t="str">
+        <x:v>UINT</x:v>
+      </x:c>
+      <x:c r="C26" s="6" t="str">
+        <x:v>PLC</x:v>
+      </x:c>
+      <x:c r="D26" s="6" t="str">
+        <x:v>First-out PLC interface diagnostic enumeration</x:v>
+      </x:c>
+      <x:c r="E26" s="6" t="str">
+        <x:v>OPC UA published node</x:v>
+      </x:c>
+      <x:c r="F26" s="6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="54" customHeight="1">
+      <x:c r="A27" s="6" t="str">
+        <x:v>VISION_MODEL_ID</x:v>
+      </x:c>
+      <x:c r="B27" s="6" t="str">
+        <x:v>STRING[32]</x:v>
+      </x:c>
+      <x:c r="C27" s="6" t="str">
+        <x:v>NVIDIA</x:v>
+      </x:c>
+      <x:c r="D27" s="6" t="str">
+        <x:v>Controlled model identifier included in the atomic result</x:v>
+      </x:c>
+      <x:c r="E27" s="6" t="str">
+        <x:v>OPC UA published result payload</x:v>
+      </x:c>
+      <x:c r="F27" s="6" t="str">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="54" customHeight="1">
+      <x:c r="A28" s="6" t="str">
+        <x:v>VISION_MODEL_SHA256</x:v>
+      </x:c>
+      <x:c r="B28" s="6" t="str">
+        <x:v>STRING[64]</x:v>
+      </x:c>
+      <x:c r="C28" s="6" t="str">
+        <x:v>NVIDIA</x:v>
+      </x:c>
+      <x:c r="D28" s="6" t="str">
+        <x:v>Exact controlled model SHA-256 included in the atomic result</x:v>
+      </x:c>
+      <x:c r="E28" s="6" t="str">
+        <x:v>OPC UA published result payload</x:v>
+      </x:c>
+      <x:c r="F28" s="6" t="str">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R71bcc7a48f6143e5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28062,7 +27988,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R881a131fbae24c58"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -28191,7 +28117,7 @@
       </x:c>
       <x:c r="P2" s="6" t="str"/>
       <x:c r="Q2" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="27" customHeight="1">
@@ -28242,7 +28168,7 @@
       </x:c>
       <x:c r="P3" s="6" t="str"/>
       <x:c r="Q3" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="27" customHeight="1">
@@ -28293,7 +28219,7 @@
       </x:c>
       <x:c r="P4" s="6" t="str"/>
       <x:c r="Q4" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="27" customHeight="1">
@@ -28344,7 +28270,7 @@
       </x:c>
       <x:c r="P5" s="6" t="str"/>
       <x:c r="Q5" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="27" customHeight="1">
@@ -28397,7 +28323,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q6" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="27" customHeight="1">
@@ -28448,7 +28374,7 @@
       </x:c>
       <x:c r="P7" s="6" t="str"/>
       <x:c r="Q7" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="27" customHeight="1">
@@ -28499,7 +28425,7 @@
       </x:c>
       <x:c r="P8" s="6" t="str"/>
       <x:c r="Q8" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="27" customHeight="1">
@@ -28552,7 +28478,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q9" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="27" customHeight="1">
@@ -28603,7 +28529,7 @@
       </x:c>
       <x:c r="P10" s="6" t="str"/>
       <x:c r="Q10" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="27" customHeight="1">
@@ -28654,7 +28580,7 @@
       </x:c>
       <x:c r="P11" s="6" t="str"/>
       <x:c r="Q11" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="27" customHeight="1">
@@ -28707,7 +28633,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q12" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="27" customHeight="1">
@@ -28758,7 +28684,7 @@
       </x:c>
       <x:c r="P13" s="6" t="str"/>
       <x:c r="Q13" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="27" customHeight="1">
@@ -28809,7 +28735,7 @@
       </x:c>
       <x:c r="P14" s="6" t="str"/>
       <x:c r="Q14" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="27" customHeight="1">
@@ -28862,7 +28788,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q15" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="27" customHeight="1">
@@ -28913,7 +28839,7 @@
       </x:c>
       <x:c r="P16" s="6" t="str"/>
       <x:c r="Q16" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="27" customHeight="1">
@@ -28964,7 +28890,7 @@
       </x:c>
       <x:c r="P17" s="6" t="str"/>
       <x:c r="Q17" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="27" customHeight="1">
@@ -29017,7 +28943,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q18" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="27" customHeight="1">
@@ -29068,7 +28994,7 @@
       </x:c>
       <x:c r="P19" s="6" t="str"/>
       <x:c r="Q19" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="27" customHeight="1">
@@ -29119,7 +29045,7 @@
       </x:c>
       <x:c r="P20" s="6" t="str"/>
       <x:c r="Q20" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="27" customHeight="1">
@@ -29172,7 +29098,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q21" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="27" customHeight="1">
@@ -29223,7 +29149,7 @@
       </x:c>
       <x:c r="P22" s="6" t="str"/>
       <x:c r="Q22" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="27" customHeight="1">
@@ -29274,7 +29200,7 @@
       </x:c>
       <x:c r="P23" s="6" t="str"/>
       <x:c r="Q23" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="27" customHeight="1">
@@ -29327,7 +29253,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q24" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="27" customHeight="1">
@@ -29378,7 +29304,7 @@
       </x:c>
       <x:c r="P25" s="6" t="str"/>
       <x:c r="Q25" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="26" ht="27" customHeight="1">
@@ -29429,7 +29355,7 @@
       </x:c>
       <x:c r="P26" s="6" t="str"/>
       <x:c r="Q26" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="27" ht="27" customHeight="1">
@@ -29482,7 +29408,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q27" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="28" ht="27" customHeight="1">
@@ -29533,7 +29459,7 @@
       </x:c>
       <x:c r="P28" s="6" t="str"/>
       <x:c r="Q28" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="29" ht="27" customHeight="1">
@@ -29584,7 +29510,7 @@
       </x:c>
       <x:c r="P29" s="6" t="str"/>
       <x:c r="Q29" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="30" ht="27" customHeight="1">
@@ -29637,7 +29563,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q30" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="31" ht="27" customHeight="1">
@@ -29688,7 +29614,7 @@
       </x:c>
       <x:c r="P31" s="6" t="str"/>
       <x:c r="Q31" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="32" ht="27" customHeight="1">
@@ -29739,7 +29665,7 @@
       </x:c>
       <x:c r="P32" s="6" t="str"/>
       <x:c r="Q32" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="33" ht="27" customHeight="1">
@@ -29792,7 +29718,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q33" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="34" ht="27" customHeight="1">
@@ -29843,7 +29769,7 @@
       </x:c>
       <x:c r="P34" s="6" t="str"/>
       <x:c r="Q34" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="35" ht="27" customHeight="1">
@@ -29894,7 +29820,7 @@
       </x:c>
       <x:c r="P35" s="6" t="str"/>
       <x:c r="Q35" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="36" ht="27" customHeight="1">
@@ -29947,7 +29873,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q36" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="37" ht="27" customHeight="1">
@@ -29998,7 +29924,7 @@
       </x:c>
       <x:c r="P37" s="6" t="str"/>
       <x:c r="Q37" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="38" ht="27" customHeight="1">
@@ -30049,7 +29975,7 @@
       </x:c>
       <x:c r="P38" s="6" t="str"/>
       <x:c r="Q38" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="39" ht="27" customHeight="1">
@@ -30100,7 +30026,7 @@
       </x:c>
       <x:c r="P39" s="6" t="str"/>
       <x:c r="Q39" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="40" ht="27" customHeight="1">
@@ -30151,7 +30077,7 @@
       </x:c>
       <x:c r="P40" s="6" t="str"/>
       <x:c r="Q40" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="41" ht="27" customHeight="1">
@@ -30202,7 +30128,7 @@
       </x:c>
       <x:c r="P41" s="6" t="str"/>
       <x:c r="Q41" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="42" ht="27" customHeight="1">
@@ -30255,7 +30181,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q42" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="43" ht="27" customHeight="1">
@@ -30306,7 +30232,7 @@
       </x:c>
       <x:c r="P43" s="6" t="str"/>
       <x:c r="Q43" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="44" ht="27" customHeight="1">
@@ -30357,7 +30283,7 @@
       </x:c>
       <x:c r="P44" s="6" t="str"/>
       <x:c r="Q44" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="45" ht="27" customHeight="1">
@@ -30410,7 +30336,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q45" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="46" ht="27" customHeight="1">
@@ -30461,7 +30387,7 @@
       </x:c>
       <x:c r="P46" s="6" t="str"/>
       <x:c r="Q46" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="47" ht="27" customHeight="1">
@@ -30514,7 +30440,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q47" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="48" ht="27" customHeight="1">
@@ -30565,7 +30491,7 @@
       </x:c>
       <x:c r="P48" s="6" t="str"/>
       <x:c r="Q48" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="49" ht="27" customHeight="1">
@@ -30618,7 +30544,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q49" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="50" ht="27" customHeight="1">
@@ -30669,7 +30595,7 @@
       </x:c>
       <x:c r="P50" s="6" t="str"/>
       <x:c r="Q50" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="51" ht="27" customHeight="1">
@@ -30722,7 +30648,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q51" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="52" ht="27" customHeight="1">
@@ -30773,7 +30699,7 @@
       </x:c>
       <x:c r="P52" s="6" t="str"/>
       <x:c r="Q52" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="53" ht="27" customHeight="1">
@@ -30826,7 +30752,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q53" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="54" ht="27" customHeight="1">
@@ -30877,7 +30803,7 @@
       </x:c>
       <x:c r="P54" s="6" t="str"/>
       <x:c r="Q54" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="55" ht="27" customHeight="1">
@@ -30930,7 +30856,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q55" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="56" ht="27" customHeight="1">
@@ -30981,7 +30907,7 @@
       </x:c>
       <x:c r="P56" s="6" t="str"/>
       <x:c r="Q56" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="57" ht="27" customHeight="1">
@@ -31034,7 +30960,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q57" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="58" ht="27" customHeight="1">
@@ -31085,7 +31011,7 @@
       </x:c>
       <x:c r="P58" s="6" t="str"/>
       <x:c r="Q58" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="59" ht="27" customHeight="1">
@@ -31138,7 +31064,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q59" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="60" ht="27" customHeight="1">
@@ -31189,7 +31115,7 @@
       </x:c>
       <x:c r="P60" s="6" t="str"/>
       <x:c r="Q60" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="61" ht="27" customHeight="1">
@@ -31242,7 +31168,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q61" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="62" ht="27" customHeight="1">
@@ -31293,7 +31219,7 @@
       </x:c>
       <x:c r="P62" s="6" t="str"/>
       <x:c r="Q62" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="63" ht="27" customHeight="1">
@@ -31346,7 +31272,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q63" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="64" ht="27" customHeight="1">
@@ -31397,7 +31323,7 @@
       </x:c>
       <x:c r="P64" s="6" t="str"/>
       <x:c r="Q64" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="65" ht="27" customHeight="1">
@@ -31450,7 +31376,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q65" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="66" ht="27" customHeight="1">
@@ -31501,7 +31427,7 @@
       </x:c>
       <x:c r="P66" s="6" t="str"/>
       <x:c r="Q66" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="67" ht="27" customHeight="1">
@@ -31554,7 +31480,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q67" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="68" ht="27" customHeight="1">
@@ -31605,7 +31531,7 @@
       </x:c>
       <x:c r="P68" s="6" t="str"/>
       <x:c r="Q68" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="69" ht="27" customHeight="1">
@@ -31658,7 +31584,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q69" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="70" ht="27" customHeight="1">
@@ -31709,7 +31635,7 @@
       </x:c>
       <x:c r="P70" s="6" t="str"/>
       <x:c r="Q70" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="71" ht="27" customHeight="1">
@@ -31760,7 +31686,7 @@
       </x:c>
       <x:c r="P71" s="6" t="str"/>
       <x:c r="Q71" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="72" ht="27" customHeight="1">
@@ -31810,10 +31736,10 @@
         <x:v>W0109</x:v>
       </x:c>
       <x:c r="P72" s="6" t="str">
-        <x:v>X0:0V</x:v>
+        <x:v>X0:MANA</x:v>
       </x:c>
       <x:c r="Q72" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="73" ht="27" customHeight="1">
@@ -31833,7 +31759,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="F73" s="6" t="str">
-        <x:v>4</x:v>
+        <x:v>SH</x:v>
       </x:c>
       <x:c r="G73" s="6" t="str">
         <x:v>-FT100</x:v>
@@ -31866,7 +31792,7 @@
         <x:v>SC100 panel-end only</x:v>
       </x:c>
       <x:c r="Q73" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="74" ht="27" customHeight="1">
@@ -31917,7 +31843,7 @@
       </x:c>
       <x:c r="P74" s="6" t="str"/>
       <x:c r="Q74" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="75" ht="27" customHeight="1">
@@ -31968,7 +31894,7 @@
       </x:c>
       <x:c r="P75" s="6" t="str"/>
       <x:c r="Q75" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="76" ht="27" customHeight="1">
@@ -32018,10 +31944,10 @@
         <x:v>W0113</x:v>
       </x:c>
       <x:c r="P76" s="6" t="str">
-        <x:v>X0:0V</x:v>
+        <x:v>X0:MANA</x:v>
       </x:c>
       <x:c r="Q76" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="77" ht="27" customHeight="1">
@@ -32041,7 +31967,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="F77" s="6" t="str">
-        <x:v>4</x:v>
+        <x:v>SH</x:v>
       </x:c>
       <x:c r="G77" s="6" t="str">
         <x:v>-FT101</x:v>
@@ -32074,7 +32000,7 @@
         <x:v>SC100 panel-end only</x:v>
       </x:c>
       <x:c r="Q77" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="78" ht="27" customHeight="1">
@@ -32094,7 +32020,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="F78" s="6" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G78" s="6" t="str">
         <x:v>-FT100</x:v>
@@ -32125,7 +32051,7 @@
       </x:c>
       <x:c r="P78" s="6" t="str"/>
       <x:c r="Q78" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="79" ht="27" customHeight="1">
@@ -32145,7 +32071,7 @@
         <x:v>C021</x:v>
       </x:c>
       <x:c r="F79" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G79" s="6" t="str">
         <x:v>-FT100</x:v>
@@ -32178,7 +32104,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q79" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="80" ht="27" customHeight="1">
@@ -32198,7 +32124,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="F80" s="6" t="str">
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="G80" s="6" t="str">
         <x:v>-FT101</x:v>
@@ -32229,7 +32155,7 @@
       </x:c>
       <x:c r="P80" s="6" t="str"/>
       <x:c r="Q80" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="81" ht="27" customHeight="1">
@@ -32249,7 +32175,7 @@
         <x:v>C022</x:v>
       </x:c>
       <x:c r="F81" s="6" t="str">
-        <x:v>6</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G81" s="6" t="str">
         <x:v>-FT101</x:v>
@@ -32282,7 +32208,7 @@
         <x:v>X0:0V</x:v>
       </x:c>
       <x:c r="Q81" s="6" t="str">
-        <x:v>Controlled Rev-C connection; native QET continuity verification remains open</x:v>
+        <x:v>Controlled Rev-D topology; conductor size/terminal family and native QET continuity verification remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="82" ht="27" customHeight="1">
@@ -32313,7 +32239,7 @@
       <x:c r="O82" s="6" t="str"/>
       <x:c r="P82" s="6" t="str"/>
       <x:c r="Q82" s="6" t="str">
-        <x:v>Reference terminal/bar; final product family and bridge plan open</x:v>
+        <x:v>Final product family and bridge plan open</x:v>
       </x:c>
     </x:row>
     <x:row r="83" ht="27" customHeight="1">
@@ -32344,7 +32270,7 @@
       <x:c r="O83" s="6" t="str"/>
       <x:c r="P83" s="6" t="str"/>
       <x:c r="Q83" s="6" t="str">
-        <x:v>Reference terminal/bar; final product family and bridge plan open</x:v>
+        <x:v>0 V/PE bonding policy requires site EMC decision</x:v>
       </x:c>
     </x:row>
     <x:row r="84" ht="27" customHeight="1">
@@ -32375,7 +32301,7 @@
       <x:c r="O84" s="6" t="str"/>
       <x:c r="P84" s="6" t="str"/>
       <x:c r="Q84" s="6" t="str">
-        <x:v>Reference terminal/bar; final product family and bridge plan open</x:v>
+        <x:v>MANA/0 V bonding follows AI manual and approved EMC plan; native verification open</x:v>
       </x:c>
     </x:row>
     <x:row r="85" ht="27" customHeight="1">
@@ -32389,7 +32315,7 @@
         <x:v>SC100:1</x:v>
       </x:c>
       <x:c r="D85" s="6" t="str">
-        <x:v>Panel-end shield-clamp reference</x:v>
+        <x:v>Panel-end shield clamp bonded once to PE100/functional earth</x:v>
       </x:c>
       <x:c r="E85" s="6" t="str"/>
       <x:c r="F85" s="6" t="str"/>
@@ -32406,13 +32332,13 @@
       <x:c r="O85" s="6" t="str"/>
       <x:c r="P85" s="6" t="str"/>
       <x:c r="Q85" s="6" t="str">
-        <x:v>Reference terminal/bar; final product family and bridge plan open</x:v>
+        <x:v>Bond conductor size and physical route open pending EMC/PE design</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R98568e9c10334e7b"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -19911,7 +19911,7 @@
         <x:v>VAL-D-STATIC</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>Revision-D canonical/source/schedule validation suite; the executed report records the current check count</x:v>
+        <x:v>Revision-D.1 canonical/source/schedule validation suite; the executed report records the current check count</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
@@ -21109,7 +21109,7 @@
         <x:v>Electrical owner</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Revision-D FCStd/exchange validation</x:v>
+        <x:v>Revision-D.1 FCStd/exchange validation</x:v>
       </x:c>
       <x:c r="E20" s="6" t="str">
         <x:v>OPEN</x:v>
@@ -21155,7 +21155,7 @@
         <x:v>Electrical owner</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
-        <x:v>Revision-D schematic authoring, reopen, export and review</x:v>
+        <x:v>Revision-D.1 schematic authoring, reopen, export and review</x:v>
       </x:c>
       <x:c r="E22" s="6" t="str">
         <x:v>OPEN</x:v>
@@ -21362,7 +21362,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Revision-D deterministic validator and source-parity checks pass; see current automated report for count</x:v>
+        <x:v>Revision-D.1 deterministic validator and source-parity checks pass; see current automated report for count</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
@@ -21468,7 +21468,7 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>Revision-D QET reopens and reconciles</x:v>
+        <x:v>Revision-D.1 QET reopens and reconciles</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
         <x:v>BLOCKED</x:v>
@@ -21488,7 +21488,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>Revision-D native schematics do not exist</x:v>
+        <x:v>Revision-D.1 native schematics do not exist</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
@@ -21496,7 +21496,7 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>Revision-D FCStd reopens</x:v>
+        <x:v>Revision-D.1 FCStd reopens</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
         <x:v>BLOCKED</x:v>
@@ -21516,7 +21516,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>Revision-D exchange files do not exist and FreeCAD is absent</x:v>
+        <x:v>Revision-D.1 exchange files do not exist and FreeCAD is absent</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
@@ -21600,7 +21600,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Local source-design scope: simulator, 32 scenarios, edge service, interface harness and Revision-D independent interface-oracle tests pass; native integration remains blocked under gates 9 and 18</x:v>
+        <x:v>Local source-design scope: simulator, 32 scenarios, edge service, interface harness and Revision-D.1 independent interface-oracle tests pass; native integration remains blocked under gates 9 and 18</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
@@ -23888,7 +23888,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="24" t="str">
-        <x:v>FICTIONAL ENGINEERING PROJECT — NOT FOR CONSTRUCTION | Revision D | Professional controlled engineering-development package</x:v>
+        <x:v>FICTIONAL ENGINEERING PROJECT — NOT FOR CONSTRUCTION | Revision D.1 | Professional controlled engineering-development release candidate</x:v>
       </x:c>
       <x:c r="B3" s="24"/>
       <x:c r="C3" s="24"/>
@@ -23934,7 +23934,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="D6" s="46" t="str">
-        <x:v>Native TIA/WinCC/Startdrive/PLCSIM, trained NVIDIA model, Revision-D QElectroTech and Revision-D panel CAD remain blocked. Historical native electrical/CAD files are quarantined baselines. No construction, safety, native compile, FAT, SAT or model-performance claim is made.</x:v>
+        <x:v>Native TIA/WinCC/Startdrive/PLCSIM, trained NVIDIA model, Revision-D.1 QElectroTech and Revision-D.1 panel CAD remain blocked. Historical native electrical/CAD files are byte-exact quarantined baselines. No construction, safety, native compile, FAT, SAT or model-performance claim is made.</x:v>
       </x:c>
       <x:c r="E6" s="46"/>
       <x:c r="F6" s="46"/>

--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -21,7 +21,8 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Coverage" sheetId="17" r:id="rId20"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Requests" sheetId="18" r:id="rId21"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Gates" sheetId="19" r:id="rId22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="20" r:id="rId23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document Register" sheetId="20" r:id="rId23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="21" r:id="rId24"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -461,6 +462,21 @@
 </x:table>
 </file>
 
+<file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="DocumentRegisterTable" displayName="DocumentRegisterTable" ref="A1:F14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F14"/>
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="document_id"/>
+    <x:tableColumn id="2" name="title"/>
+    <x:tableColumn id="3" name="path"/>
+    <x:tableColumn id="4" name="revision"/>
+    <x:tableColumn id="5" name="owner"/>
+    <x:tableColumn id="6" name="status"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
 <x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="DrivePZDTable" displayName="DrivePZDTable" ref="A1:J9" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:J9"/>
@@ -1151,11 +1167,17 @@
       <x:c r="H8" s="6" t="str">
         <x:v>Startdrive selection open</x:v>
       </x:c>
-      <x:c r="I8" s="6" t="str"/>
-      <x:c r="J8" s="6" t="str"/>
-      <x:c r="K8" s="6" t="str"/>
+      <x:c r="I8" s="6" t="str">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K8" s="6" t="str">
+        <x:v>225.4</x:v>
+      </x:c>
       <x:c r="L8" s="6" t="str">
-        <x:v>Rating, envelope and clearances blocked by motor/mechanics and native Startdrive</x:v>
+        <x:v>SELECTED ENVELOPE; drive rating/duty and Startdrive configuration remain provisional</x:v>
       </x:c>
       <x:c r="M8" s="6" t="str">
         <x:v>https://mall.industry.siemens.com/mall/en/WW/Catalog/Product/6SL3210-1KE12-3UF2</x:v>
@@ -1192,11 +1214,17 @@
       <x:c r="H9" s="6" t="str">
         <x:v>Startdrive selection open</x:v>
       </x:c>
-      <x:c r="I9" s="6" t="str"/>
-      <x:c r="J9" s="6" t="str"/>
-      <x:c r="K9" s="6" t="str"/>
+      <x:c r="I9" s="6" t="str">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="K9" s="6" t="str">
+        <x:v>225.4</x:v>
+      </x:c>
       <x:c r="L9" s="6" t="str">
-        <x:v>Rating, envelope and clearances blocked by pump curve and motor data</x:v>
+        <x:v>SELECTED ENVELOPE; drive rating/duty and Startdrive configuration remain provisional</x:v>
       </x:c>
       <x:c r="M9" s="6" t="str">
         <x:v>https://mall.industry.siemens.com/mall/en/WW/Catalog/Product/6SL3210-1KE12-3UF2</x:v>
@@ -1280,7 +1308,9 @@
       <x:c r="H11" s="6" t="str">
         <x:v>Native configuration open</x:v>
       </x:c>
-      <x:c r="I11" s="6" t="str"/>
+      <x:c r="I11" s="6" t="str">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="J11" s="6" t="str">
         <x:v>147</x:v>
       </x:c>
@@ -1288,7 +1318,7 @@
         <x:v>127</x:v>
       </x:c>
       <x:c r="L11" s="6" t="str">
-        <x:v>Exact width and site policy remain procurement/native gates</x:v>
+        <x:v>SELECTED NETWORK BASELINE — native configuration and site policy open</x:v>
       </x:c>
       <x:c r="M11" s="6" t="str">
         <x:v>https://mall.industry.siemens.com/mall/en/oeii/Catalog/Product?SiepCountryCode=OE&amp;mlfb=6GK5615-0AA01-2AA2</x:v>
@@ -1323,11 +1353,17 @@
       <x:c r="H12" s="6" t="str">
         <x:v>JetPack/DeepStream image not selected</x:v>
       </x:c>
-      <x:c r="I12" s="6" t="str"/>
-      <x:c r="J12" s="6" t="str"/>
-      <x:c r="K12" s="6" t="str"/>
+      <x:c r="I12" s="6" t="str">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="str">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="K12" s="6" t="str">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="L12" s="6" t="str">
-        <x:v>Carrier, thermals, power, EMC and lifecycle are open</x:v>
+        <x:v>TBD — NOT PROCUREMENT OR CONSTRUCTION DATA; confirm industrial carrier, thermal solution, EMC and lifecycle</x:v>
       </x:c>
       <x:c r="M12" s="6" t="str">
         <x:v>https://developer.nvidia.com/deepstream-sdk</x:v>
@@ -18666,10 +18702,10 @@
         <x:v>-A100</x:v>
       </x:c>
       <x:c r="B2" s="6" t="str">
-        <x:v>120</x:v>
+        <x:v>300</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
         <x:v>35</x:v>
@@ -18687,7 +18723,7 @@
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I2" s="6" t="str">
-        <x:v>Controls</x:v>
+        <x:v>PLC / control</x:v>
       </x:c>
       <x:c r="J2" s="6" t="str">
         <x:v>25</x:v>
@@ -18696,16 +18732,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L2" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M2" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N2" s="6" t="str">
-        <x:v>Official Siemens data sheet</x:v>
+        <x:v>Official Siemens product data; simplified rectangular selected-device envelope</x:v>
       </x:c>
       <x:c r="O2" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED BASELINE — native TIA catalog/configuration and accessory confirmation open</x:v>
       </x:c>
       <x:c r="P2" s="6" t="str">
         <x:v>=FC01+CP01-A100</x:v>
@@ -18716,10 +18752,10 @@
         <x:v>-A101</x:v>
       </x:c>
       <x:c r="B3" s="6" t="str">
-        <x:v>185</x:v>
+        <x:v>339</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
         <x:v>35</x:v>
@@ -18737,7 +18773,7 @@
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I3" s="6" t="str">
-        <x:v>Controls</x:v>
+        <x:v>PLC / control</x:v>
       </x:c>
       <x:c r="J3" s="6" t="str">
         <x:v>25</x:v>
@@ -18746,16 +18782,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L3" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M3" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N3" s="6" t="str">
-        <x:v>Official Siemens data sheet</x:v>
+        <x:v>Official Siemens product data; simplified rectangular selected-device envelope</x:v>
       </x:c>
       <x:c r="O3" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED BASELINE — native TIA catalog/configuration and accessory confirmation open</x:v>
       </x:c>
       <x:c r="P3" s="6" t="str">
         <x:v>=FC01+CP01-A101</x:v>
@@ -18766,10 +18802,10 @@
         <x:v>-A102</x:v>
       </x:c>
       <x:c r="B4" s="6" t="str">
-        <x:v>250</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
         <x:v>35</x:v>
@@ -18787,7 +18823,7 @@
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I4" s="6" t="str">
-        <x:v>Controls</x:v>
+        <x:v>PLC / control</x:v>
       </x:c>
       <x:c r="J4" s="6" t="str">
         <x:v>25</x:v>
@@ -18796,16 +18832,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L4" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M4" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N4" s="6" t="str">
-        <x:v>Official Siemens data sheet</x:v>
+        <x:v>Official Siemens product data; simplified rectangular selected-device envelope</x:v>
       </x:c>
       <x:c r="O4" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED BASELINE — native TIA catalog/configuration and accessory confirmation open</x:v>
       </x:c>
       <x:c r="P4" s="6" t="str">
         <x:v>=FC01+CP01-A102</x:v>
@@ -18816,10 +18852,10 @@
         <x:v>-A103</x:v>
       </x:c>
       <x:c r="B5" s="6" t="str">
-        <x:v>315</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>35</x:v>
@@ -18837,7 +18873,7 @@
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I5" s="6" t="str">
-        <x:v>Controls</x:v>
+        <x:v>PLC / control</x:v>
       </x:c>
       <x:c r="J5" s="6" t="str">
         <x:v>25</x:v>
@@ -18846,16 +18882,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L5" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M5" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N5" s="6" t="str">
-        <x:v>Official Siemens data sheet</x:v>
+        <x:v>Official Siemens product data; simplified rectangular selected-device envelope</x:v>
       </x:c>
       <x:c r="O5" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED BASELINE — native TIA catalog/configuration and accessory confirmation open</x:v>
       </x:c>
       <x:c r="P5" s="6" t="str">
         <x:v>=FC01+CP01-A103</x:v>
@@ -18866,10 +18902,10 @@
         <x:v>-A104</x:v>
       </x:c>
       <x:c r="B6" s="6" t="str">
-        <x:v>380</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>35</x:v>
@@ -18887,7 +18923,7 @@
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I6" s="6" t="str">
-        <x:v>Analog</x:v>
+        <x:v>PLC / control</x:v>
       </x:c>
       <x:c r="J6" s="6" t="str">
         <x:v>25</x:v>
@@ -18896,16 +18932,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L6" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M6" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N6" s="6" t="str">
-        <x:v>Official Siemens data sheet</x:v>
+        <x:v>Official Siemens product data; simplified rectangular selected-device envelope</x:v>
       </x:c>
       <x:c r="O6" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED BASELINE — native TIA catalog/configuration and accessory confirmation open</x:v>
       </x:c>
       <x:c r="P6" s="6" t="str">
         <x:v>=FC01+CP01-A104</x:v>
@@ -18916,19 +18952,19 @@
         <x:v>-H100</x:v>
       </x:c>
       <x:c r="B7" s="6" t="str">
-        <x:v>290</x:v>
+        <x:v>300.85</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
-        <x:v>200</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>214</x:v>
+        <x:v>198.3</x:v>
       </x:c>
       <x:c r="E7" s="6" t="str">
-        <x:v>158</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="F7" s="6" t="str">
-        <x:v>63.6</x:v>
+        <x:v>55.6</x:v>
       </x:c>
       <x:c r="G7" s="6" t="str">
         <x:v>Door cutout</x:v>
@@ -18940,22 +18976,22 @@
         <x:v>HMI</x:v>
       </x:c>
       <x:c r="J7" s="6" t="str">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K7" s="6" t="str">
-        <x:v>25</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L7" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M7" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N7" s="6" t="str">
-        <x:v>Official Siemens data sheet</x:v>
+        <x:v>Official Siemens envelope/cutout: outer 214 x 158 x 63.6 mm; cutout 198.3 x 142 mm</x:v>
       </x:c>
       <x:c r="O7" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED BASELINE — native WinCC project/compile and door reinforcement open</x:v>
       </x:c>
       <x:c r="P7" s="6" t="str">
         <x:v>=FC01+CP01-H100</x:v>
@@ -18966,40 +19002,46 @@
         <x:v>-U100</x:v>
       </x:c>
       <x:c r="B8" s="6" t="str">
-        <x:v>120</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="D8" s="6" t="str"/>
-      <x:c r="E8" s="6" t="str"/>
-      <x:c r="F8" s="6" t="str"/>
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>225.4</x:v>
+      </x:c>
       <x:c r="G8" s="6" t="str">
-        <x:v>Mounting plate</x:v>
+        <x:v>Direct mounting plate</x:v>
       </x:c>
       <x:c r="H8" s="6" t="str">
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I8" s="6" t="str">
-        <x:v>VFD heat zone</x:v>
+        <x:v>Mains / drive heat</x:v>
       </x:c>
       <x:c r="J8" s="6" t="str">
-        <x:v>100</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K8" s="6" t="str">
         <x:v>100</x:v>
       </x:c>
       <x:c r="L8" s="6" t="str">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="6" t="str">
-        <x:v>TBD</x:v>
+        <x:v>38.6</x:v>
       </x:c>
       <x:c r="N8" s="6" t="str">
-        <x:v>OPEN - exact selected-device envelope unavailable</x:v>
+        <x:v>Siemens order-number data sheet: 73 W x 196 H x 225.4 D mm; FSA PN</x:v>
       </x:c>
       <x:c r="O8" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED ENVELOPE; drive rating/duty and Startdrive configuration remain provisional</x:v>
       </x:c>
       <x:c r="P8" s="6" t="str">
         <x:v>=FC01+CP01-U100</x:v>
@@ -19010,40 +19052,46 @@
         <x:v>-U101</x:v>
       </x:c>
       <x:c r="B9" s="6" t="str">
-        <x:v>370</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>430</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="str"/>
-      <x:c r="E9" s="6" t="str"/>
-      <x:c r="F9" s="6" t="str"/>
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>225.4</x:v>
+      </x:c>
       <x:c r="G9" s="6" t="str">
-        <x:v>Mounting plate</x:v>
+        <x:v>Direct mounting plate</x:v>
       </x:c>
       <x:c r="H9" s="6" t="str">
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I9" s="6" t="str">
-        <x:v>VFD heat zone</x:v>
+        <x:v>Mains / drive heat</x:v>
       </x:c>
       <x:c r="J9" s="6" t="str">
-        <x:v>100</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="K9" s="6" t="str">
         <x:v>100</x:v>
       </x:c>
       <x:c r="L9" s="6" t="str">
-        <x:v>50</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="6" t="str">
-        <x:v>TBD</x:v>
+        <x:v>38.6</x:v>
       </x:c>
       <x:c r="N9" s="6" t="str">
-        <x:v>OPEN - exact selected-device envelope unavailable</x:v>
+        <x:v>Siemens order-number data sheet: 73 W x 196 H x 225.4 D mm; FSA PN</x:v>
       </x:c>
       <x:c r="O9" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED ENVELOPE; drive rating/duty and Startdrive configuration remain provisional</x:v>
       </x:c>
       <x:c r="P9" s="6" t="str">
         <x:v>=FC01+CP01-U101</x:v>
@@ -19054,10 +19102,10 @@
         <x:v>-SW100</x:v>
       </x:c>
       <x:c r="B10" s="6" t="str">
-        <x:v>450</x:v>
+        <x:v>505</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
-        <x:v>90</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>60</x:v>
@@ -19084,16 +19132,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L10" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M10" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N10" s="6" t="str">
-        <x:v>Official Siemens data sheet</x:v>
+        <x:v>Official Siemens technical data; controlled 5 mm lateral layout-clearance assumption; confirm against order-number installation data</x:v>
       </x:c>
       <x:c r="O10" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED NETWORK BASELINE — native configuration and site policy open</x:v>
       </x:c>
       <x:c r="P10" s="6" t="str">
         <x:v>=FC01+CP01-SW100</x:v>
@@ -19104,12 +19152,14 @@
         <x:v>-FW100</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>540</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="str"/>
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>35</x:v>
+      </x:c>
       <x:c r="E11" s="6" t="str">
         <x:v>147</x:v>
       </x:c>
@@ -19132,16 +19182,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L11" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M11" s="6" t="str">
-        <x:v>Manufacturer data required</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N11" s="6" t="str">
-        <x:v>OPEN - exact selected-device envelope unavailable</x:v>
+        <x:v>Siemens S615/S615 EEC operating instructions; variant CAx confirmation open; controlled 5 mm lateral layout-clearance assumption; confirm against order-number installation data</x:v>
       </x:c>
       <x:c r="O11" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>SELECTED NETWORK BASELINE — native configuration and site policy open</x:v>
       </x:c>
       <x:c r="P11" s="6" t="str">
         <x:v>=FC01+CP01-FW100</x:v>
@@ -19152,14 +19202,20 @@
         <x:v>-PC200</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>600</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
-        <x:v>250</x:v>
-      </x:c>
-      <x:c r="D12" s="6" t="str"/>
-      <x:c r="E12" s="6" t="str"/>
-      <x:c r="F12" s="6" t="str"/>
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>80</x:v>
+      </x:c>
       <x:c r="G12" s="6" t="str">
         <x:v>DIN rail / shelf</x:v>
       </x:c>
@@ -19167,7 +19223,7 @@
         <x:v>Vertical unless manufacturer requires otherwise</x:v>
       </x:c>
       <x:c r="I12" s="6" t="str">
-        <x:v>Vision</x:v>
+        <x:v>Vision edge</x:v>
       </x:c>
       <x:c r="J12" s="6" t="str">
         <x:v>25</x:v>
@@ -19176,16 +19232,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="L12" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="M12" s="6" t="str">
         <x:v>TBD</x:v>
       </x:c>
       <x:c r="N12" s="6" t="str">
-        <x:v>OPEN - exact selected-device envelope unavailable</x:v>
+        <x:v>CONTROLLED ARCHITECTURE-ONLY ENVELOPE ASSUMPTION — carrier, cooling kit and interfaces not selected</x:v>
       </x:c>
       <x:c r="O12" s="6" t="str">
-        <x:v>Coordinate reserved; native CAD and clearance verification open</x:v>
+        <x:v>TBD — NOT PROCUREMENT OR CONSTRUCTION DATA; confirm industrial carrier, thermal solution, EMC and lifecycle</x:v>
       </x:c>
       <x:c r="P12" s="6" t="str">
         <x:v>=FC01+CP01-PC200</x:v>
@@ -19196,19 +19252,19 @@
         <x:v>-PE100</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>120</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>755</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>630</x:v>
+        <x:v>640</x:v>
       </x:c>
       <x:c r="E13" s="6" t="str">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F13" s="6" t="str">
-        <x:v>25</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="6" t="str">
         <x:v>Mounting plate</x:v>
@@ -19220,22 +19276,22 @@
         <x:v>PE</x:v>
       </x:c>
       <x:c r="J13" s="6" t="str">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K13" s="6" t="str">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L13" s="6" t="str">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="6" t="str">
-        <x:v>0</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N13" s="6" t="str">
-        <x:v>Provisional bar envelope</x:v>
+        <x:v>Controlled provisional bar envelope; section and fixing hardware open</x:v>
       </x:c>
       <x:c r="O13" s="6" t="str">
-        <x:v>Final PE sizing open</x:v>
+        <x:v>TBD — PE sizing, bonding points and fault-current basis required</x:v>
       </x:c>
       <x:c r="P13" s="6" t="str">
         <x:v>=FC01+CP01-PE100</x:v>
@@ -19246,19 +19302,19 @@
         <x:v>-X100..-X199</x:v>
       </x:c>
       <x:c r="B14" s="6" t="str">
-        <x:v>120</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
-        <x:v>650</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>630</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="E14" s="6" t="str">
         <x:v>50</x:v>
       </x:c>
       <x:c r="F14" s="6" t="str">
-        <x:v>70</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G14" s="6" t="str">
         <x:v>DIN rail R4</x:v>
@@ -19270,22 +19326,22 @@
         <x:v>Field termination</x:v>
       </x:c>
       <x:c r="J14" s="6" t="str">
-        <x:v>40</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K14" s="6" t="str">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="L14" s="6" t="str">
-        <x:v>20</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="6" t="str">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N14" s="6" t="str">
-        <x:v>Reserved terminal-row envelope</x:v>
+        <x:v>Revision-E native schedule: 84 logical terminals plus controlled PE/shield terminal objects</x:v>
       </x:c>
       <x:c r="O14" s="6" t="str">
-        <x:v>Terminal family and count open</x:v>
+        <x:v>NATIVE GEOMETRY VERIFIED; terminal family, bridges, accessories and construction release remain open</x:v>
       </x:c>
       <x:c r="P14" s="6" t="str">
         <x:v>=FC01+CP01-X100..-X199</x:v>
@@ -19296,19 +19352,19 @@
         <x:v>-WD100</x:v>
       </x:c>
       <x:c r="B15" s="6" t="str">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C15" s="6" t="str">
-        <x:v>50</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>40</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E15" s="6" t="str">
-        <x:v>540</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="F15" s="6" t="str">
-        <x:v>60</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G15" s="6" t="str">
         <x:v>Mounting plate</x:v>
@@ -19317,7 +19373,7 @@
         <x:v>Vertical duct</x:v>
       </x:c>
       <x:c r="I15" s="6" t="str">
-        <x:v>24 VDC routing</x:v>
+        <x:v>Routing</x:v>
       </x:c>
       <x:c r="J15" s="6" t="str">
         <x:v>0</x:v>
@@ -19326,16 +19382,16 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="L15" s="6" t="str">
-        <x:v>15</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="6" t="str">
-        <x:v>0</x:v>
+        <x:v>TBD</x:v>
       </x:c>
       <x:c r="N15" s="6" t="str">
-        <x:v>Provisional routing reserve</x:v>
+        <x:v>Controlled routing envelope; duct family and fill calculation open</x:v>
       </x:c>
       <x:c r="O15" s="6" t="str">
-        <x:v>Duct fill calculation open</x:v>
+        <x:v>PROVISIONAL — VERIFY DUCT FILL, bend radius, conductor count and EMC separation</x:v>
       </x:c>
       <x:c r="P15" s="6" t="str">
         <x:v>=FC01+CP01-WD100</x:v>
@@ -19888,7 +19944,7 @@
         <x:v>TC-001..TC-032</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>32 scenario traces and 20 unit/property tests</x:v>
+        <x:v>32 deterministic scenarios plus 88 source/simulator/native-contract tests, 59 edge-service tests and 15 interface-harness tests; see the executed report</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
@@ -19911,7 +19967,7 @@
         <x:v>VAL-D-STATIC</x:v>
       </x:c>
       <x:c r="G24" s="6" t="str">
-        <x:v>Revision-D.1 canonical/source/schedule validation suite; the executed report records the current check count</x:v>
+        <x:v>Revision-E canonical/source/schedule/native-evidence validator; the executed report records the exact current check count</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="54" customHeight="1">
@@ -21103,22 +21159,22 @@
         <x:v>IR-019</x:v>
       </x:c>
       <x:c r="B20" s="6" t="str">
-        <x:v>FreeCAD installation and qualified panel-CAD reviewer</x:v>
+        <x:v>Qualified panel-CAD reviewer, final vendor envelopes/clearances and construction confirmation</x:v>
       </x:c>
       <x:c r="C20" s="6" t="str">
         <x:v>Electrical owner</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Revision-D.1 FCStd/exchange validation</x:v>
+        <x:v>Construction release of Revision-E native panel CAD</x:v>
       </x:c>
       <x:c r="E20" s="6" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="F20" s="6" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="G20" s="6" t="str">
-        <x:v>Approved source document or native evidence</x:v>
+        <x:v>Qualified-human review plus approved vendor/site construction data</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
@@ -21149,22 +21205,22 @@
         <x:v>IR-021</x:v>
       </x:c>
       <x:c r="B22" s="6" t="str">
-        <x:v>Usable QElectroTech installation and qualified electrical schematic reviewer</x:v>
+        <x:v>Native reopen/export/all-page review of corrected QET and qualified electrical schematic reviewer</x:v>
       </x:c>
       <x:c r="C22" s="6" t="str">
         <x:v>Electrical owner</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
-        <x:v>Revision-D.1 schematic authoring, reopen, export and review</x:v>
+        <x:v>Native schematic gate and construction review</x:v>
       </x:c>
       <x:c r="E22" s="6" t="str">
-        <x:v>OPEN</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="F22" s="6" t="str">
         <x:v>2026-08-02</x:v>
       </x:c>
       <x:c r="G22" s="6" t="str">
-        <x:v>Approved source document or native evidence</x:v>
+        <x:v>Exact corrected-hash QET reopen, PDF export, cross-reference report and qualified-human review</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
@@ -21348,7 +21404,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Controlled model and tests present; owner approval absent</x:v>
+        <x:v>Controlled model, native-workstream schedules and tests are traceable; identified requirements-owner approval is absent</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="54" customHeight="1">
@@ -21362,7 +21418,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Revision-D.1 deterministic validator and source-parity checks pass; see current automated report for count</x:v>
+        <x:v>Revision-E deterministic validator and source/schedule/native-evidence contracts pass; see current automated report for exact count</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
@@ -21376,7 +21432,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>V20/FW4.0 design baseline documented; native catalog and delivered state open</x:v>
+        <x:v>V20/FW4.0 source baseline and selected envelopes documented; authorized native catalog confirmation and delivered-state evidence remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -21390,7 +21446,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>No genuine AP20 project created</x:v>
+        <x:v>No genuine AP20 project; active identity is not TIA Engineer/Openness-authorized and V20 entitlement is unproven</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
@@ -21404,7 +21460,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>No genuine ZAP20 archive created</x:v>
+        <x:v>No genuine ZAP20 archive exists; native authorized project creation/restoration was not available</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
@@ -21418,7 +21474,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>Static source lint only; native compile not run</x:v>
+        <x:v>67 source/simulator contracts pass at Revision-E authoring time; TIA V20 compile was not run</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
@@ -21432,7 +21488,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>WinCC project not created</x:v>
+        <x:v>WinCC V20 components exist but no authorized/licensed native HMI project or compile is proven</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
@@ -21446,7 +21502,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Startdrive not installed and motor data absent</x:v>
+        <x:v>Startdrive is not installed; motor, pump and site inputs are also missing</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
@@ -21460,7 +21516,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>PLCSIM not installed; Python simulator is independent evidence</x:v>
+        <x:v>PLCSIM/PLCSIM Advanced are not installed; deterministic Python evidence is explicitly independent</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
@@ -21468,13 +21524,13 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B11" s="6" t="str">
-        <x:v>Revision-D.1 QET reopens and reconciles</x:v>
+        <x:v>Revision-E QET reopens and reconciles</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>No runnable QElectroTech found; historical revision-A native baseline only</x:v>
+        <x:v>Corrected 26-folio QET source BCA022BE0B9F65AA061F9731C1EE0BD0399947F04C94EE596D4AD231BB47AAD5 passes 24/24 static and 6/6 contract checks; exact corrected hash was not natively reopened/exported, so native reconciliation remains partial</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
@@ -21482,13 +21538,13 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B12" s="6" t="str">
-        <x:v>Schematics visual review</x:v>
+        <x:v>Schematics export and all-page visual review</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>Revision-D.1 native schematics do not exist</x:v>
+        <x:v>Native QET PDF export was not completed and only sampled folios were inspected; all-page visual and native cross-reference review remain blocked</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
@@ -21496,13 +21552,13 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B13" s="6" t="str">
-        <x:v>Revision-D.1 FCStd reopens</x:v>
+        <x:v>Revision-E FCStd reopens</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>No runnable FreeCAD found; historical baseline only</x:v>
+        <x:v>FreeCADCmd independently reopened 165 objects / 148 controlled solids; STEP retained 148 solids; IGES retained bounded face geometry; DXF entities and 30 scheduled holes reconciled</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
@@ -21513,10 +21569,10 @@
         <x:v>STEP/IGES/DXF reimport</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
-        <x:v>BLOCKED</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>Revision-D.1 exchange files do not exist and FreeCAD is absent</x:v>
+        <x:v>FreeCADCmd independently reopened 165 objects / 148 controlled solids; STEP retained 148 solids; IGES retained bounded face geometry; DXF entities and 30 scheduled holes reconciled</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
@@ -21530,7 +21586,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>Expanded controlled schedules; unresolved selections and native CAD remain open</x:v>
+        <x:v>Revision-E native layout covers selected architecture and controlled provisional envelopes; final carrier, terminal/relay families, vendor clearances, thermal and construction inputs remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
@@ -21544,7 +21600,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
-        <x:v>Site supply, fault current, loads and environmental inputs missing</x:v>
+        <x:v>Supply, earthing, fault current, motors/pump, cable routes, installation method, ambient and enclosure/site requirements remain unconfirmed</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
@@ -21558,7 +21614,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>No real dataset supplied</x:v>
+        <x:v>No representative labeled project dataset or golden/negative image sets were supplied</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
@@ -21572,7 +21628,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
-        <x:v>No dataset or TAO runtime</x:v>
+        <x:v>No controlled dataset, training run, evaluated model, ONNX export or defensible metrics exist</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
@@ -21586,7 +21642,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D19" s="6" t="str">
-        <x:v>No selected target carrier/runtime</x:v>
+        <x:v>No selected industrial Jetson carrier/runtime image; CUDA Toolkit, TensorRT, DeepStream and TAO are absent locally</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -21600,7 +21656,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Local source-design scope: simulator, 32 scenarios, edge service, interface harness and Revision-D.1 independent interface-oracle tests pass; native integration remains blocked under gates 9 and 18</x:v>
+        <x:v>Source/simulator, edge-service, interface-harness and real asyncua encrypted server/client integration tests pass; production PLC/Jetson endpoint validation remains outside this local gate</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
@@ -21614,7 +21670,7 @@
         <x:v>OPEN</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
-        <x:v>Procedures issued, never executed</x:v>
+        <x:v>Controlled procedures issued; no FAT, SAT or commissioning was executed</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
@@ -21628,7 +21684,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
-        <x:v>External qualified work required</x:v>
+        <x:v>Project-specific qualified machinery-safety engineering, verification and validation are external and not performed</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
@@ -21639,10 +21695,10 @@
         <x:v>Manifest independently verifies</x:v>
       </x:c>
       <x:c r="C23" s="6" t="str">
-        <x:v>PASS</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
-        <x:v>Final deterministic JSON/CSV verifier reports zero missing, unlisted or mismatched files on the frozen release tree; regenerate after any file change</x:v>
+        <x:v>Pre-publication source and generated-artifact controls are implemented; final staged/HEAD manifest, upstream alignment and pushed-commit fresh-clone verification remain pending until the candidate is committed and published</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -23855,6 +23911,306 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="30" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="22.5" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="31.5" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>document_id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>title</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>path</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>revision</x:v>
+      </x:c>
+      <x:c r="E1" s="12" t="str">
+        <x:v>owner</x:v>
+      </x:c>
+      <x:c r="F1" s="12" t="str">
+        <x:v>status</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="54" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>DOC-001</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Repository overview</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>README.md</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>Lead systems engineer</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="54" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>DOC-002</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Canonical model</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>00_project_control/canonical_model.json</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>Lead systems engineer</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>DOC-003</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>Functional design specification</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>13_documentation/functional_design_specification.md</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>Controls engineer</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>Controlled; native compile open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>DOC-004</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>Software design specification</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>13_documentation/software_design_specification.md</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>Controls engineer</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>Controlled; native compile open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>DOC-005</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>PLC-NVIDIA interface control</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>02_system_architecture/interface_control_document.md</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>Controls/vision</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>Controlled; production endpoint open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>DOC-006</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Panel design report</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>13_documentation/panel_design_report.md</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>Electrical/panel</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>Controlled assumptions; construction open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>DOC-007</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Electrical calculation report</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>13_documentation/electrical_calculation_report.md</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>Electrical</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>Provisional; site inputs open</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>DOC-008</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Acceptance gate status</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>14_qa/acceptance_gate_status.md</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>Independent V&amp;V</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>DOC-009</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>Engineering workbook</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>10_schedules/FC01_engineering_schedules.xlsx</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>Lead systems engineer</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>Controlled generated artifact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>DOC-010</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>Release evidence PDF</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>release/FC01_release_evidence.pdf</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>Lead systems engineer</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>Controlled generated artifact</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>DOC-011</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Release manifest</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>release/manifest.json</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>Configuration management</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>Frozen after all content</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>DOC-012</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>Native panel verification</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>09_panel_cad/revision_e/native_verification.json</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>Panel engineer</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>Native gate evidence</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>DOC-013</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>Native QET verification</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>03_electrical/revision_e/native_verification.json</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>Electrical engineer</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>Native gate evidence when present</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="32.5" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="16.25" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="13.75" hidden="0" customWidth="1"/>
@@ -23866,7 +24222,7 @@
   <x:sheetData>
     <x:row r="1">
       <x:c r="A1" s="18" t="str">
-        <x:v>FC01 — SIEMENS / NVIDIA ENGINEERING SCHEDULES</x:v>
+        <x:v>FC01 - SIEMENS / NVIDIA ENGINEERING SCHEDULES</x:v>
       </x:c>
       <x:c r="B1" s="18"/>
       <x:c r="C1" s="18"/>
@@ -23888,7 +24244,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="24" t="str">
-        <x:v>FICTIONAL ENGINEERING PROJECT — NOT FOR CONSTRUCTION | Revision D.1 | Professional controlled engineering-development release candidate</x:v>
+        <x:v>FICTIONAL ENGINEERING PROJECT - NOT FOR CONSTRUCTION | Revision E | Controlled native-engineering release candidate</x:v>
       </x:c>
       <x:c r="B3" s="24"/>
       <x:c r="C3" s="24"/>
@@ -23900,7 +24256,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="30" t="str">
-        <x:v>CONCEPTUAL SAFETY ARCHITECTURE — REQUIRES PROJECT-SPECIFIC RISK ASSESSMENT, DESIGN, VERIFICATION AND VALIDATION BY A QUALIFIED MACHINERY-SAFETY ENGINEER. NO PERFORMANCE LEVEL, SIL, CATEGORY, CE CONFORMITY OR REGULATORY COMPLIANCE IS CLAIMED.</x:v>
+        <x:v>CONCEPTUAL SAFETY ARCHITECTURE - REQUIRES PROJECT-SPECIFIC RISK ASSESSMENT, DESIGN, VERIFICATION AND VALIDATION BY A QUALIFIED MACHINERY-SAFETY ENGINEER. NO PERFORMANCE LEVEL, SIL, CATEGORY, CE CONFORMITY OR REGULATORY COMPLIANCE IS CLAIMED.</x:v>
       </x:c>
       <x:c r="B4" s="30"/>
       <x:c r="C4" s="30"/>
@@ -23934,7 +24290,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="D6" s="46" t="str">
-        <x:v>Native TIA/WinCC/Startdrive/PLCSIM, trained NVIDIA model, Revision-D.1 QElectroTech and Revision-D.1 panel CAD remain blocked. Historical native electrical/CAD files are byte-exact quarantined baselines. No construction, safety, native compile, FAT, SAT or model-performance claim is made.</x:v>
+        <x:v>Revision E includes source-tested poll-safe PLC/AI logic, secure asyncua integration and separately controlled native CAD/QET evidence. Native TIA/WinCC/Startdrive/PLCSIM, final site electrical design, trained NVIDIA model, target runtime, FAT/SAT, qualified safety and physical commissioning remain blocked or open exactly as listed. No construction, safety, native compile or model-performance claim is made.</x:v>
       </x:c>
       <x:c r="E6" s="46"/>
       <x:c r="F6" s="46"/>
@@ -24013,7 +24369,7 @@
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="36" t="str">
-        <x:v>Controlled tests</x:v>
+        <x:v>Traceability test records</x:v>
       </x:c>
       <x:c r="B12" t="n">
         <x:f>COUNTA('Test Coverage'!A2:A100)</x:f>
@@ -24027,11 +24383,11 @@
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="36" t="str">
-        <x:v>Open/blocked gates</x:v>
+        <x:v>PASS gates</x:v>
       </x:c>
       <x:c r="B13" t="n">
-        <x:f>COUNTIF('Acceptance Gates'!C2:C100,"BLOCKED")+COUNTIF('Acceptance Gates'!C2:C100,"OPEN")</x:f>
-        <x:v>16</x:v>
+        <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PASS")</x:f>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D13" s="46"/>
       <x:c r="E13" s="46"/>
@@ -24041,18 +24397,46 @@
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="36" t="str">
+        <x:v>PARTIAL gates</x:v>
+      </x:c>
+      <x:c r="B14" t="n">
+        <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PARTIAL")</x:f>
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="D14" s="46"/>
+      <x:c r="E14" s="46"/>
+      <x:c r="F14" s="46"/>
+      <x:c r="G14" s="46"/>
+      <x:c r="H14" s="46"/>
+    </x:row>
+    <x:row r="15">
+      <x:c r="A15" s="36" t="str">
+        <x:v>BLOCKED + OPEN gates</x:v>
+      </x:c>
+      <x:c r="B15" t="n">
+        <x:f>COUNTIF('Acceptance Gates'!C2:C100,"BLOCKED")+COUNTIF('Acceptance Gates'!C2:C100,"OPEN")</x:f>
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="D15" s="46"/>
+      <x:c r="E15" s="46"/>
+      <x:c r="F15" s="46"/>
+      <x:c r="G15" s="46"/>
+      <x:c r="H15" s="46"/>
+    </x:row>
+    <x:row r="16">
+      <x:c r="A16" s="36" t="str">
         <x:v>24 VDC demand (W)</x:v>
       </x:c>
-      <x:c r="B14" t="n">
+      <x:c r="B16" t="n">
         <x:f>55+24+120+100</x:f>
         <x:v>299</x:v>
       </x:c>
     </x:row>
-    <x:row r="15">
-      <x:c r="A15" s="36" t="str">
+    <x:row r="17">
+      <x:c r="A17" s="36" t="str">
         <x:v>Minimum current for 25% margin (A)</x:v>
       </x:c>
-      <x:c r="B15" t="n">
+      <x:c r="B17" t="n">
         <x:f>(55+24+120+100)/24*1.25</x:f>
         <x:v>15.572916666666668</x:v>
       </x:c>
@@ -24063,7 +24447,7 @@
     <x:mergeCell ref="A3:H3"/>
     <x:mergeCell ref="A4:H4"/>
     <x:mergeCell ref="D5:H5"/>
-    <x:mergeCell ref="D6:H13"/>
+    <x:mergeCell ref="D6:H15"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
@@ -27246,10 +27630,10 @@
         <x:v>PLC</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>One-shot request</x:v>
+        <x:v>Level-held inspection request; remains true until coherent BUSY observation or terminal result for the immutable session/inspection ID</x:v>
       </x:c>
       <x:c r="E3" s="6" t="str">
-        <x:v>OPC UA subscribed/published node</x:v>
+        <x:v>OPC UA subscribed request level; monotonic session/ID is authoritative</x:v>
       </x:c>
       <x:c r="F3" s="6" t="str">
         <x:v>0</x:v>

--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -463,8 +463,8 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="DocumentRegisterTable" displayName="DocumentRegisterTable" ref="A1:F14" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="DocumentRegisterTable" displayName="DocumentRegisterTable" ref="A1:F15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F15"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="document_id"/>
     <x:tableColumn id="2" name="title"/>
@@ -21695,10 +21695,10 @@
         <x:v>Manifest independently verifies</x:v>
       </x:c>
       <x:c r="C23" s="6" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
-        <x:v>Pre-publication source and generated-artifact controls are implemented; final staged/HEAD manifest, upstream alignment and pushed-commit fresh-clone verification remain pending until the candidate is committed and published</x:v>
+        <x:v>Published candidate b9633c6255fe34e48a1be34afe5024935f48651e was cloned afresh from GitHub outside OneDrive and passed the complete HEAD workflow: manifest 310/310 with zero discrepancies, integrity 534/534, validator 551/551, all tests/native checks, deterministic artifacts and clean state</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -24199,6 +24199,26 @@
         <x:v>Native gate evidence when present</x:v>
       </x:c>
     </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>DOC-014</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>Post-push fresh-clone reproduction</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>14_qa/post_push_reproduction.md</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>E</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
+        <x:v>Configuration management</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>Published-candidate release-integrity evidence</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
@@ -24387,7 +24407,7 @@
       </x:c>
       <x:c r="B13" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PASS")</x:f>
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D13" s="46"/>
       <x:c r="E13" s="46"/>
@@ -24401,7 +24421,7 @@
       </x:c>
       <x:c r="B14" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PARTIAL")</x:f>
-        <x:v>5</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D14" s="46"/>
       <x:c r="E14" s="46"/>

--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -27974,7 +27974,7 @@
         <x:v>TC-001..TC-032</x:v>
       </x:c>
       <x:c r="G23" s="6" t="str">
-        <x:v>32 deterministic process scenarios plus 99 source/simulator/native-contract tests, 28 deterministic vision-fault scenarios, 85 edge-service tests and 17 interface-harness tests; see the executed report</x:v>
+        <x:v>32 deterministic process scenarios plus 99 source/simulator/native-contract tests, 28 deterministic vision-fault scenarios, 86 edge-service tests and 17 interface-harness tests; see the executed report</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="54" customHeight="1">
@@ -28054,7 +28054,7 @@
         <x:v>Keep NVIDIA non-safety and unable to command actuators or bypass PLC interlocks</x:v>
       </x:c>
       <x:c r="C27" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D27" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28077,7 +28077,7 @@
         <x:v>Support camera, recorded-directory and explicitly synthetic non-production acquisition adapters</x:v>
       </x:c>
       <x:c r="C28" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D28" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28100,7 +28100,7 @@
         <x:v>Validate versioned configuration schema, reject unknown keys and publish configuration hashes</x:v>
       </x:c>
       <x:c r="C29" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D29" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28123,7 +28123,7 @@
         <x:v>Correlate capture acknowledgement and processing state to the immutable inspection identity</x:v>
       </x:c>
       <x:c r="C30" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D30" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28146,7 +28146,7 @@
         <x:v>Publish explicit PASS HOLD FAIL or FAULT disposition with structured reason bits</x:v>
       </x:c>
       <x:c r="C31" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D31" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28169,7 +28169,7 @@
         <x:v>Bind model, dataset and calibration identities to each accepted result</x:v>
       </x:c>
       <x:c r="C32" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D32" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28192,7 +28192,7 @@
         <x:v>Provide diagnostic UTC timestamps while retaining PLC monotonic timing as acceptance authority</x:v>
       </x:c>
       <x:c r="C33" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D33" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28215,7 +28215,7 @@
         <x:v>Expose service, camera, model, maintenance, queue and diagnostic health</x:v>
       </x:c>
       <x:c r="C34" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D34" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28238,7 +28238,7 @@
         <x:v>Fail closed when durable inspection audit records cannot be written</x:v>
       </x:c>
       <x:c r="C35" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D35" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28261,7 +28261,7 @@
         <x:v>Version and hash dataset records and split by production lot to prevent leakage</x:v>
       </x:c>
       <x:c r="C36" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D36" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28284,7 +28284,7 @@
         <x:v>Provide reproducible evaluation, FAR/FRR, threshold and latency tooling without fabricated results</x:v>
       </x:c>
       <x:c r="C37" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D37" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28307,7 +28307,7 @@
         <x:v>Define optical resolution, exposure, motion-blur, glare, focus and calibration acceptance methods</x:v>
       </x:c>
       <x:c r="C38" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D38" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28330,7 +28330,7 @@
         <x:v>Apply least-privilege certificate-based OPC UA across the controlled quality zone</x:v>
       </x:c>
       <x:c r="C39" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D39" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28353,7 +28353,7 @@
         <x:v>Retain bounded deployment rollback and independent model/configuration/calibration identities</x:v>
       </x:c>
       <x:c r="C40" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D40" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28376,7 +28376,7 @@
         <x:v>Do not retain raw production images by default and require an approved retention/privacy policy</x:v>
       </x:c>
       <x:c r="C41" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D41" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28399,7 +28399,7 @@
         <x:v>Reserve separately protected edge, camera, lighting and maintenance electrical branches</x:v>
       </x:c>
       <x:c r="C42" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D42" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28422,7 +28422,7 @@
         <x:v>Reject queue saturation, concurrent transaction reuse and results for unknown IDs</x:v>
       </x:c>
       <x:c r="C43" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D43" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28445,7 +28445,7 @@
         <x:v>Invalidate an active inspection on recipe change or unacceptable clock discontinuity</x:v>
       </x:c>
       <x:c r="C44" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D44" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28468,7 +28468,7 @@
         <x:v>Require explicit recovery and a new start following PLC or edge restart</x:v>
       </x:c>
       <x:c r="C45" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D45" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -28491,7 +28491,7 @@
         <x:v>Keep flow and level instrumentation as the primary deterministic filling measurement</x:v>
       </x:c>
       <x:c r="C46" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D46" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -31631,7 +31631,7 @@
         <x:v>Verification</x:v>
       </x:c>
       <x:c r="F19" s="6" t="str">
-        <x:v>Software-in-the-loop</x:v>
+        <x:v>Structured behavioral fault-injection model</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -31691,7 +31691,7 @@
         <x:v>Verification</x:v>
       </x:c>
       <x:c r="F22" s="6" t="str">
-        <x:v>Issued; SIL executed only</x:v>
+        <x:v>Issued; software-only behavioral fault injection executed</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
@@ -36866,7 +36866,7 @@
         <x:v>Keep NVIDIA non-safety and unable to command actuators or bypass PLC interlocks</x:v>
       </x:c>
       <x:c r="C2" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -36889,7 +36889,7 @@
         <x:v>Support camera, recorded-directory and explicitly synthetic non-production acquisition adapters</x:v>
       </x:c>
       <x:c r="C3" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -36912,7 +36912,7 @@
         <x:v>Validate versioned configuration schema, reject unknown keys and publish configuration hashes</x:v>
       </x:c>
       <x:c r="C4" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -36935,7 +36935,7 @@
         <x:v>Correlate capture acknowledgement and processing state to the immutable inspection identity</x:v>
       </x:c>
       <x:c r="C5" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -36958,7 +36958,7 @@
         <x:v>Publish explicit PASS HOLD FAIL or FAULT disposition with structured reason bits</x:v>
       </x:c>
       <x:c r="C6" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -36981,7 +36981,7 @@
         <x:v>Bind model, dataset and calibration identities to each accepted result</x:v>
       </x:c>
       <x:c r="C7" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37004,7 +37004,7 @@
         <x:v>Provide diagnostic UTC timestamps while retaining PLC monotonic timing as acceptance authority</x:v>
       </x:c>
       <x:c r="C8" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37027,7 +37027,7 @@
         <x:v>Expose service, camera, model, maintenance, queue and diagnostic health</x:v>
       </x:c>
       <x:c r="C9" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37050,7 +37050,7 @@
         <x:v>Fail closed when durable inspection audit records cannot be written</x:v>
       </x:c>
       <x:c r="C10" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37073,7 +37073,7 @@
         <x:v>Version and hash dataset records and split by production lot to prevent leakage</x:v>
       </x:c>
       <x:c r="C11" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37096,7 +37096,7 @@
         <x:v>Provide reproducible evaluation, FAR/FRR, threshold and latency tooling without fabricated results</x:v>
       </x:c>
       <x:c r="C12" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37119,7 +37119,7 @@
         <x:v>Define optical resolution, exposure, motion-blur, glare, focus and calibration acceptance methods</x:v>
       </x:c>
       <x:c r="C13" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37142,7 +37142,7 @@
         <x:v>Apply least-privilege certificate-based OPC UA across the controlled quality zone</x:v>
       </x:c>
       <x:c r="C14" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37165,7 +37165,7 @@
         <x:v>Retain bounded deployment rollback and independent model/configuration/calibration identities</x:v>
       </x:c>
       <x:c r="C15" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37188,7 +37188,7 @@
         <x:v>Do not retain raw production images by default and require an approved retention/privacy policy</x:v>
       </x:c>
       <x:c r="C16" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37211,7 +37211,7 @@
         <x:v>Reserve separately protected edge, camera, lighting and maintenance electrical branches</x:v>
       </x:c>
       <x:c r="C17" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37234,7 +37234,7 @@
         <x:v>Reject queue saturation, concurrent transaction reuse and results for unknown IDs</x:v>
       </x:c>
       <x:c r="C18" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37257,7 +37257,7 @@
         <x:v>Invalidate an active inspection on recipe change or unacceptable clock discontinuity</x:v>
       </x:c>
       <x:c r="C19" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D19" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37280,7 +37280,7 @@
         <x:v>Require explicit recovery and a new start following PLC or edge restart</x:v>
       </x:c>
       <x:c r="C20" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>
@@ -37303,7 +37303,7 @@
         <x:v>Keep flow and level instrumentation as the primary deterministic filling measurement</x:v>
       </x:c>
       <x:c r="C21" s="6" t="str">
-        <x:v>Review plus deterministic source/SIL tests where applicable</x:v>
+        <x:v>Review plus deterministic source tests and structured behavioral fault injection where applicable</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
         <x:v>Implemented locally where possible; external native/data/hardware acceptance remains explicit</x:v>

--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -31228,10 +31228,10 @@
         <x:v>Manifest independently verifies</x:v>
       </x:c>
       <x:c r="C23" s="6" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
-        <x:v>Manifest and clean-clone release-integrity gate closes only after the final Revision-F commit is pushed and reproduced</x:v>
+        <x:v>Published candidate f6e9f3b1e928a2e04d21913caac2547469b0f647 reproduced from GitHub with 425/425 manifest entries, zero discrepancies and final Git-clean assertion</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -32082,7 +32082,7 @@
       </x:c>
       <x:c r="B13" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PASS")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="46"/>
       <x:c r="E13" s="46"/>
@@ -32096,7 +32096,7 @@
       </x:c>
       <x:c r="B14" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PARTIAL")</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="46"/>
       <x:c r="E14" s="46"/>

--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -14,20 +14,21 @@
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA Electrical" sheetId="10" r:id="rId13"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NVIDIA Versions" sheetId="11" r:id="rId14"/>
     <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revision-F Gaps" sheetId="12" r:id="rId15"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Nodes" sheetId="13" r:id="rId16"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Terminal Plan" sheetId="14" r:id="rId17"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Point-to-Point" sheetId="15" r:id="rId18"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cable Schedule" sheetId="16" r:id="rId19"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire List" sheetId="17" r:id="rId20"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="18" r:id="rId21"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Budget" sheetId="19" r:id="rId22"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel Placement" sheetId="20" r:id="rId23"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements Trace" sheetId="21" r:id="rId24"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Coverage" sheetId="22" r:id="rId25"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Requests" sheetId="23" r:id="rId26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Gates" sheetId="24" r:id="rId27"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document Register" sheetId="25" r:id="rId28"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="26" r:id="rId29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Revision-G Gates" sheetId="13" r:id="rId16"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Network Nodes" sheetId="14" r:id="rId17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Terminal Plan" sheetId="15" r:id="rId18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Point-to-Point" sheetId="16" r:id="rId19"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cable Schedule" sheetId="17" r:id="rId20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Wire List" sheetId="18" r:id="rId21"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BOM" sheetId="19" r:id="rId22"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Load Budget" sheetId="20" r:id="rId23"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Panel Placement" sheetId="21" r:id="rId24"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Requirements Trace" sheetId="22" r:id="rId25"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Test Coverage" sheetId="23" r:id="rId26"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Input Requests" sheetId="24" r:id="rId27"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acceptance Gates" sheetId="25" r:id="rId28"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Document Register" sheetId="26" r:id="rId29"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Release Summary" sheetId="27" r:id="rId30"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -300,7 +301,26 @@
 </file>
 
 <file path=xl/tables/table13.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="NetworkNodesTable" displayName="NetworkNodesTable" ref="A1:H8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="13" name="RevisionGGatesTable" displayName="RevisionGGatesTable" ref="A1:J15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:J15"/>
+  <x:tableColumns count="10">
+    <x:tableColumn id="1" name="gate_id"/>
+    <x:tableColumn id="2" name="requirement"/>
+    <x:tableColumn id="3" name="current_evidence"/>
+    <x:tableColumn id="4" name="current_status"/>
+    <x:tableColumn id="5" name="missing_input"/>
+    <x:tableColumn id="6" name="responsible_agent"/>
+    <x:tableColumn id="7" name="planned_action"/>
+    <x:tableColumn id="8" name="acceptance_evidence"/>
+    <x:tableColumn id="9" name="external_dependency"/>
+    <x:tableColumn id="10" name="final_disposition"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="NetworkNodesTable" displayName="NetworkNodesTable" ref="A1:H8" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:H8"/>
   <x:tableColumns count="8">
     <x:tableColumn id="1" name="node"/>
@@ -316,8 +336,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table14.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="14" name="TerminalPlanTable" displayName="TerminalPlanTable" ref="A1:Q85" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="TerminalPlanTable" displayName="TerminalPlanTable" ref="A1:Q85" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:Q85"/>
   <x:tableColumns count="17">
     <x:tableColumn id="1" name="terminal"/>
@@ -342,8 +362,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table15.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="15" name="PointtoPointTable" displayName="PointtoPointTable" ref="A1:V119" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="PointtoPointTable" displayName="PointtoPointTable" ref="A1:V119" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:V119"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="signal"/>
@@ -373,8 +393,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table16.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="16" name="CableScheduleTable" displayName="CableScheduleTable" ref="A1:L23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="CableScheduleTable" displayName="CableScheduleTable" ref="A1:L23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:L23"/>
   <x:tableColumns count="12">
     <x:tableColumn id="1" name="cable_id"/>
@@ -394,8 +414,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table17.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="17" name="WireListTable" displayName="WireListTable" ref="A1:V119" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="WireListTable" displayName="WireListTable" ref="A1:V119" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:V119"/>
   <x:tableColumns count="22">
     <x:tableColumn id="1" name="signal"/>
@@ -425,8 +445,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table18.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="18" name="BOMTable" displayName="BOMTable" ref="A1:J63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="BOMTable" displayName="BOMTable" ref="A1:J63" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:J63"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="item"/>
@@ -439,21 +459,6 @@
     <x:tableColumn id="8" name="scope"/>
     <x:tableColumn id="9" name="basis_or_blocker"/>
     <x:tableColumn id="10" name="full_designation"/>
-  </x:tableColumns>
-  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</x:table>
-</file>
-
-<file path=xl/tables/table19.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="19" name="LoadBudgetTable" displayName="LoadBudgetTable" ref="A1:F11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F11"/>
-  <x:tableColumns count="6">
-    <x:tableColumn id="1" name="load"/>
-    <x:tableColumn id="2" name="voltage"/>
-    <x:tableColumn id="3" name="nominal_w"/>
-    <x:tableColumn id="4" name="demand_factor"/>
-    <x:tableColumn id="5" name="demand_w"/>
-    <x:tableColumn id="6" name="basis"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
@@ -478,7 +483,22 @@
 </file>
 
 <file path=xl/tables/table20.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="PanelPlacementTable" displayName="PanelPlacementTable" ref="A1:P15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="20" name="LoadBudgetTable" displayName="LoadBudgetTable" ref="A1:F11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F11"/>
+  <x:tableColumns count="6">
+    <x:tableColumn id="1" name="load"/>
+    <x:tableColumn id="2" name="voltage"/>
+    <x:tableColumn id="3" name="nominal_w"/>
+    <x:tableColumn id="4" name="demand_factor"/>
+    <x:tableColumn id="5" name="demand_w"/>
+    <x:tableColumn id="6" name="basis"/>
+  </x:tableColumns>
+  <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</x:table>
+</file>
+
+<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="PanelPlacementTable" displayName="PanelPlacementTable" ref="A1:P15" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:P15"/>
   <x:tableColumns count="16">
     <x:tableColumn id="1" name="tag"/>
@@ -502,8 +522,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table21.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="21" name="RequirementsTraceTable" displayName="RequirementsTraceTable" ref="A1:G46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="RequirementsTraceTable" displayName="RequirementsTraceTable" ref="A1:G46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G46"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="requirement_id"/>
@@ -518,8 +538,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table22.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="22" name="TestCoverageTable" displayName="TestCoverageTable" ref="A1:G73" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="TestCoverageTable" displayName="TestCoverageTable" ref="A1:G73" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G73"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="test_id"/>
@@ -534,8 +554,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table23.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="23" name="InputRequestsTable" displayName="InputRequestsTable" ref="A1:G29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="InputRequestsTable" displayName="InputRequestsTable" ref="A1:G29" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:G29"/>
   <x:tableColumns count="7">
     <x:tableColumn id="1" name="request_id"/>
@@ -550,8 +570,8 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table24.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="24" name="AcceptanceGatesTable" displayName="AcceptanceGatesTable" ref="A1:D23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="AcceptanceGatesTable" displayName="AcceptanceGatesTable" ref="A1:D23" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:D23"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="gate"/>
@@ -563,9 +583,9 @@
 </x:table>
 </file>
 
-<file path=xl/tables/table25.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="25" name="DocumentRegisterTable" displayName="DocumentRegisterTable" ref="A1:F32" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F32"/>
+<file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="DocumentRegisterTable" displayName="DocumentRegisterTable" ref="A1:F46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F46"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="document_id"/>
     <x:tableColumn id="2" name="title"/>
@@ -2579,6 +2599,510 @@
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
+    <x:col min="1" max="1" width="10.630000114440918" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="33.75" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="33.75" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="22.5" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="33.75" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="19.3799991607666" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="31.5" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>gate_id</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>requirement</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>current_evidence</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>current_status</x:v>
+      </x:c>
+      <x:c r="E1" s="12" t="str">
+        <x:v>missing_input</x:v>
+      </x:c>
+      <x:c r="F1" s="12" t="str">
+        <x:v>responsible_agent</x:v>
+      </x:c>
+      <x:c r="G1" s="12" t="str">
+        <x:v>planned_action</x:v>
+      </x:c>
+      <x:c r="H1" s="12" t="str">
+        <x:v>acceptance_evidence</x:v>
+      </x:c>
+      <x:c r="I1" s="12" t="str">
+        <x:v>external_dependency</x:v>
+      </x:c>
+      <x:c r="J1" s="12" t="str">
+        <x:v>final_disposition</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="54" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>G0-01</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>Reviewable two-environment Google Cloud architecture</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>cloud/architecture.md and cloud/terraform</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>VERIFIED</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>None for design</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>Cloud/DevSecOps workstream</x:v>
+      </x:c>
+      <x:c r="G2" s="6" t="str">
+        <x:v>Retain architecture under release control</x:v>
+      </x:c>
+      <x:c r="H2" s="6" t="str">
+        <x:v>Revision-G static security verification</x:v>
+      </x:c>
+      <x:c r="I2" s="6" t="str">
+        <x:v>None</x:v>
+      </x:c>
+      <x:c r="J2" s="6" t="str">
+        <x:v>VERIFIED - design only; no resources created</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="54" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>G0-02</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>Terraform format, native validate and non-destructive plan</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>Static HCL/security checks pass; Terraform CLI absent</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>BLOCKED BY EXTERNAL SYSTEM</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>Approved Terraform/OpenTofu CLI, Google project, billing identity and ADC</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>Cloud owner</x:v>
+      </x:c>
+      <x:c r="G3" s="6" t="str">
+        <x:v>Run cloud/scripts/plan_cloud.ps1 after consolidated approval</x:v>
+      </x:c>
+      <x:c r="H3" s="6" t="str">
+        <x:v>fmt/validate/plan logs and plan SHA-256</x:v>
+      </x:c>
+      <x:c r="I3" s="6" t="str">
+        <x:v>User cloud authorization and tool approval</x:v>
+      </x:c>
+      <x:c r="J3" s="6" t="str">
+        <x:v>BLOCKED - no plan or apply claimed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>G0-03</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>Cloud security, budget and shutdown controls</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>No external IPs, IAP-only ingress, separate service accounts, budgets, schedules and bucket controls encoded</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>IMPLEMENTABLE NOW</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>Project-specific IAM principals, billing account and reviewed budget</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>Cloud security owner</x:v>
+      </x:c>
+      <x:c r="G4" s="6" t="str">
+        <x:v>Parameterize and plan only after approval</x:v>
+      </x:c>
+      <x:c r="H4" s="6" t="str">
+        <x:v>Reviewed plan plus Security Command Center/IAM evidence after apply</x:v>
+      </x:c>
+      <x:c r="I4" s="6" t="str">
+        <x:v>Cloud project and billing access</x:v>
+      </x:c>
+      <x:c r="J4" s="6" t="str">
+        <x:v>DEPLOYABLE; NOT PROVISIONED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>G1-01</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>Authorized TIA Portal V20 native project and reopen</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>Portal executable 2000.0.9501.1 and Openness V20 assemblies installed; no genuine AP20</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>REQUIRES LICENCE</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>Valid STEP 7/WinCC licences and Siemens TIA Openness group membership</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>Licensed Siemens engineer</x:v>
+      </x:c>
+      <x:c r="G5" s="6" t="str">
+        <x:v>Execute siemens_native handoff and import controlled sources</x:v>
+      </x:c>
+      <x:c r="H5" s="6" t="str">
+        <x:v>Native AP20/ZAP20, reopen log and hashes</x:v>
+      </x:c>
+      <x:c r="I5" s="6" t="str">
+        <x:v>Licence, authorization and qualified operator</x:v>
+      </x:c>
+      <x:c r="J5" s="6" t="str">
+        <x:v>BLOCKED - no AP20/ZAP20 fabricated</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>G1-02</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>Native PLC, hardware and HMI compile</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>99 source/simulator contract tests; import-ready SCL/HMI tables</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>REQUIRES LICENCE</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>Authorized TIA session and catalog confirmation</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>Licensed Siemens engineer</x:v>
+      </x:c>
+      <x:c r="G6" s="6" t="str">
+        <x:v>Compile and disposition every warning</x:v>
+      </x:c>
+      <x:c r="H6" s="6" t="str">
+        <x:v>Raw native compile logs and screenshots</x:v>
+      </x:c>
+      <x:c r="I6" s="6" t="str">
+        <x:v>TIA licence/authorization</x:v>
+      </x:c>
+      <x:c r="J6" s="6" t="str">
+        <x:v>BLOCKED - source tests are not native compilation</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>G1-03</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>Startdrive and PLCSIM execution</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>Neither Startdrive nor PLCSIM is installed</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>REQUIRES LICENCE</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>Approved installers/licences plus motor and pump data</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>Drives/controls owner</x:v>
+      </x:c>
+      <x:c r="G7" s="6" t="str">
+        <x:v>Install through approved Siemens channel, configure, compile and simulate</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="str">
+        <x:v>Product inventory, native compile and PLCSIM traces</x:v>
+      </x:c>
+      <x:c r="I7" s="6" t="str">
+        <x:v>Software, licences and machine data</x:v>
+      </x:c>
+      <x:c r="J7" s="6" t="str">
+        <x:v>BLOCKED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>G2-01</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>Production-shaped fail-closed PLC-AI edge contract</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>47-node contract, encrypted asyncua integration and immutable ACK behavior; 86 edge and 17 harness tests</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>VERIFIED</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>Production S7/Jetson endpoint for deployment acceptance</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>NVIDIA/controls owners</x:v>
+      </x:c>
+      <x:c r="G8" s="6" t="str">
+        <x:v>Retain software contract and repeat on target</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="str">
+        <x:v>Automated unit/integration/fault evidence</x:v>
+      </x:c>
+      <x:c r="I8" s="6" t="str">
+        <x:v>Target endpoint for production validation</x:v>
+      </x:c>
+      <x:c r="J8" s="6" t="str">
+        <x:v>VERIFIED AS SOFTWARE-ONLY NON-SAFETY CONTRACT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>G2-02</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>Dataset provenance, taxonomy and split controls</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>Acquisition/labeling plans, empty controlled manifest and executable validation/split tooling</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>REQUIRES REAL DATA</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>Approved representative multi-lot images and annotations</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>Vision product owner</x:v>
+      </x:c>
+      <x:c r="G9" s="6" t="str">
+        <x:v>Collect and double-review approved real data</x:v>
+      </x:c>
+      <x:c r="H9" s="6" t="str">
+        <x:v>Hashed manifest, provenance, class balance, leakage/duplicate review</x:v>
+      </x:c>
+      <x:c r="I9" s="6" t="str">
+        <x:v>Real process samples, camera/lighting and data approval</x:v>
+      </x:c>
+      <x:c r="J9" s="6" t="str">
+        <x:v>PIPELINE READY; DATASET ABSENT</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>G2-03</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>Real TAO training, independent evaluation and deployment artifacts</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>Pinned configuration templates and synthetic fail-closed smoke only</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>REQUIRES REAL DATA</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>Approved dataset, Linux GPU runtime and selected architecture</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>Vision/MLOps owner</x:v>
+      </x:c>
+      <x:c r="G10" s="6" t="str">
+        <x:v>Train, evaluate, export ONNX and generate target TensorRT engine</x:v>
+      </x:c>
+      <x:c r="H10" s="6" t="str">
+        <x:v>Raw logs, held-out metrics, model card, artifact hashes and target latency</x:v>
+      </x:c>
+      <x:c r="I10" s="6" t="str">
+        <x:v>Dataset, GPU environment and model approval</x:v>
+      </x:c>
+      <x:c r="J10" s="6" t="str">
+        <x:v>BLOCKED - no model or metric claimed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>G2-04</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>DeepStream/TAO/TensorRT native runtime</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>RTX 5060 driver 595.95 is present; nvcc, Docker, TAO, TensorRT and DeepStream absent</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>REQUIRES USER APPROVAL</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>Approved Ubuntu 24.04/container runtime installation or cloud GPU plan</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>NVIDIA platform owner</x:v>
+      </x:c>
+      <x:c r="G11" s="6" t="str">
+        <x:v>Execute pinned environment runbook after approval</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="str">
+        <x:v>Native version logs, container digest, SBOM and measured smoke/latency logs</x:v>
+      </x:c>
+      <x:c r="I11" s="6" t="str">
+        <x:v>Installation approval, registry terms and runtime</x:v>
+      </x:c>
+      <x:c r="J11" s="6" t="str">
+        <x:v>BLOCKED - GPU inventory only</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="54" customHeight="1">
+      <x:c r="A12" s="6" t="str">
+        <x:v>G3A-01</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="str">
+        <x:v>Controlled commissioning procedures and blank records</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="str">
+        <x:v>commissioning directory contains FAT/SAT, inspection, calibration, I/O and safety-review templates</x:v>
+      </x:c>
+      <x:c r="D12" s="6" t="str">
+        <x:v>VERIFIED</x:v>
+      </x:c>
+      <x:c r="E12" s="6" t="str">
+        <x:v>None for controlled blank templates</x:v>
+      </x:c>
+      <x:c r="F12" s="6" t="str">
+        <x:v>Commissioning preparation owner</x:v>
+      </x:c>
+      <x:c r="G12" s="6" t="str">
+        <x:v>Issue to qualified execution team</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="str">
+        <x:v>Revision-G consistency and schema verification</x:v>
+      </x:c>
+      <x:c r="I12" s="6" t="str">
+        <x:v>None for preparation</x:v>
+      </x:c>
+      <x:c r="J12" s="6" t="str">
+        <x:v>VERIFIED AS DOCUMENTATION ONLY</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="54" customHeight="1">
+      <x:c r="A13" s="6" t="str">
+        <x:v>G3A-02</x:v>
+      </x:c>
+      <x:c r="B13" s="6" t="str">
+        <x:v>Construction information reconciled to final site/equipment inputs</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="str">
+        <x:v>Deterministic fictional schedules exist; Revision-F vision electrical delta and site calculations remain provisional</x:v>
+      </x:c>
+      <x:c r="D13" s="6" t="str">
+        <x:v>REQUIRES REAL DATA</x:v>
+      </x:c>
+      <x:c r="E13" s="6" t="str">
+        <x:v>Supply, earthing, fault current, motors, routes, ambient, enclosure and selected vision hardware</x:v>
+      </x:c>
+      <x:c r="F13" s="6" t="str">
+        <x:v>Qualified electrical designer</x:v>
+      </x:c>
+      <x:c r="G13" s="6" t="str">
+        <x:v>Finalize calculations and apply controlled QET/CAD change</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="str">
+        <x:v>Approved calculations, updated native QET/CAD and construction review</x:v>
+      </x:c>
+      <x:c r="I13" s="6" t="str">
+        <x:v>Site/equipment data and qualified review</x:v>
+      </x:c>
+      <x:c r="J13" s="6" t="str">
+        <x:v>PARTIAL - not construction ready</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="54" customHeight="1">
+      <x:c r="A14" s="6" t="str">
+        <x:v>G3B-01</x:v>
+      </x:c>
+      <x:c r="B14" s="6" t="str">
+        <x:v>Physical FAT/SAT and commissioning evidence</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="str">
+        <x:v>Blank records only</x:v>
+      </x:c>
+      <x:c r="D14" s="6" t="str">
+        <x:v>REQUIRES HARDWARE</x:v>
+      </x:c>
+      <x:c r="E14" s="6" t="str">
+        <x:v>Built panel/machine, calibrated instruments, site and qualified testers</x:v>
+      </x:c>
+      <x:c r="F14" s="6" t="str">
+        <x:v>Commissioning manager</x:v>
+      </x:c>
+      <x:c r="G14" s="6" t="str">
+        <x:v>Execute controlled procedures without prefilled values</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="str">
+        <x:v>Signed raw measurements, punch closure and as-built redlines</x:v>
+      </x:c>
+      <x:c r="I14" s="6" t="str">
+        <x:v>Hardware and personnel</x:v>
+      </x:c>
+      <x:c r="J14" s="6" t="str">
+        <x:v>0% EXECUTED</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="54" customHeight="1">
+      <x:c r="A15" s="6" t="str">
+        <x:v>G3C-01</x:v>
+      </x:c>
+      <x:c r="B15" s="6" t="str">
+        <x:v>Qualified electrical and machinery-safety review</x:v>
+      </x:c>
+      <x:c r="C15" s="6" t="str">
+        <x:v>Conceptual boundary, hazard assumptions and validation template only</x:v>
+      </x:c>
+      <x:c r="D15" s="6" t="str">
+        <x:v>REQUIRES QUALIFIED PERSON</x:v>
+      </x:c>
+      <x:c r="E15" s="6" t="str">
+        <x:v>Named competent electrical and machinery-safety engineers plus project risk assessment</x:v>
+      </x:c>
+      <x:c r="F15" s="6" t="str">
+        <x:v>Project owner</x:v>
+      </x:c>
+      <x:c r="G15" s="6" t="str">
+        <x:v>Submit qualified-review handoff</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="str">
+        <x:v>Signed review, validated calculations and safety lifecycle records</x:v>
+      </x:c>
+      <x:c r="I15" s="6" t="str">
+        <x:v>Qualified people and organization approval</x:v>
+      </x:c>
+      <x:c r="J15" s="6" t="str">
+        <x:v>0% EXECUTED</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
     <x:col min="1" max="1" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="19.3799991607666" hidden="0" customWidth="1"/>
@@ -2805,7 +3329,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -7155,7 +7679,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -14313,7 +14837,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -15213,7 +15737,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -22371,7 +22895,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -24207,246 +24731,6 @@
       </x:c>
       <x:c r="J63" s="6" t="str">
         <x:v>=FC01+FLD-B131</x:v>
-      </x:c>
-    </x:row>
-  </x:sheetData>
-  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </x:tableParts>
-</x:worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:sheetFormatPr defaultRowHeight="15"/>
-  <x:cols>
-    <x:col min="1" max="1" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="4" max="4" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="5" max="5" width="19.3799991607666" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="33.75" hidden="0" customWidth="1"/>
-  </x:cols>
-  <x:sheetData>
-    <x:row r="1" ht="31.5" customHeight="1">
-      <x:c r="A1" s="12" t="str">
-        <x:v>load</x:v>
-      </x:c>
-      <x:c r="B1" s="12" t="str">
-        <x:v>voltage</x:v>
-      </x:c>
-      <x:c r="C1" s="12" t="str">
-        <x:v>nominal_w</x:v>
-      </x:c>
-      <x:c r="D1" s="12" t="str">
-        <x:v>demand_factor</x:v>
-      </x:c>
-      <x:c r="E1" s="12" t="str">
-        <x:v>demand_w</x:v>
-      </x:c>
-      <x:c r="F1" s="12" t="str">
-        <x:v>basis</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="2" ht="54" customHeight="1">
-      <x:c r="A2" s="6" t="str">
-        <x:v>PLC CPU and I/O</x:v>
-      </x:c>
-      <x:c r="B2" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C2" s="6" t="str">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D2" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E2" s="6" t="str">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F2" s="6" t="str">
-        <x:v>Preliminary allowance; verify Siemens configuration</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" ht="54" customHeight="1">
-      <x:c r="A3" s="6" t="str">
-        <x:v>HMI</x:v>
-      </x:c>
-      <x:c r="B3" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C3" s="6" t="str">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D3" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E3" s="6" t="str">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F3" s="6" t="str">
-        <x:v>Maximum-current allowance from product data</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" ht="54" customHeight="1">
-      <x:c r="A4" s="6" t="str">
-        <x:v>Relays, sensors and solenoids</x:v>
-      </x:c>
-      <x:c r="B4" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C4" s="6" t="str">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="D4" s="6" t="str">
-        <x:v>0.8</x:v>
-      </x:c>
-      <x:c r="E4" s="6" t="str">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="F4" s="6" t="str">
-        <x:v>Duty-cycle allowance; inrush not finalized</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" ht="54" customHeight="1">
-      <x:c r="A5" s="6" t="str">
-        <x:v>Vision edge compute allowance</x:v>
-      </x:c>
-      <x:c r="B5" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C5" s="6" t="str">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="D5" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E5" s="6" t="str">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F5" s="6" t="str">
-        <x:v>Provisional branch -F220; carrier/input/inrush unconfirmed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" ht="54" customHeight="1">
-      <x:c r="A6" s="6" t="str">
-        <x:v>Vision camera allowance</x:v>
-      </x:c>
-      <x:c r="B6" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C6" s="6" t="str">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D6" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E6" s="6" t="str">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="F6" s="6" t="str">
-        <x:v>Provisional branch -F221; PoE not assumed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" ht="54" customHeight="1">
-      <x:c r="A7" s="6" t="str">
-        <x:v>Vision lighting allowance</x:v>
-      </x:c>
-      <x:c r="B7" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C7" s="6" t="str">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D7" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E7" s="6" t="str">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="F7" s="6" t="str">
-        <x:v>Provisional branch -F222; pulse duty/inrush unconfirmed</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" ht="54" customHeight="1">
-      <x:c r="A8" s="6" t="str">
-        <x:v>Vision service/network allowance</x:v>
-      </x:c>
-      <x:c r="B8" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C8" s="6" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E8" s="6" t="str">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="F8" s="6" t="str">
-        <x:v>Provisional branch -F223; maintenance-only service</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" ht="54" customHeight="1">
-      <x:c r="A9" s="6" t="str">
-        <x:v>24 VDC subtotal</x:v>
-      </x:c>
-      <x:c r="B9" s="6" t="str">
-        <x:v>24 VDC</x:v>
-      </x:c>
-      <x:c r="C9" s="6" t="str">
-        <x:v>329</x:v>
-      </x:c>
-      <x:c r="D9" s="6" t="str">
-        <x:v>N/A</x:v>
-      </x:c>
-      <x:c r="E9" s="6" t="str">
-        <x:v>299</x:v>
-      </x:c>
-      <x:c r="F9" s="6" t="str">
-        <x:v>12.458 A demand; 20 A concept leaves 7.542 A (37.71% of rating) unused; minimum 15.573 A for 25% demand margin before inrush/derating</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" ht="54" customHeight="1">
-      <x:c r="A10" s="6" t="str">
-        <x:v>Conveyor drive</x:v>
-      </x:c>
-      <x:c r="B10" s="6" t="str">
-        <x:v>400 VAC</x:v>
-      </x:c>
-      <x:c r="C10" s="6" t="str">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="D10" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E10" s="6" t="str">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="F10" s="6" t="str">
-        <x:v>Motor nameplate not supplied</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" ht="54" customHeight="1">
-      <x:c r="A11" s="6" t="str">
-        <x:v>Pump drive</x:v>
-      </x:c>
-      <x:c r="B11" s="6" t="str">
-        <x:v>400 VAC</x:v>
-      </x:c>
-      <x:c r="C11" s="6" t="str">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="D11" s="6" t="str">
-        <x:v>1.0</x:v>
-      </x:c>
-      <x:c r="E11" s="6" t="str">
-        <x:v>750</x:v>
-      </x:c>
-      <x:c r="F11" s="6" t="str">
-        <x:v>Pump curve/motor nameplate not supplied</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -26662,6 +26946,246 @@
     <x:col min="1" max="1" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="2" max="2" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="4" max="4" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="33.75" hidden="0" customWidth="1"/>
+  </x:cols>
+  <x:sheetData>
+    <x:row r="1" ht="31.5" customHeight="1">
+      <x:c r="A1" s="12" t="str">
+        <x:v>load</x:v>
+      </x:c>
+      <x:c r="B1" s="12" t="str">
+        <x:v>voltage</x:v>
+      </x:c>
+      <x:c r="C1" s="12" t="str">
+        <x:v>nominal_w</x:v>
+      </x:c>
+      <x:c r="D1" s="12" t="str">
+        <x:v>demand_factor</x:v>
+      </x:c>
+      <x:c r="E1" s="12" t="str">
+        <x:v>demand_w</x:v>
+      </x:c>
+      <x:c r="F1" s="12" t="str">
+        <x:v>basis</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="54" customHeight="1">
+      <x:c r="A2" s="6" t="str">
+        <x:v>PLC CPU and I/O</x:v>
+      </x:c>
+      <x:c r="B2" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C2" s="6" t="str">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D2" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E2" s="6" t="str">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F2" s="6" t="str">
+        <x:v>Preliminary allowance; verify Siemens configuration</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="54" customHeight="1">
+      <x:c r="A3" s="6" t="str">
+        <x:v>HMI</x:v>
+      </x:c>
+      <x:c r="B3" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C3" s="6" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D3" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E3" s="6" t="str">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F3" s="6" t="str">
+        <x:v>Maximum-current allowance from product data</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="54" customHeight="1">
+      <x:c r="A4" s="6" t="str">
+        <x:v>Relays, sensors and solenoids</x:v>
+      </x:c>
+      <x:c r="B4" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C4" s="6" t="str">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="D4" s="6" t="str">
+        <x:v>0.8</x:v>
+      </x:c>
+      <x:c r="E4" s="6" t="str">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F4" s="6" t="str">
+        <x:v>Duty-cycle allowance; inrush not finalized</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="54" customHeight="1">
+      <x:c r="A5" s="6" t="str">
+        <x:v>Vision edge compute allowance</x:v>
+      </x:c>
+      <x:c r="B5" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C5" s="6" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="D5" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E5" s="6" t="str">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F5" s="6" t="str">
+        <x:v>Provisional branch -F220; carrier/input/inrush unconfirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="54" customHeight="1">
+      <x:c r="A6" s="6" t="str">
+        <x:v>Vision camera allowance</x:v>
+      </x:c>
+      <x:c r="B6" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C6" s="6" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="D6" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E6" s="6" t="str">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="F6" s="6" t="str">
+        <x:v>Provisional branch -F221; PoE not assumed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="54" customHeight="1">
+      <x:c r="A7" s="6" t="str">
+        <x:v>Vision lighting allowance</x:v>
+      </x:c>
+      <x:c r="B7" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C7" s="6" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="D7" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E7" s="6" t="str">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="F7" s="6" t="str">
+        <x:v>Provisional branch -F222; pulse duty/inrush unconfirmed</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="54" customHeight="1">
+      <x:c r="A8" s="6" t="str">
+        <x:v>Vision service/network allowance</x:v>
+      </x:c>
+      <x:c r="B8" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C8" s="6" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="D8" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E8" s="6" t="str">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="F8" s="6" t="str">
+        <x:v>Provisional branch -F223; maintenance-only service</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="54" customHeight="1">
+      <x:c r="A9" s="6" t="str">
+        <x:v>24 VDC subtotal</x:v>
+      </x:c>
+      <x:c r="B9" s="6" t="str">
+        <x:v>24 VDC</x:v>
+      </x:c>
+      <x:c r="C9" s="6" t="str">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="D9" s="6" t="str">
+        <x:v>N/A</x:v>
+      </x:c>
+      <x:c r="E9" s="6" t="str">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="F9" s="6" t="str">
+        <x:v>12.458 A demand; 20 A concept leaves 7.542 A (37.71% of rating) unused; minimum 15.573 A for 25% demand margin before inrush/derating</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="54" customHeight="1">
+      <x:c r="A10" s="6" t="str">
+        <x:v>Conveyor drive</x:v>
+      </x:c>
+      <x:c r="B10" s="6" t="str">
+        <x:v>400 VAC</x:v>
+      </x:c>
+      <x:c r="C10" s="6" t="str">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="D10" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E10" s="6" t="str">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="F10" s="6" t="str">
+        <x:v>Motor nameplate not supplied</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="54" customHeight="1">
+      <x:c r="A11" s="6" t="str">
+        <x:v>Pump drive</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="str">
+        <x:v>400 VAC</x:v>
+      </x:c>
+      <x:c r="C11" s="6" t="str">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="D11" s="6" t="str">
+        <x:v>1.0</x:v>
+      </x:c>
+      <x:c r="E11" s="6" t="str">
+        <x:v>750</x:v>
+      </x:c>
+      <x:c r="F11" s="6" t="str">
+        <x:v>Pump curve/motor nameplate not supplied</x:v>
+      </x:c>
+    </x:row>
+  </x:sheetData>
+  <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <x:tableParts count="1">
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </x:tableParts>
+</x:worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <x:sheetFormatPr defaultRowHeight="15"/>
+  <x:cols>
+    <x:col min="1" max="1" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="19.3799991607666" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="10.630000114440918" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="19.3799991607666" hidden="0" customWidth="1"/>
     <x:col min="6" max="6" width="19.3799991607666" hidden="0" customWidth="1"/>
@@ -27435,7 +27959,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -28514,7 +29038,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -30214,7 +30738,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -30902,7 +31426,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -30937,7 +31461,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D2" s="6" t="str">
-        <x:v>Revision-F requirements and evidence are traceable; identified owner approval remains absent</x:v>
+        <x:v>Revision-G requirements, execution gates and evidence are traceable; owner and qualified-human approvals remain absent</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="54" customHeight="1">
@@ -30951,7 +31475,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D3" s="6" t="str">
-        <x:v>Core canonical/interface schedules reconcile; the standalone Revision-F NVIDIA electrical delta is internally consistent but is not yet incorporated into canonical BOM/terminal/cable/P2P/QET/CAD authorities</x:v>
+        <x:v>Core authorities reconcile; the Revision-F NVIDIA electrical delta remains provisional and outside final QET/CAD/construction authorities</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="54" customHeight="1">
@@ -30965,7 +31489,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D4" s="6" t="str">
-        <x:v>V20/FW4.0 source baseline and selected envelopes documented; authorized native catalog confirmation and delivered-state evidence remain open</x:v>
+        <x:v>TIA V20/Openness installation is inventoried exactly; authorized native catalog confirmation and delivered hardware remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="54" customHeight="1">
@@ -30979,7 +31503,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D5" s="6" t="str">
-        <x:v>No genuine AP20 project; active identity is not TIA Engineer/Openness-authorized and V20 entitlement is unproven</x:v>
+        <x:v>TIA V20 exists but no licensed/Openness-authorized session or genuine AP20 project was available</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="54" customHeight="1">
@@ -30993,7 +31517,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D6" s="6" t="str">
-        <x:v>No genuine ZAP20 archive exists; native authorized project creation/restoration was not available</x:v>
+        <x:v>No genuine ZAP20 archive exists; no native archive was fabricated</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="54" customHeight="1">
@@ -31007,7 +31531,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D7" s="6" t="str">
-        <x:v>Expanded import-ready SCL/source contracts pass locally; native TIA V20 compile was not run</x:v>
+        <x:v>99 Siemens/source/simulator contract tests pass; native TIA compile was not run</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="54" customHeight="1">
@@ -31021,7 +31545,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D8" s="6" t="str">
-        <x:v>Expanded HMI definitions are source-controlled; native WinCC Unified compile/usability review was not run</x:v>
+        <x:v>HMI definitions are controlled; native WinCC Unified compile/usability review was not run</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="54" customHeight="1">
@@ -31035,7 +31559,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D9" s="6" t="str">
-        <x:v>Startdrive is not installed; motor, pump and site inputs are also missing</x:v>
+        <x:v>Startdrive is absent and motor/pump/site data remain unconfirmed</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="54" customHeight="1">
@@ -31049,7 +31573,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D10" s="6" t="str">
-        <x:v>PLCSIM/PLCSIM Advanced are not installed; deterministic Python evidence is explicitly independent</x:v>
+        <x:v>PLCSIM/PLCSIM Advanced are absent; Python evidence is independent and explicitly non-native</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="54" customHeight="1">
@@ -31063,7 +31587,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D11" s="6" t="str">
-        <x:v>Exact controlled Revision-E QET hash reopened natively with 26/26 folios; automatic cross-reference resolution remains unsupported</x:v>
+        <x:v>Inherited exact-hash 26-folio QET reopen remains valid; executable was not found for a new Revision-G execution and automatic cross-references remain unsupported</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="54" customHeight="1">
@@ -31077,7 +31601,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D12" s="6" t="str">
-        <x:v>Native 26-page PDF export completed; all pages were reviewed, with one clipped in-body statement on folio 25 and dense text noted</x:v>
+        <x:v>Inherited 26-page native export was reviewed; folio 25 clipping/density limitation remains open</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="54" customHeight="1">
@@ -31091,7 +31615,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D13" s="6" t="str">
-        <x:v>FreeCADCmd independently reopened 165 objects / 148 controlled solids; STEP retained 148 solids; IGES retained bounded face geometry; DXF entities and 30 scheduled holes reconciled</x:v>
+        <x:v>FreeCADCmd 1.1.3 re-executed in Revision G: 165 objects, 148 solids, zero invalid shapes</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="54" customHeight="1">
@@ -31105,7 +31629,7 @@
         <x:v>PASS</x:v>
       </x:c>
       <x:c r="D14" s="6" t="str">
-        <x:v>FreeCADCmd independently reopened 165 objects / 148 controlled solids; STEP retained 148 solids; IGES retained bounded face geometry; DXF entities and 30 scheduled holes reconciled</x:v>
+        <x:v>Revision-G FreeCAD execution reimported STEP/IGES/DXF and reconciled 30 mounting holes</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="54" customHeight="1">
@@ -31119,7 +31643,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D15" s="6" t="str">
-        <x:v>Revision-E panel CAD remains natively verified; Revision-F electrical delta uses provisional carrier/camera/light envelopes and is not incorporated into QET/CAD</x:v>
+        <x:v>Revision-E CAD remains natively verified; final selected vision envelopes and electrical delta incorporation remain open</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="54" customHeight="1">
@@ -31133,7 +31657,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D16" s="6" t="str">
-        <x:v>Supply, earthing, fault current, motors/pump, cable routes, installation method, ambient and enclosure/site requirements remain unconfirmed</x:v>
+        <x:v>Supply, earthing, fault current, motor/pump, routes, installation, ambient and enclosure inputs remain absent</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="54" customHeight="1">
@@ -31147,7 +31671,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D17" s="6" t="str">
-        <x:v>Dataset tooling, schema, collection matrix and leakage-safe split checks are ready; no representative labeled dataset exists</x:v>
+        <x:v>Dataset acquisition/labeling/schema tooling is controlled; representative real data is absent</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="54" customHeight="1">
@@ -31161,7 +31685,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D18" s="6" t="str">
-        <x:v>Training/evaluation tooling is ready; no approved dataset, training run, model or defensible production metrics exist</x:v>
+        <x:v>Training/evaluation configuration is ready; no approved dataset, training run, model or metric exists</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="54" customHeight="1">
@@ -31175,7 +31699,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D19" s="6" t="str">
-        <x:v>DeepStream 9.1/TAO 7.0.1 policy is documented; CUDA/TAO/TensorRT/DeepStream/Docker and target hardware are absent</x:v>
+        <x:v>RTX 5060 driver query passed; CUDA, Docker, TAO, TensorRT, DeepStream and target Jetson/cloud runtime are absent</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="54" customHeight="1">
@@ -31189,7 +31713,7 @@
         <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D20" s="6" t="str">
-        <x:v>Source, edge, durable-audit, encrypted OPC UA and interface tests pass locally; native SCL enum binding, production S7/Jetson endpoint and physical timing remain unverified</x:v>
+        <x:v>Fail-closed edge/OPC UA/harness/synthetic-authorization tests pass; production S7/Jetson endpoint and physical timing remain unverified</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="54" customHeight="1">
@@ -31203,7 +31727,7 @@
         <x:v>OPEN</x:v>
       </x:c>
       <x:c r="D21" s="6" t="str">
-        <x:v>Controlled procedures issued; no FAT, SAT or commissioning was executed</x:v>
+        <x:v>G3A procedures and blank records are issued; no FAT, SAT or commissioning measurement was executed</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="54" customHeight="1">
@@ -31217,7 +31741,7 @@
         <x:v>BLOCKED</x:v>
       </x:c>
       <x:c r="D22" s="6" t="str">
-        <x:v>Project-specific qualified machinery-safety engineering, verification and validation are external and not performed</x:v>
+        <x:v>Conceptual boundary and handoff exist; qualified machinery-safety/electrical verification and validation were not performed</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="54" customHeight="1">
@@ -31228,10 +31752,10 @@
         <x:v>Manifest independently verifies</x:v>
       </x:c>
       <x:c r="C23" s="6" t="str">
-        <x:v>PASS</x:v>
+        <x:v>PARTIAL</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
-        <x:v>Published candidate f6e9f3b1e928a2e04d21913caac2547469b0f647 reproduced from GitHub with 425/425 manifest entries, zero discrepancies and final Git-clean assertion</x:v>
+        <x:v>Revision-G candidate manifest, final commit and post-push fresh-clone reproduction are pending release freeze</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -31242,7 +31766,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -31894,6 +32418,286 @@
         <x:v>Software-agent evidence</x:v>
       </x:c>
     </x:row>
+    <x:row r="33" ht="54" customHeight="1">
+      <x:c r="A33" s="6" t="str">
+        <x:v>DOC-G-001</x:v>
+      </x:c>
+      <x:c r="B33" s="6" t="str">
+        <x:v>Revision-G charter</x:v>
+      </x:c>
+      <x:c r="C33" s="6" t="str">
+        <x:v>00_project_control/revision_g_charter.md</x:v>
+      </x:c>
+      <x:c r="D33" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E33" s="6" t="str">
+        <x:v>Lead systems</x:v>
+      </x:c>
+      <x:c r="F33" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="54" customHeight="1">
+      <x:c r="A34" s="6" t="str">
+        <x:v>DOC-G-002</x:v>
+      </x:c>
+      <x:c r="B34" s="6" t="str">
+        <x:v>Revision-G gap matrix</x:v>
+      </x:c>
+      <x:c r="C34" s="6" t="str">
+        <x:v>00_project_control/revision_g_gap_matrix.csv</x:v>
+      </x:c>
+      <x:c r="D34" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E34" s="6" t="str">
+        <x:v>Lead systems</x:v>
+      </x:c>
+      <x:c r="F34" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="54" customHeight="1">
+      <x:c r="A35" s="6" t="str">
+        <x:v>DOC-G-003</x:v>
+      </x:c>
+      <x:c r="B35" s="6" t="str">
+        <x:v>Secure cloud architecture</x:v>
+      </x:c>
+      <x:c r="C35" s="6" t="str">
+        <x:v>cloud/architecture.md</x:v>
+      </x:c>
+      <x:c r="D35" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E35" s="6" t="str">
+        <x:v>Cloud security</x:v>
+      </x:c>
+      <x:c r="F35" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="54" customHeight="1">
+      <x:c r="A36" s="6" t="str">
+        <x:v>DOC-G-004</x:v>
+      </x:c>
+      <x:c r="B36" s="6" t="str">
+        <x:v>Cloud Terraform source</x:v>
+      </x:c>
+      <x:c r="C36" s="6" t="str">
+        <x:v>cloud/terraform/README.md</x:v>
+      </x:c>
+      <x:c r="D36" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E36" s="6" t="str">
+        <x:v>Cloud security</x:v>
+      </x:c>
+      <x:c r="F36" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="54" customHeight="1">
+      <x:c r="A37" s="6" t="str">
+        <x:v>DOC-G-005</x:v>
+      </x:c>
+      <x:c r="B37" s="6" t="str">
+        <x:v>Siemens native report</x:v>
+      </x:c>
+      <x:c r="C37" s="6" t="str">
+        <x:v>siemens_native/native_execution_report.md</x:v>
+      </x:c>
+      <x:c r="D37" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E37" s="6" t="str">
+        <x:v>Controls</x:v>
+      </x:c>
+      <x:c r="F37" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="54" customHeight="1">
+      <x:c r="A38" s="6" t="str">
+        <x:v>DOC-G-006</x:v>
+      </x:c>
+      <x:c r="B38" s="6" t="str">
+        <x:v>NVIDIA native report</x:v>
+      </x:c>
+      <x:c r="C38" s="6" t="str">
+        <x:v>nvidia_native/native_execution_report.md</x:v>
+      </x:c>
+      <x:c r="D38" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E38" s="6" t="str">
+        <x:v>Vision</x:v>
+      </x:c>
+      <x:c r="F38" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="54" customHeight="1">
+      <x:c r="A39" s="6" t="str">
+        <x:v>DOC-G-007</x:v>
+      </x:c>
+      <x:c r="B39" s="6" t="str">
+        <x:v>Commissioning package</x:v>
+      </x:c>
+      <x:c r="C39" s="6" t="str">
+        <x:v>commissioning/README.md</x:v>
+      </x:c>
+      <x:c r="D39" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E39" s="6" t="str">
+        <x:v>Commissioning</x:v>
+      </x:c>
+      <x:c r="F39" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="54" customHeight="1">
+      <x:c r="A40" s="6" t="str">
+        <x:v>DOC-G-008</x:v>
+      </x:c>
+      <x:c r="B40" s="6" t="str">
+        <x:v>Revision-G limitations</x:v>
+      </x:c>
+      <x:c r="C40" s="6" t="str">
+        <x:v>release/REVISION_G_KNOWN_LIMITATIONS.md</x:v>
+      </x:c>
+      <x:c r="D40" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E40" s="6" t="str">
+        <x:v>Release</x:v>
+      </x:c>
+      <x:c r="F40" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="54" customHeight="1">
+      <x:c r="A41" s="6" t="str">
+        <x:v>DOC-G-009</x:v>
+      </x:c>
+      <x:c r="B41" s="6" t="str">
+        <x:v>Revision-G evidence PDF</x:v>
+      </x:c>
+      <x:c r="C41" s="6" t="str">
+        <x:v>release/FC01_release_evidence.pdf</x:v>
+      </x:c>
+      <x:c r="D41" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E41" s="6" t="str">
+        <x:v>Release</x:v>
+      </x:c>
+      <x:c r="F41" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="54" customHeight="1">
+      <x:c r="A42" s="6" t="str">
+        <x:v>DOC-G-010</x:v>
+      </x:c>
+      <x:c r="B42" s="6" t="str">
+        <x:v>Revision-G engineering workbook</x:v>
+      </x:c>
+      <x:c r="C42" s="6" t="str">
+        <x:v>10_schedules/FC01_engineering_schedules.xlsx</x:v>
+      </x:c>
+      <x:c r="D42" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E42" s="6" t="str">
+        <x:v>Release</x:v>
+      </x:c>
+      <x:c r="F42" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="54" customHeight="1">
+      <x:c r="A43" s="6" t="str">
+        <x:v>DOC-G-011</x:v>
+      </x:c>
+      <x:c r="B43" s="6" t="str">
+        <x:v>Revision-G adversarial self-audit</x:v>
+      </x:c>
+      <x:c r="C43" s="6" t="str">
+        <x:v>14_qa/revision_g_audit_report.md</x:v>
+      </x:c>
+      <x:c r="D43" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E43" s="6" t="str">
+        <x:v>Release</x:v>
+      </x:c>
+      <x:c r="F43" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="54" customHeight="1">
+      <x:c r="A44" s="6" t="str">
+        <x:v>DOC-G-012</x:v>
+      </x:c>
+      <x:c r="B44" s="6" t="str">
+        <x:v>NVIDIA model/runtime evidence status</x:v>
+      </x:c>
+      <x:c r="C44" s="6" t="str">
+        <x:v>nvidia_native/model_card.md</x:v>
+      </x:c>
+      <x:c r="D44" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E44" s="6" t="str">
+        <x:v>Vision</x:v>
+      </x:c>
+      <x:c r="F44" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="54" customHeight="1">
+      <x:c r="A45" s="6" t="str">
+        <x:v>DOC-G-013</x:v>
+      </x:c>
+      <x:c r="B45" s="6" t="str">
+        <x:v>Qualified safety-review preparation</x:v>
+      </x:c>
+      <x:c r="C45" s="6" t="str">
+        <x:v>commissioning/qualified_review_handoff.md</x:v>
+      </x:c>
+      <x:c r="D45" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E45" s="6" t="str">
+        <x:v>Safety boundary</x:v>
+      </x:c>
+      <x:c r="F45" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="54" customHeight="1">
+      <x:c r="A46" s="6" t="str">
+        <x:v>DOC-G-014</x:v>
+      </x:c>
+      <x:c r="B46" s="6" t="str">
+        <x:v>Cloud plan status</x:v>
+      </x:c>
+      <x:c r="C46" s="6" t="str">
+        <x:v>cloud/plan_status.md</x:v>
+      </x:c>
+      <x:c r="D46" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E46" s="6" t="str">
+        <x:v>Cloud security</x:v>
+      </x:c>
+      <x:c r="F46" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
@@ -31902,7 +32706,7 @@
 </x:worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
@@ -31939,7 +32743,7 @@
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="24" t="str">
-        <x:v>FICTIONAL ENGINEERING PROJECT - NOT FOR CONSTRUCTION | Revision F | NVIDIA implementation-readiness release candidate</x:v>
+        <x:v>FICTIONAL ENGINEERING PROJECT - NOT FOR CONSTRUCTION | Revision G | cloud-ready and native-execution-ready release candidate</x:v>
       </x:c>
       <x:c r="B3" s="24"/>
       <x:c r="C3" s="24"/>
@@ -31951,7 +32755,7 @@
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="30" t="str">
-        <x:v>CONCEPTUAL SAFETY ARCHITECTURE - REQUIRES PROJECT-SPECIFIC RISK ASSESSMENT, DESIGN, VERIFICATION AND VALIDATION BY A QUALIFIED MACHINERY-SAFETY ENGINEER. NO PERFORMANCE LEVEL, SIL, CATEGORY, CE CONFORMITY OR REGULATORY COMPLIANCE IS CLAIMED.</x:v>
+        <x:v>CONCEPTUAL SAFETY ARCHITECTURE - REQUIRES PROJECT-SPECIFIC RISK ASSESSMENT, DESIGN, VERIFICATION AND VALIDATION BY A QUALIFIED MACHINERY-SAFETY ENGINEER. NO PERFORMANCE LEVEL, SIL, CATEGORY, CE/UKCA CONFORMITY OR REGULATORY COMPLIANCE IS CLAIMED.</x:v>
       </x:c>
       <x:c r="B4" s="30"/>
       <x:c r="C4" s="30"/>
@@ -31985,7 +32789,7 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="D6" s="46" t="str">
-        <x:v>Revision F includes a source-tested 47-node fail-closed PLC/AI contract, production-structured edge and dataset tooling, 28 structured behavioral vision fault injections, a controlled electrical delta, secure local asyncua integration and inherited native CAD/QET evidence. The behavioral model is software-only evidence, not PLCSIM, HIL or physical testing. THE NVIDIA VISION SUBSYSTEM IS NON-SAFETY-RELATED AND MUST NOT BE USED AS THE SOLE MEANS OF PERSONNEL PROTECTION, SAFE STOP, GUARD MONITORING OR HAZARDOUS-MOTION CONTROL. Native Siemens, real dataset/model, target runtime, site electrical, FAT/SAT, qualified safety and physical commissioning remain blocked or open exactly as listed.</x:v>
+        <x:v>Revision G preserves the source-tested 47-node fail-closed PLC/AI contract, secure local asyncua integration, 28 structured behavioral fault injections and inherited native CAD/QET evidence. It adds disabled-by-default cloud infrastructure, actual Siemens/NVIDIA inventory, exact external handoffs, data/model execution scaffolding and blank commissioning records. The evidence is software/laboratory only: no cloud apply, TIA/WinCC/Startdrive/PLCSIM compile, representative dataset, trained model, target runtime, physical test or qualified approval exists. THE NVIDIA VISION SUBSYSTEM IS NON-SAFETY-RELATED AND MUST NOT COMMAND HAZARDOUS MOTION OR BYPASS PLC INTERLOCKS.</x:v>
       </x:c>
       <x:c r="E6" s="46"/>
       <x:c r="F6" s="46"/>
@@ -32082,7 +32886,7 @@
       </x:c>
       <x:c r="B13" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PASS")</x:f>
-        <x:v>3</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D13" s="46"/>
       <x:c r="E13" s="46"/>
@@ -32096,7 +32900,7 @@
       </x:c>
       <x:c r="B14" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PARTIAL")</x:f>
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D14" s="46"/>
       <x:c r="E14" s="46"/>

--- a/10_schedules/FC01_engineering_schedules.xlsx
+++ b/10_schedules/FC01_engineering_schedules.xlsx
@@ -584,8 +584,8 @@
 </file>
 
 <file path=xl/tables/table26.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="DocumentRegisterTable" displayName="DocumentRegisterTable" ref="A1:F46" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:F46"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="26" name="DocumentRegisterTable" displayName="DocumentRegisterTable" ref="A1:F47" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:F47"/>
   <x:tableColumns count="6">
     <x:tableColumn id="1" name="document_id"/>
     <x:tableColumn id="2" name="title"/>
@@ -31752,10 +31752,10 @@
         <x:v>Manifest independently verifies</x:v>
       </x:c>
       <x:c r="C23" s="6" t="str">
-        <x:v>PARTIAL</x:v>
+        <x:v>PASS</x:v>
       </x:c>
       <x:c r="D23" s="6" t="str">
-        <x:v>Revision-G candidate manifest, final commit and post-push fresh-clone reproduction are pending release freeze</x:v>
+        <x:v>Published candidate 38ab54deace5e6b71479bb4a347cd39c0233f37d reproduced from a fresh GitHub clone: manifest 504/504, zero discrepancies; see DOC-G-015</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -32695,6 +32695,26 @@
         <x:v>Cloud security</x:v>
       </x:c>
       <x:c r="F46" s="6" t="str">
+        <x:v>Controlled</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="54" customHeight="1">
+      <x:c r="A47" s="6" t="str">
+        <x:v>DOC-G-015</x:v>
+      </x:c>
+      <x:c r="B47" s="6" t="str">
+        <x:v>Revision-G post-push reproduction</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="str">
+        <x:v>14_qa/revision_g_post_push_reproduction.md</x:v>
+      </x:c>
+      <x:c r="D47" s="6" t="str">
+        <x:v>G</x:v>
+      </x:c>
+      <x:c r="E47" s="6" t="str">
+        <x:v>Configuration management</x:v>
+      </x:c>
+      <x:c r="F47" s="6" t="str">
         <x:v>Controlled</x:v>
       </x:c>
     </x:row>
@@ -32886,7 +32906,7 @@
       </x:c>
       <x:c r="B13" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PASS")</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D13" s="46"/>
       <x:c r="E13" s="46"/>
@@ -32900,7 +32920,7 @@
       </x:c>
       <x:c r="B14" t="n">
         <x:f>COUNTIF('Acceptance Gates'!C2:C100,"PARTIAL")</x:f>
-        <x:v>8</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D14" s="46"/>
       <x:c r="E14" s="46"/>
